--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_oilfield_svcs_equip.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="brvm_shec" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,25 +590,28 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0547</v>
+        <v>0.0786</v>
+      </c>
+      <c r="E2">
+        <v>-0.128</v>
       </c>
       <c r="G2">
-        <v>0.003804435810263882</v>
+        <v>0.02623294858342078</v>
       </c>
       <c r="H2">
-        <v>0.003804435810263882</v>
+        <v>0.02623294858342078</v>
       </c>
       <c r="I2">
-        <v>-0.01207706006151854</v>
+        <v>0.01146754609503823</v>
       </c>
       <c r="J2">
-        <v>-0.01207706006151854</v>
+        <v>0.008340033523664164</v>
       </c>
       <c r="K2">
-        <v>-9.210000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="L2">
-        <v>-0.01491015055852356</v>
+        <v>0.005036726128016789</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -615,7 +620,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -624,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,10 +641,10 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>0.09524117101732954</v>
+        <v>0.1506905496459751</v>
       </c>
       <c r="AB2">
-        <v>0.09524117101732954</v>
+        <v>0.1506905496459751</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -660,16 +665,16 @@
         <v>0</v>
       </c>
       <c r="AL2">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AM2">
-        <v>1.338</v>
+        <v>1.206</v>
       </c>
       <c r="AO2">
-        <v>-3.22943722943723</v>
+        <v>3.642857142857143</v>
       </c>
       <c r="AQ2">
-        <v>-5.575485799701046</v>
+        <v>6.343283582089553</v>
       </c>
     </row>
     <row r="3">
@@ -689,25 +694,28 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0547</v>
+        <v>0.0786</v>
+      </c>
+      <c r="E3">
+        <v>-0.128</v>
       </c>
       <c r="G3">
-        <v>0.003804435810263882</v>
+        <v>0.02623294858342078</v>
       </c>
       <c r="H3">
-        <v>0.003804435810263882</v>
+        <v>0.02623294858342078</v>
       </c>
       <c r="I3">
-        <v>-0.01207706006151854</v>
+        <v>0.01146754609503823</v>
       </c>
       <c r="J3">
-        <v>-0.01207706006151854</v>
+        <v>0.008340033523664164</v>
       </c>
       <c r="K3">
-        <v>-9.210000000000001</v>
+        <v>3.36</v>
       </c>
       <c r="L3">
-        <v>-0.01491015055852356</v>
+        <v>0.005036726128016789</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -716,7 +724,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -725,7 +733,7 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -737,10 +745,10 @@
         <v>0</v>
       </c>
       <c r="X3">
-        <v>0.09524117101732954</v>
+        <v>0.1506905496459751</v>
       </c>
       <c r="AB3">
-        <v>0.09524117101732954</v>
+        <v>0.1506905496459751</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -761,16 +769,8714 @@
         <v>0</v>
       </c>
       <c r="AL3">
+        <v>2.1</v>
+      </c>
+      <c r="AM3">
+        <v>1.206</v>
+      </c>
+      <c r="AO3">
+        <v>3.642857142857143</v>
+      </c>
+      <c r="AQ3">
+        <v>6.343283582089553</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Vivo Energy Cote d'Ivoire SA (BRVM:SHEC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>BRVM:SHEC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Oilfield Svcs/Equip.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0.01</v>
+      </c>
+      <c r="G2">
+        <v>77</v>
+      </c>
+      <c r="H2">
+        <v>55.916202787415</v>
+      </c>
+      <c r="I2">
+        <v>77</v>
+      </c>
+      <c r="J2">
+        <v>56.686202787415</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0.77</v>
+      </c>
+      <c r="M2">
+        <v>0.150690549645975</v>
+      </c>
+      <c r="N2">
+        <v>0.19078711324959</v>
+      </c>
+      <c r="O2">
+        <v>0.0684787844036697</v>
+      </c>
+      <c r="P2">
+        <v>2.83295584415584</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.150690549645975</v>
+      </c>
+      <c r="T2">
+        <v>0.164098540210133</v>
+      </c>
+      <c r="U2">
+        <v>0.92305985625808</v>
+      </c>
+      <c r="V2">
+        <v>1.03367132328564</v>
+      </c>
+      <c r="W2">
+        <v>-43.45319671952837</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>77</v>
+      </c>
+      <c r="AB2">
+        <v>0.1212170033041622</v>
+      </c>
+      <c r="AC2">
+        <v>0.09130504587155963</v>
+      </c>
+      <c r="AD2">
+        <v>0.25</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>7.99</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
+        <v>0</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2">
+        <v>2.1</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>77</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>7.99</v>
+      </c>
+      <c r="L2">
+        <v>-7.99</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-7.99</v>
+      </c>
+      <c r="O2">
+        <v>-1.9975</v>
+      </c>
+      <c r="P2">
+        <v>-5.9925</v>
+      </c>
+      <c r="Q2">
+        <v>1.9975</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1907871132495903</v>
+      </c>
+      <c r="C3">
+        <v>55.91620278741497</v>
+      </c>
+      <c r="D3">
+        <v>56.68620278741498</v>
+      </c>
+      <c r="E3">
+        <v>0.77</v>
+      </c>
+      <c r="F3">
+        <v>0.77</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>77</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>7.99</v>
+      </c>
+      <c r="L3">
+        <v>-7.99</v>
+      </c>
+      <c r="M3">
+        <v>0.183876</v>
+      </c>
+      <c r="N3">
+        <v>-8.173876</v>
+      </c>
+      <c r="O3">
+        <v>-2.043469</v>
+      </c>
+      <c r="P3">
+        <v>-6.130407</v>
+      </c>
+      <c r="Q3">
+        <v>1.859593</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1640985402101332</v>
+      </c>
+      <c r="T3">
+        <v>1.033671323285641</v>
+      </c>
+      <c r="U3">
+        <v>0.2388</v>
+      </c>
+      <c r="V3">
+        <v>-10.86329917988209</v>
+      </c>
+      <c r="W3">
+        <v>2.832955844155844</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-43.45319671952837</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1927871132495904</v>
+      </c>
+      <c r="C4">
+        <v>54.4099567264146</v>
+      </c>
+      <c r="D4">
+        <v>55.9499567264146</v>
+      </c>
+      <c r="E4">
+        <v>1.54</v>
+      </c>
+      <c r="F4">
+        <v>1.54</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>77</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>7.99</v>
+      </c>
+      <c r="L4">
+        <v>-7.99</v>
+      </c>
+      <c r="M4">
+        <v>0.367752</v>
+      </c>
+      <c r="N4">
+        <v>-8.357752</v>
+      </c>
+      <c r="O4">
+        <v>-2.089438</v>
+      </c>
+      <c r="P4">
+        <v>-6.268314</v>
+      </c>
+      <c r="Q4">
+        <v>1.721686</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1653770967428897</v>
+      </c>
+      <c r="T4">
+        <v>1.04421898984978</v>
+      </c>
+      <c r="U4">
+        <v>0.2388</v>
+      </c>
+      <c r="V4">
+        <v>-5.431649589941047</v>
+      </c>
+      <c r="W4">
+        <v>1.535877922077922</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-21.72659835976419</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1947871132495903</v>
+      </c>
+      <c r="C5">
+        <v>52.92259032914188</v>
+      </c>
+      <c r="D5">
+        <v>55.23259032914189</v>
+      </c>
+      <c r="E5">
         <v>2.31</v>
       </c>
-      <c r="AM3">
-        <v>1.338</v>
-      </c>
-      <c r="AO3">
-        <v>-3.22943722943723</v>
-      </c>
-      <c r="AQ3">
-        <v>-5.575485799701046</v>
+      <c r="F5">
+        <v>2.31</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>7.99</v>
+      </c>
+      <c r="L5">
+        <v>-7.99</v>
+      </c>
+      <c r="M5">
+        <v>0.551628</v>
+      </c>
+      <c r="N5">
+        <v>-8.541627999999999</v>
+      </c>
+      <c r="O5">
+        <v>-2.135407</v>
+      </c>
+      <c r="P5">
+        <v>-6.406220999999999</v>
+      </c>
+      <c r="Q5">
+        <v>1.583779000000001</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1666820152660123</v>
+      </c>
+      <c r="T5">
+        <v>1.054984134075035</v>
+      </c>
+      <c r="U5">
+        <v>0.2388</v>
+      </c>
+      <c r="V5">
+        <v>-3.621099726627365</v>
+      </c>
+      <c r="W5">
+        <v>1.103518614718615</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-14.48439890650946</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1967871132495903</v>
+      </c>
+      <c r="C6">
+        <v>51.45338658786099</v>
+      </c>
+      <c r="D6">
+        <v>54.53338658786099</v>
+      </c>
+      <c r="E6">
+        <v>3.08</v>
+      </c>
+      <c r="F6">
+        <v>3.08</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>77</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>7.99</v>
+      </c>
+      <c r="L6">
+        <v>-7.99</v>
+      </c>
+      <c r="M6">
+        <v>0.735504</v>
+      </c>
+      <c r="N6">
+        <v>-8.725504000000001</v>
+      </c>
+      <c r="O6">
+        <v>-2.181376</v>
+      </c>
+      <c r="P6">
+        <v>-6.544128000000001</v>
+      </c>
+      <c r="Q6">
+        <v>1.445872</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1680141195916999</v>
+      </c>
+      <c r="T6">
+        <v>1.065973552138317</v>
+      </c>
+      <c r="U6">
+        <v>0.2388</v>
+      </c>
+      <c r="V6">
+        <v>-2.715824794970524</v>
+      </c>
+      <c r="W6">
+        <v>0.887338961038961</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-10.86329917988209</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1987871132495903</v>
+      </c>
+      <c r="C7">
+        <v>50.00166434811051</v>
+      </c>
+      <c r="D7">
+        <v>53.85166434811051</v>
+      </c>
+      <c r="E7">
+        <v>3.85</v>
+      </c>
+      <c r="F7">
+        <v>3.85</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>77</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>7.99</v>
+      </c>
+      <c r="L7">
+        <v>-7.99</v>
+      </c>
+      <c r="M7">
+        <v>0.9193800000000001</v>
+      </c>
+      <c r="N7">
+        <v>-8.909380000000001</v>
+      </c>
+      <c r="O7">
+        <v>-2.227345</v>
+      </c>
+      <c r="P7">
+        <v>-6.682035000000001</v>
+      </c>
+      <c r="Q7">
+        <v>1.307964999999999</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.169374268218981</v>
+      </c>
+      <c r="T7">
+        <v>1.077194326371352</v>
+      </c>
+      <c r="U7">
+        <v>0.2388</v>
+      </c>
+      <c r="V7">
+        <v>-2.172659835976419</v>
+      </c>
+      <c r="W7">
+        <v>0.7576311688311688</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-8.690639343905675</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.2007871132495903</v>
+      </c>
+      <c r="C8">
+        <v>48.56677609536246</v>
+      </c>
+      <c r="D8">
+        <v>53.18677609536246</v>
+      </c>
+      <c r="E8">
+        <v>4.62</v>
+      </c>
+      <c r="F8">
+        <v>4.62</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>77</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>7.99</v>
+      </c>
+      <c r="L8">
+        <v>-7.99</v>
+      </c>
+      <c r="M8">
+        <v>1.103256</v>
+      </c>
+      <c r="N8">
+        <v>-9.093256</v>
+      </c>
+      <c r="O8">
+        <v>-2.273314</v>
+      </c>
+      <c r="P8">
+        <v>-6.819942</v>
+      </c>
+      <c r="Q8">
+        <v>1.170058</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1707633561787573</v>
+      </c>
+      <c r="T8">
+        <v>1.088653840481686</v>
+      </c>
+      <c r="U8">
+        <v>0.2388</v>
+      </c>
+      <c r="V8">
+        <v>-1.810549863313683</v>
+      </c>
+      <c r="W8">
+        <v>0.6711593073593075</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-7.242199453254729</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.2027871132495903</v>
+      </c>
+      <c r="C9">
+        <v>47.1481059036455</v>
+      </c>
+      <c r="D9">
+        <v>52.5381059036455</v>
+      </c>
+      <c r="E9">
+        <v>5.390000000000001</v>
+      </c>
+      <c r="F9">
+        <v>5.390000000000001</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>77</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>7.99</v>
+      </c>
+      <c r="L9">
+        <v>-7.99</v>
+      </c>
+      <c r="M9">
+        <v>1.287132</v>
+      </c>
+      <c r="N9">
+        <v>-9.277132</v>
+      </c>
+      <c r="O9">
+        <v>-2.319283</v>
+      </c>
+      <c r="P9">
+        <v>-6.957849</v>
+      </c>
+      <c r="Q9">
+        <v>1.032151000000001</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1721823169978837</v>
+      </c>
+      <c r="T9">
+        <v>1.100359795755682</v>
+      </c>
+      <c r="U9">
+        <v>0.2388</v>
+      </c>
+      <c r="V9">
+        <v>-1.551899882840299</v>
+      </c>
+      <c r="W9">
+        <v>0.6093936920222635</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-6.207599531361196</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.2047871132495903</v>
+      </c>
+      <c r="C10">
+        <v>45.74506753247212</v>
+      </c>
+      <c r="D10">
+        <v>51.90506753247212</v>
+      </c>
+      <c r="E10">
+        <v>6.16</v>
+      </c>
+      <c r="F10">
+        <v>6.16</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>77</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>7.99</v>
+      </c>
+      <c r="L10">
+        <v>-7.99</v>
+      </c>
+      <c r="M10">
+        <v>1.471008</v>
+      </c>
+      <c r="N10">
+        <v>-9.461008</v>
+      </c>
+      <c r="O10">
+        <v>-2.365252</v>
+      </c>
+      <c r="P10">
+        <v>-7.095756</v>
+      </c>
+      <c r="Q10">
+        <v>0.8942440000000005</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.173632124791339</v>
+      </c>
+      <c r="T10">
+        <v>1.112320228318244</v>
+      </c>
+      <c r="U10">
+        <v>0.2388</v>
+      </c>
+      <c r="V10">
+        <v>-1.357912397485262</v>
+      </c>
+      <c r="W10">
+        <v>0.5630694805194806</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-5.431649589941046</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.2067871132495903</v>
+      </c>
+      <c r="C11">
+        <v>44.35710265971008</v>
+      </c>
+      <c r="D11">
+        <v>51.28710265971008</v>
+      </c>
+      <c r="E11">
+        <v>6.93</v>
+      </c>
+      <c r="F11">
+        <v>6.93</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>77</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>7.99</v>
+      </c>
+      <c r="L11">
+        <v>-7.99</v>
+      </c>
+      <c r="M11">
+        <v>1.654884</v>
+      </c>
+      <c r="N11">
+        <v>-9.644884000000001</v>
+      </c>
+      <c r="O11">
+        <v>-2.411221</v>
+      </c>
+      <c r="P11">
+        <v>-7.233663000000001</v>
+      </c>
+      <c r="Q11">
+        <v>0.7563369999999994</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1751137964923427</v>
+      </c>
+      <c r="T11">
+        <v>1.124543527530532</v>
+      </c>
+      <c r="U11">
+        <v>0.2388</v>
+      </c>
+      <c r="V11">
+        <v>-1.207033242209122</v>
+      </c>
+      <c r="W11">
+        <v>0.5270395382395383</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-4.828132968836487</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.2087871132495904</v>
+      </c>
+      <c r="C12">
+        <v>42.98367923920165</v>
+      </c>
+      <c r="D12">
+        <v>50.68367923920165</v>
+      </c>
+      <c r="E12">
+        <v>7.7</v>
+      </c>
+      <c r="F12">
+        <v>7.7</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>77</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>7.99</v>
+      </c>
+      <c r="L12">
+        <v>-7.99</v>
+      </c>
+      <c r="M12">
+        <v>1.83876</v>
+      </c>
+      <c r="N12">
+        <v>-9.828760000000001</v>
+      </c>
+      <c r="O12">
+        <v>-2.45719</v>
+      </c>
+      <c r="P12">
+        <v>-7.37157</v>
+      </c>
+      <c r="Q12">
+        <v>0.61843</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1766283942311466</v>
+      </c>
+      <c r="T12">
+        <v>1.137038455614205</v>
+      </c>
+      <c r="U12">
+        <v>0.2388</v>
+      </c>
+      <c r="V12">
+        <v>-1.086329917988209</v>
+      </c>
+      <c r="W12">
+        <v>0.4982155844155843</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-4.345319671952837</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.2107871132495903</v>
+      </c>
+      <c r="C13">
+        <v>41.62428997297626</v>
+      </c>
+      <c r="D13">
+        <v>50.09428997297626</v>
+      </c>
+      <c r="E13">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="F13">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>77</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>7.99</v>
+      </c>
+      <c r="L13">
+        <v>-7.99</v>
+      </c>
+      <c r="M13">
+        <v>2.022636</v>
+      </c>
+      <c r="N13">
+        <v>-10.012636</v>
+      </c>
+      <c r="O13">
+        <v>-2.503159</v>
+      </c>
+      <c r="P13">
+        <v>-7.509477</v>
+      </c>
+      <c r="Q13">
+        <v>0.4805229999999998</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1781770278741931</v>
+      </c>
+      <c r="T13">
+        <v>1.149814168598634</v>
+      </c>
+      <c r="U13">
+        <v>0.2388</v>
+      </c>
+      <c r="V13">
+        <v>-0.9875726527165539</v>
+      </c>
+      <c r="W13">
+        <v>0.4746323494687131</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-3.950290610866215</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.2127871132495903</v>
+      </c>
+      <c r="C14">
+        <v>40.27845088883541</v>
+      </c>
+      <c r="D14">
+        <v>49.51845088883541</v>
+      </c>
+      <c r="E14">
+        <v>9.24</v>
+      </c>
+      <c r="F14">
+        <v>9.24</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>77</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>7.99</v>
+      </c>
+      <c r="L14">
+        <v>-7.99</v>
+      </c>
+      <c r="M14">
+        <v>2.206512</v>
+      </c>
+      <c r="N14">
+        <v>-10.196512</v>
+      </c>
+      <c r="O14">
+        <v>-2.549128</v>
+      </c>
+      <c r="P14">
+        <v>-7.647384000000001</v>
+      </c>
+      <c r="Q14">
+        <v>0.3426159999999996</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1797608577363999</v>
+      </c>
+      <c r="T14">
+        <v>1.162880238696346</v>
+      </c>
+      <c r="U14">
+        <v>0.2388</v>
+      </c>
+      <c r="V14">
+        <v>-0.9052749316568413</v>
+      </c>
+      <c r="W14">
+        <v>0.4549796536796538</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-3.621099726627365</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.2147871132495903</v>
+      </c>
+      <c r="C15">
+        <v>38.94570001492789</v>
+      </c>
+      <c r="D15">
+        <v>48.95570001492788</v>
+      </c>
+      <c r="E15">
+        <v>10.01</v>
+      </c>
+      <c r="F15">
+        <v>10.01</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>77</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>7.99</v>
+      </c>
+      <c r="L15">
+        <v>-7.99</v>
+      </c>
+      <c r="M15">
+        <v>2.390388</v>
+      </c>
+      <c r="N15">
+        <v>-10.380388</v>
+      </c>
+      <c r="O15">
+        <v>-2.595097</v>
+      </c>
+      <c r="P15">
+        <v>-7.785291</v>
+      </c>
+      <c r="Q15">
+        <v>0.2047090000000003</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1813810974804964</v>
+      </c>
+      <c r="T15">
+        <v>1.176246678221591</v>
+      </c>
+      <c r="U15">
+        <v>0.2388</v>
+      </c>
+      <c r="V15">
+        <v>-0.8356383984524688</v>
+      </c>
+      <c r="W15">
+        <v>0.4383504495504496</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-3.342553593809875</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.2167871132495904</v>
+      </c>
+      <c r="C16">
+        <v>37.62559614368549</v>
+      </c>
+      <c r="D16">
+        <v>48.40559614368549</v>
+      </c>
+      <c r="E16">
+        <v>10.78</v>
+      </c>
+      <c r="F16">
+        <v>10.78</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>77</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>7.99</v>
+      </c>
+      <c r="L16">
+        <v>-7.99</v>
+      </c>
+      <c r="M16">
+        <v>2.574264</v>
+      </c>
+      <c r="N16">
+        <v>-10.564264</v>
+      </c>
+      <c r="O16">
+        <v>-2.641066</v>
+      </c>
+      <c r="P16">
+        <v>-7.923198000000001</v>
+      </c>
+      <c r="Q16">
+        <v>0.06680199999999914</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1830390172186417</v>
+      </c>
+      <c r="T16">
+        <v>1.189923965177656</v>
+      </c>
+      <c r="U16">
+        <v>0.2388</v>
+      </c>
+      <c r="V16">
+        <v>-0.7759499414201495</v>
+      </c>
+      <c r="W16">
+        <v>0.4240968460111317</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-3.103799765680598</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.2187871132495904</v>
+      </c>
+      <c r="C17">
+        <v>36.31771767816935</v>
+      </c>
+      <c r="D17">
+        <v>47.86771767816935</v>
+      </c>
+      <c r="E17">
+        <v>11.55</v>
+      </c>
+      <c r="F17">
+        <v>11.55</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>77</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>7.99</v>
+      </c>
+      <c r="L17">
+        <v>-7.99</v>
+      </c>
+      <c r="M17">
+        <v>2.75814</v>
+      </c>
+      <c r="N17">
+        <v>-10.74814</v>
+      </c>
+      <c r="O17">
+        <v>-2.687035</v>
+      </c>
+      <c r="P17">
+        <v>-8.061105</v>
+      </c>
+      <c r="Q17">
+        <v>-0.07110499999999931</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1847359468329787</v>
+      </c>
+      <c r="T17">
+        <v>1.203923070650335</v>
+      </c>
+      <c r="U17">
+        <v>0.2388</v>
+      </c>
+      <c r="V17">
+        <v>-0.724219945325473</v>
+      </c>
+      <c r="W17">
+        <v>0.411743722943723</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-2.896879781301891</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.2207871132495904</v>
+      </c>
+      <c r="C18">
+        <v>35.02166155448634</v>
+      </c>
+      <c r="D18">
+        <v>47.34166155448634</v>
+      </c>
+      <c r="E18">
+        <v>12.32</v>
+      </c>
+      <c r="F18">
+        <v>12.32</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>77</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>7.99</v>
+      </c>
+      <c r="L18">
+        <v>-7.99</v>
+      </c>
+      <c r="M18">
+        <v>2.942016</v>
+      </c>
+      <c r="N18">
+        <v>-10.932016</v>
+      </c>
+      <c r="O18">
+        <v>-2.733004</v>
+      </c>
+      <c r="P18">
+        <v>-8.199012</v>
+      </c>
+      <c r="Q18">
+        <v>-0.2090119999999995</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1864732795333713</v>
+      </c>
+      <c r="T18">
+        <v>1.218255488158077</v>
+      </c>
+      <c r="U18">
+        <v>0.2388</v>
+      </c>
+      <c r="V18">
+        <v>-0.6789561987426309</v>
+      </c>
+      <c r="W18">
+        <v>0.4009347402597403</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-2.715824794970524</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.2227871132495903</v>
+      </c>
+      <c r="C19">
+        <v>33.73704223448794</v>
+      </c>
+      <c r="D19">
+        <v>46.82704223448795</v>
+      </c>
+      <c r="E19">
+        <v>13.09</v>
+      </c>
+      <c r="F19">
+        <v>13.09</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>77</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>7.99</v>
+      </c>
+      <c r="L19">
+        <v>-7.99</v>
+      </c>
+      <c r="M19">
+        <v>3.125892</v>
+      </c>
+      <c r="N19">
+        <v>-11.115892</v>
+      </c>
+      <c r="O19">
+        <v>-2.778973</v>
+      </c>
+      <c r="P19">
+        <v>-8.336919</v>
+      </c>
+      <c r="Q19">
+        <v>-0.3469189999999998</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1882524756723276</v>
+      </c>
+      <c r="T19">
+        <v>1.232933265123837</v>
+      </c>
+      <c r="U19">
+        <v>0.2388</v>
+      </c>
+      <c r="V19">
+        <v>-0.6390175988165937</v>
+      </c>
+      <c r="W19">
+        <v>0.3913974025974026</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-2.556070395266375</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.2247871132495903</v>
+      </c>
+      <c r="C20">
+        <v>32.46349076346053</v>
+      </c>
+      <c r="D20">
+        <v>46.32349076346053</v>
+      </c>
+      <c r="E20">
+        <v>13.86</v>
+      </c>
+      <c r="F20">
+        <v>13.86</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>77</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>7.99</v>
+      </c>
+      <c r="L20">
+        <v>-7.99</v>
+      </c>
+      <c r="M20">
+        <v>3.309768</v>
+      </c>
+      <c r="N20">
+        <v>-11.299768</v>
+      </c>
+      <c r="O20">
+        <v>-2.824942</v>
+      </c>
+      <c r="P20">
+        <v>-8.474826</v>
+      </c>
+      <c r="Q20">
+        <v>-0.484826</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1900750668390633</v>
+      </c>
+      <c r="T20">
+        <v>1.247969036649737</v>
+      </c>
+      <c r="U20">
+        <v>0.2388</v>
+      </c>
+      <c r="V20">
+        <v>-0.6035166211045608</v>
+      </c>
+      <c r="W20">
+        <v>0.3829197691197692</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-2.414066484418243</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.2267871132495904</v>
+      </c>
+      <c r="C21">
+        <v>31.20065388796728</v>
+      </c>
+      <c r="D21">
+        <v>45.83065388796729</v>
+      </c>
+      <c r="E21">
+        <v>14.63</v>
+      </c>
+      <c r="F21">
+        <v>14.63</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>77</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>7.99</v>
+      </c>
+      <c r="L21">
+        <v>-7.99</v>
+      </c>
+      <c r="M21">
+        <v>3.493644</v>
+      </c>
+      <c r="N21">
+        <v>-11.483644</v>
+      </c>
+      <c r="O21">
+        <v>-2.870911</v>
+      </c>
+      <c r="P21">
+        <v>-8.612733</v>
+      </c>
+      <c r="Q21">
+        <v>-0.6227330000000002</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1919426602568295</v>
+      </c>
+      <c r="T21">
+        <v>1.263376061793561</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>-0.5717525884148471</v>
+      </c>
+      <c r="W21">
+        <v>0.3753345181134655</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-2.287010353659388</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.2287871132495903</v>
+      </c>
+      <c r="C22">
+        <v>29.94819322940927</v>
+      </c>
+      <c r="D22">
+        <v>45.34819322940927</v>
+      </c>
+      <c r="E22">
+        <v>15.4</v>
+      </c>
+      <c r="F22">
+        <v>15.4</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>77</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>7.99</v>
+      </c>
+      <c r="L22">
+        <v>-7.99</v>
+      </c>
+      <c r="M22">
+        <v>3.67752</v>
+      </c>
+      <c r="N22">
+        <v>-11.66752</v>
+      </c>
+      <c r="O22">
+        <v>-2.91688</v>
+      </c>
+      <c r="P22">
+        <v>-8.750640000000001</v>
+      </c>
+      <c r="Q22">
+        <v>-0.7606400000000004</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1938569435100399</v>
+      </c>
+      <c r="T22">
+        <v>1.279168262565981</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>-0.5431649589941047</v>
+      </c>
+      <c r="W22">
+        <v>0.3685077922077922</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-2.172659835976419</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.2307871132495903</v>
+      </c>
+      <c r="C23">
+        <v>28.70578450924215</v>
+      </c>
+      <c r="D23">
+        <v>44.87578450924214</v>
+      </c>
+      <c r="E23">
+        <v>16.17</v>
+      </c>
+      <c r="F23">
+        <v>16.17</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>77</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>7.99</v>
+      </c>
+      <c r="L23">
+        <v>-7.99</v>
+      </c>
+      <c r="M23">
+        <v>3.861396</v>
+      </c>
+      <c r="N23">
+        <v>-11.851396</v>
+      </c>
+      <c r="O23">
+        <v>-2.962849</v>
+      </c>
+      <c r="P23">
+        <v>-8.888546999999999</v>
+      </c>
+      <c r="Q23">
+        <v>-0.8985469999999989</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1958196896304201</v>
+      </c>
+      <c r="T23">
+        <v>1.2953602658896</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>-0.5172999609467664</v>
+      </c>
+      <c r="W23">
+        <v>0.3623312306740878</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-2.069199843787066</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.2327871132495903</v>
+      </c>
+      <c r="C24">
+        <v>27.47311682212106</v>
+      </c>
+      <c r="D24">
+        <v>44.41311682212106</v>
+      </c>
+      <c r="E24">
+        <v>16.94</v>
+      </c>
+      <c r="F24">
+        <v>16.94</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>77</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>7.99</v>
+      </c>
+      <c r="L24">
+        <v>-7.99</v>
+      </c>
+      <c r="M24">
+        <v>4.045272000000001</v>
+      </c>
+      <c r="N24">
+        <v>-12.035272</v>
+      </c>
+      <c r="O24">
+        <v>-3.008818</v>
+      </c>
+      <c r="P24">
+        <v>-9.026454000000001</v>
+      </c>
+      <c r="Q24">
+        <v>-1.036454000000001</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1978327625743999</v>
+      </c>
+      <c r="T24">
+        <v>1.311967448785621</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>-0.493786326358277</v>
+      </c>
+      <c r="W24">
+        <v>0.3567161747343565</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-1.975145305433108</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.2347871132495903</v>
+      </c>
+      <c r="C25">
+        <v>26.24989195354961</v>
+      </c>
+      <c r="D25">
+        <v>43.95989195354962</v>
+      </c>
+      <c r="E25">
+        <v>17.71</v>
+      </c>
+      <c r="F25">
+        <v>17.71</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>77</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>7.99</v>
+      </c>
+      <c r="L25">
+        <v>-7.99</v>
+      </c>
+      <c r="M25">
+        <v>4.229148</v>
+      </c>
+      <c r="N25">
+        <v>-12.219148</v>
+      </c>
+      <c r="O25">
+        <v>-3.054787</v>
+      </c>
+      <c r="P25">
+        <v>-9.164361</v>
+      </c>
+      <c r="Q25">
+        <v>-1.174360999999999</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1998981231273141</v>
+      </c>
+      <c r="T25">
+        <v>1.329005987081538</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>-0.4723173556470476</v>
+      </c>
+      <c r="W25">
+        <v>0.351589384528515</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-1.88926942258819</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.2367871132495903</v>
+      </c>
+      <c r="C26">
+        <v>25.03582373888625</v>
+      </c>
+      <c r="D26">
+        <v>43.51582373888625</v>
+      </c>
+      <c r="E26">
+        <v>18.48</v>
+      </c>
+      <c r="F26">
+        <v>18.48</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>77</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>7.99</v>
+      </c>
+      <c r="L26">
+        <v>-7.99</v>
+      </c>
+      <c r="M26">
+        <v>4.413024</v>
+      </c>
+      <c r="N26">
+        <v>-12.403024</v>
+      </c>
+      <c r="O26">
+        <v>-3.100756</v>
+      </c>
+      <c r="P26">
+        <v>-9.302268</v>
+      </c>
+      <c r="Q26">
+        <v>-1.312268</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.2020178352737262</v>
+      </c>
+      <c r="T26">
+        <v>1.34649290796419</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>-0.4526374658284206</v>
+      </c>
+      <c r="W26">
+        <v>0.3468898268398269</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-1.810549863313682</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.2387871132495903</v>
+      </c>
+      <c r="C27">
+        <v>23.83063746081266</v>
+      </c>
+      <c r="D27">
+        <v>43.08063746081266</v>
+      </c>
+      <c r="E27">
+        <v>19.25</v>
+      </c>
+      <c r="F27">
+        <v>19.25</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>77</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>7.99</v>
+      </c>
+      <c r="L27">
+        <v>-7.99</v>
+      </c>
+      <c r="M27">
+        <v>4.596900000000001</v>
+      </c>
+      <c r="N27">
+        <v>-12.5869</v>
+      </c>
+      <c r="O27">
+        <v>-3.146725</v>
+      </c>
+      <c r="P27">
+        <v>-9.440175</v>
+      </c>
+      <c r="Q27">
+        <v>-1.450175</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2041940730773759</v>
+      </c>
+      <c r="T27">
+        <v>1.364446146737046</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>-0.4345319671952838</v>
+      </c>
+      <c r="W27">
+        <v>0.3425662337662337</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-1.738127868781135</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.2407871132495903</v>
+      </c>
+      <c r="C28">
+        <v>22.63406928259844</v>
+      </c>
+      <c r="D28">
+        <v>42.65406928259844</v>
+      </c>
+      <c r="E28">
+        <v>20.02</v>
+      </c>
+      <c r="F28">
+        <v>20.02</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>77</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>7.99</v>
+      </c>
+      <c r="L28">
+        <v>-7.99</v>
+      </c>
+      <c r="M28">
+        <v>4.780776</v>
+      </c>
+      <c r="N28">
+        <v>-12.770776</v>
+      </c>
+      <c r="O28">
+        <v>-3.192694</v>
+      </c>
+      <c r="P28">
+        <v>-9.578082000000002</v>
+      </c>
+      <c r="Q28">
+        <v>-1.588082000000002</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.206429128118962</v>
+      </c>
+      <c r="T28">
+        <v>1.382884608179438</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>-0.4178191992262344</v>
+      </c>
+      <c r="W28">
+        <v>0.3385752247752248</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-1.671276796904938</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.2427871132495903</v>
+      </c>
+      <c r="C29">
+        <v>21.44586571470532</v>
+      </c>
+      <c r="D29">
+        <v>42.23586571470532</v>
+      </c>
+      <c r="E29">
+        <v>20.79</v>
+      </c>
+      <c r="F29">
+        <v>20.79</v>
+      </c>
+      <c r="G29">
+        <v>0</v>
+      </c>
+      <c r="H29">
+        <v>77</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>7.99</v>
+      </c>
+      <c r="L29">
+        <v>-7.99</v>
+      </c>
+      <c r="M29">
+        <v>4.964652000000001</v>
+      </c>
+      <c r="N29">
+        <v>-12.954652</v>
+      </c>
+      <c r="O29">
+        <v>-3.238663</v>
+      </c>
+      <c r="P29">
+        <v>-9.715989</v>
+      </c>
+      <c r="Q29">
+        <v>-1.725989</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2087254175452491</v>
+      </c>
+      <c r="T29">
+        <v>1.40182823294902</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>-0.4023444140697071</v>
+      </c>
+      <c r="W29">
+        <v>0.3348798460798461</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-1.609377656278828</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.2447871132495903</v>
+      </c>
+      <c r="C30">
+        <v>20.26578311246477</v>
+      </c>
+      <c r="D30">
+        <v>41.82578311246477</v>
+      </c>
+      <c r="E30">
+        <v>21.56</v>
+      </c>
+      <c r="F30">
+        <v>21.56</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+      <c r="H30">
+        <v>77</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>7.99</v>
+      </c>
+      <c r="L30">
+        <v>-7.99</v>
+      </c>
+      <c r="M30">
+        <v>5.148528000000001</v>
+      </c>
+      <c r="N30">
+        <v>-13.138528</v>
+      </c>
+      <c r="O30">
+        <v>-3.284632</v>
+      </c>
+      <c r="P30">
+        <v>-9.853896000000001</v>
+      </c>
+      <c r="Q30">
+        <v>-1.863896</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.2110854927889332</v>
+      </c>
+      <c r="T30">
+        <v>1.421298069517756</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>-0.3879749707100748</v>
+      </c>
+      <c r="W30">
+        <v>0.3314484230055659</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-1.551899882840299</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.2467871132495904</v>
+      </c>
+      <c r="C31">
+        <v>19.09358720273768</v>
+      </c>
+      <c r="D31">
+        <v>41.42358720273768</v>
+      </c>
+      <c r="E31">
+        <v>22.33</v>
+      </c>
+      <c r="F31">
+        <v>22.33</v>
+      </c>
+      <c r="G31">
+        <v>0</v>
+      </c>
+      <c r="H31">
+        <v>77</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>7.99</v>
+      </c>
+      <c r="L31">
+        <v>-7.99</v>
+      </c>
+      <c r="M31">
+        <v>5.332403999999999</v>
+      </c>
+      <c r="N31">
+        <v>-13.322404</v>
+      </c>
+      <c r="O31">
+        <v>-3.330601</v>
+      </c>
+      <c r="P31">
+        <v>-9.991802999999999</v>
+      </c>
+      <c r="Q31">
+        <v>-2.001802999999999</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2135120490253971</v>
+      </c>
+      <c r="T31">
+        <v>1.44131635218702</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>-0.3745965234442102</v>
+      </c>
+      <c r="W31">
+        <v>0.3282536497984774</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-1.498386093776841</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.2487871132495903</v>
+      </c>
+      <c r="C32">
+        <v>17.92905263762367</v>
+      </c>
+      <c r="D32">
+        <v>41.02905263762367</v>
+      </c>
+      <c r="E32">
+        <v>23.1</v>
+      </c>
+      <c r="F32">
+        <v>23.1</v>
+      </c>
+      <c r="G32">
+        <v>0</v>
+      </c>
+      <c r="H32">
+        <v>77</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>7.99</v>
+      </c>
+      <c r="L32">
+        <v>-7.99</v>
+      </c>
+      <c r="M32">
+        <v>5.51628</v>
+      </c>
+      <c r="N32">
+        <v>-13.50628</v>
+      </c>
+      <c r="O32">
+        <v>-3.37657</v>
+      </c>
+      <c r="P32">
+        <v>-10.12971</v>
+      </c>
+      <c r="Q32">
+        <v>-2.139709999999999</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.2160079354400456</v>
+      </c>
+      <c r="T32">
+        <v>1.461906585789692</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>-0.3621099726627365</v>
+      </c>
+      <c r="W32">
+        <v>0.3252718614718614</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-1.448439890650946</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.2507871132495904</v>
+      </c>
+      <c r="C33">
+        <v>16.77196257343361</v>
+      </c>
+      <c r="D33">
+        <v>40.64196257343361</v>
+      </c>
+      <c r="E33">
+        <v>23.87</v>
+      </c>
+      <c r="F33">
+        <v>23.87</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33">
+        <v>77</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>7.99</v>
+      </c>
+      <c r="L33">
+        <v>-7.99</v>
+      </c>
+      <c r="M33">
+        <v>5.700156000000001</v>
+      </c>
+      <c r="N33">
+        <v>-13.690156</v>
+      </c>
+      <c r="O33">
+        <v>-3.422539</v>
+      </c>
+      <c r="P33">
+        <v>-10.267617</v>
+      </c>
+      <c r="Q33">
+        <v>-2.277617000000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.218576166388452</v>
+      </c>
+      <c r="T33">
+        <v>1.483093637757658</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>-0.3504290058026482</v>
+      </c>
+      <c r="W33">
+        <v>0.3224824465856724</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-1.401716023210593</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.2527871132495903</v>
+      </c>
+      <c r="C34">
+        <v>15.62210827327275</v>
+      </c>
+      <c r="D34">
+        <v>40.26210827327275</v>
+      </c>
+      <c r="E34">
+        <v>24.64</v>
+      </c>
+      <c r="F34">
+        <v>24.64</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>77</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>7.99</v>
+      </c>
+      <c r="L34">
+        <v>-7.99</v>
+      </c>
+      <c r="M34">
+        <v>5.884032</v>
+      </c>
+      <c r="N34">
+        <v>-13.874032</v>
+      </c>
+      <c r="O34">
+        <v>-3.468508</v>
+      </c>
+      <c r="P34">
+        <v>-10.405524</v>
+      </c>
+      <c r="Q34">
+        <v>-2.415524</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2212199335412234</v>
+      </c>
+      <c r="T34">
+        <v>1.504903838312918</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>-0.3394780993713155</v>
+      </c>
+      <c r="W34">
+        <v>0.3198673701298701</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-1.357912397485262</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.2547871132495904</v>
+      </c>
+      <c r="C35">
+        <v>14.47928873170365</v>
+      </c>
+      <c r="D35">
+        <v>39.88928873170365</v>
+      </c>
+      <c r="E35">
+        <v>25.41</v>
+      </c>
+      <c r="F35">
+        <v>25.41</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35">
+        <v>77</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>7.99</v>
+      </c>
+      <c r="L35">
+        <v>-7.99</v>
+      </c>
+      <c r="M35">
+        <v>6.067908</v>
+      </c>
+      <c r="N35">
+        <v>-14.057908</v>
+      </c>
+      <c r="O35">
+        <v>-3.514477</v>
+      </c>
+      <c r="P35">
+        <v>-10.543431</v>
+      </c>
+      <c r="Q35">
+        <v>-2.553431000000002</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2239426191164655</v>
+      </c>
+      <c r="T35">
+        <v>1.527365089631022</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>-0.3291908842388513</v>
+      </c>
+      <c r="W35">
+        <v>0.3174107831562377</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-1.316763536955405</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.2567871132495903</v>
+      </c>
+      <c r="C36">
+        <v>13.34331032007129</v>
+      </c>
+      <c r="D36">
+        <v>39.5233103200713</v>
+      </c>
+      <c r="E36">
+        <v>26.18</v>
+      </c>
+      <c r="F36">
+        <v>26.18</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>77</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>7.99</v>
+      </c>
+      <c r="L36">
+        <v>-7.99</v>
+      </c>
+      <c r="M36">
+        <v>6.251784000000001</v>
+      </c>
+      <c r="N36">
+        <v>-14.241784</v>
+      </c>
+      <c r="O36">
+        <v>-3.560446</v>
+      </c>
+      <c r="P36">
+        <v>-10.681338</v>
+      </c>
+      <c r="Q36">
+        <v>-2.691338</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2267478103151999</v>
+      </c>
+      <c r="T36">
+        <v>1.550506984928461</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>-0.3195087994082969</v>
+      </c>
+      <c r="W36">
+        <v>0.3150987012987013</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-1.278035197633188</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.2587871132495904</v>
+      </c>
+      <c r="C37">
+        <v>12.21398645117512</v>
+      </c>
+      <c r="D37">
+        <v>39.16398645117512</v>
+      </c>
+      <c r="E37">
+        <v>26.95</v>
+      </c>
+      <c r="F37">
+        <v>26.95</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37">
+        <v>77</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>7.99</v>
+      </c>
+      <c r="L37">
+        <v>-7.99</v>
+      </c>
+      <c r="M37">
+        <v>6.435660000000001</v>
+      </c>
+      <c r="N37">
+        <v>-14.42566</v>
+      </c>
+      <c r="O37">
+        <v>-3.606415</v>
+      </c>
+      <c r="P37">
+        <v>-10.819245</v>
+      </c>
+      <c r="Q37">
+        <v>-2.829245</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2296393150892798</v>
+      </c>
+      <c r="T37">
+        <v>1.574360938542745</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>-0.3103799765680598</v>
+      </c>
+      <c r="W37">
+        <v>0.3129187384044527</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-1.241519906272239</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2607871132495903</v>
+      </c>
+      <c r="C38">
+        <v>11.091137262068</v>
+      </c>
+      <c r="D38">
+        <v>38.811137262068</v>
+      </c>
+      <c r="E38">
+        <v>27.72</v>
+      </c>
+      <c r="F38">
+        <v>27.72</v>
+      </c>
+      <c r="G38">
+        <v>0</v>
+      </c>
+      <c r="H38">
+        <v>77</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>7.99</v>
+      </c>
+      <c r="L38">
+        <v>-7.99</v>
+      </c>
+      <c r="M38">
+        <v>6.619536</v>
+      </c>
+      <c r="N38">
+        <v>-14.609536</v>
+      </c>
+      <c r="O38">
+        <v>-3.652384</v>
+      </c>
+      <c r="P38">
+        <v>-10.957152</v>
+      </c>
+      <c r="Q38">
+        <v>-2.967152</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2326211793875498</v>
+      </c>
+      <c r="T38">
+        <v>1.598960328207476</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>-0.3017583105522804</v>
+      </c>
+      <c r="W38">
+        <v>0.3108598845598846</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-1.207033242209122</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2627871132495903</v>
+      </c>
+      <c r="C39">
+        <v>9.974589313849027</v>
+      </c>
+      <c r="D39">
+        <v>38.46458931384903</v>
+      </c>
+      <c r="E39">
+        <v>28.49</v>
+      </c>
+      <c r="F39">
+        <v>28.49</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>77</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>7.99</v>
+      </c>
+      <c r="L39">
+        <v>-7.99</v>
+      </c>
+      <c r="M39">
+        <v>6.803412</v>
+      </c>
+      <c r="N39">
+        <v>-14.793412</v>
+      </c>
+      <c r="O39">
+        <v>-3.698353</v>
+      </c>
+      <c r="P39">
+        <v>-11.095059</v>
+      </c>
+      <c r="Q39">
+        <v>-3.105058999999999</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2356977060444951</v>
+      </c>
+      <c r="T39">
+        <v>1.624340650877435</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>-0.2936026805373539</v>
+      </c>
+      <c r="W39">
+        <v>0.3089123201123201</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-1.174410722149416</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2647871132495904</v>
+      </c>
+      <c r="C40">
+        <v>8.864175307397534</v>
+      </c>
+      <c r="D40">
+        <v>38.12417530739754</v>
+      </c>
+      <c r="E40">
+        <v>29.26</v>
+      </c>
+      <c r="F40">
+        <v>29.26</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
+      </c>
+      <c r="H40">
+        <v>77</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>7.99</v>
+      </c>
+      <c r="L40">
+        <v>-7.99</v>
+      </c>
+      <c r="M40">
+        <v>6.987288</v>
+      </c>
+      <c r="N40">
+        <v>-14.977288</v>
+      </c>
+      <c r="O40">
+        <v>-3.744322</v>
+      </c>
+      <c r="P40">
+        <v>-11.232966</v>
+      </c>
+      <c r="Q40">
+        <v>-3.242966000000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2388734754968256</v>
+      </c>
+      <c r="T40">
+        <v>1.650539693633523</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>-0.2858762942074236</v>
+      </c>
+      <c r="W40">
+        <v>0.3070672590567328</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-1.143505176829694</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2667871132495904</v>
+      </c>
+      <c r="C41">
+        <v>7.759733814069264</v>
+      </c>
+      <c r="D41">
+        <v>37.78973381406927</v>
+      </c>
+      <c r="E41">
+        <v>30.03</v>
+      </c>
+      <c r="F41">
+        <v>30.03</v>
+      </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
+      <c r="H41">
+        <v>77</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>7.99</v>
+      </c>
+      <c r="L41">
+        <v>-7.99</v>
+      </c>
+      <c r="M41">
+        <v>7.171164000000001</v>
+      </c>
+      <c r="N41">
+        <v>-15.161164</v>
+      </c>
+      <c r="O41">
+        <v>-3.790291</v>
+      </c>
+      <c r="P41">
+        <v>-11.370873</v>
+      </c>
+      <c r="Q41">
+        <v>-3.380873000000001</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.2421533685377572</v>
+      </c>
+      <c r="T41">
+        <v>1.677597721398007</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>-0.2785461328174896</v>
+      </c>
+      <c r="W41">
+        <v>0.3053168165168165</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-1.114184531269958</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.2687871132495903</v>
+      </c>
+      <c r="C42">
+        <v>6.661109020443906</v>
+      </c>
+      <c r="D42">
+        <v>37.46110902044391</v>
+      </c>
+      <c r="E42">
+        <v>30.8</v>
+      </c>
+      <c r="F42">
+        <v>30.8</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>77</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>7.99</v>
+      </c>
+      <c r="L42">
+        <v>-7.99</v>
+      </c>
+      <c r="M42">
+        <v>7.355040000000001</v>
+      </c>
+      <c r="N42">
+        <v>-15.34504</v>
+      </c>
+      <c r="O42">
+        <v>-3.83626</v>
+      </c>
+      <c r="P42">
+        <v>-11.50878</v>
+      </c>
+      <c r="Q42">
+        <v>-3.518780000000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2455425913467198</v>
+      </c>
+      <c r="T42">
+        <v>1.705557683421307</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>-0.2715824794970523</v>
+      </c>
+      <c r="W42">
+        <v>0.3036538961038961</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-1.08632991798821</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2707871132495904</v>
+      </c>
+      <c r="C43">
+        <v>5.568150486276185</v>
+      </c>
+      <c r="D43">
+        <v>37.13815048627619</v>
+      </c>
+      <c r="E43">
+        <v>31.57</v>
+      </c>
+      <c r="F43">
+        <v>31.57</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>77</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>7.99</v>
+      </c>
+      <c r="L43">
+        <v>-7.99</v>
+      </c>
+      <c r="M43">
+        <v>7.538916000000001</v>
+      </c>
+      <c r="N43">
+        <v>-15.528916</v>
+      </c>
+      <c r="O43">
+        <v>-3.882229000000001</v>
+      </c>
+      <c r="P43">
+        <v>-11.646687</v>
+      </c>
+      <c r="Q43">
+        <v>-3.656687000000002</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2490467030644609</v>
+      </c>
+      <c r="T43">
+        <v>1.734465440767431</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>-0.2649585165824901</v>
+      </c>
+      <c r="W43">
+        <v>0.3020720937598987</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-1.059834066329961</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2727871132495904</v>
+      </c>
+      <c r="C44">
+        <v>4.480712914860355</v>
+      </c>
+      <c r="D44">
+        <v>36.82071291486035</v>
+      </c>
+      <c r="E44">
+        <v>32.34</v>
+      </c>
+      <c r="F44">
+        <v>32.34</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>77</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>7.99</v>
+      </c>
+      <c r="L44">
+        <v>-7.99</v>
+      </c>
+      <c r="M44">
+        <v>7.722791999999999</v>
+      </c>
+      <c r="N44">
+        <v>-15.712792</v>
+      </c>
+      <c r="O44">
+        <v>-3.928198</v>
+      </c>
+      <c r="P44">
+        <v>-11.784594</v>
+      </c>
+      <c r="Q44">
+        <v>-3.794594</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2526716462207446</v>
+      </c>
+      <c r="T44">
+        <v>1.764370017332387</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>-0.2586499804733832</v>
+      </c>
+      <c r="W44">
+        <v>0.300565615337044</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-1.034599921893533</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2747871132495904</v>
+      </c>
+      <c r="C45">
+        <v>3.398655935071652</v>
+      </c>
+      <c r="D45">
+        <v>36.50865593507165</v>
+      </c>
+      <c r="E45">
+        <v>33.11</v>
+      </c>
+      <c r="F45">
+        <v>33.11</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>77</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>7.99</v>
+      </c>
+      <c r="L45">
+        <v>-7.99</v>
+      </c>
+      <c r="M45">
+        <v>7.906668000000001</v>
+      </c>
+      <c r="N45">
+        <v>-15.896668</v>
+      </c>
+      <c r="O45">
+        <v>-3.974167</v>
+      </c>
+      <c r="P45">
+        <v>-11.922501</v>
+      </c>
+      <c r="Q45">
+        <v>-3.932501</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2564237803649682</v>
+      </c>
+      <c r="T45">
+        <v>1.795323877285587</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>-0.2526348646484208</v>
+      </c>
+      <c r="W45">
+        <v>0.2991292056780429</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-1.010539458593683</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2767871132495904</v>
+      </c>
+      <c r="C46">
+        <v>2.321843894397979</v>
+      </c>
+      <c r="D46">
+        <v>36.20184389439798</v>
+      </c>
+      <c r="E46">
+        <v>33.88</v>
+      </c>
+      <c r="F46">
+        <v>33.88</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>77</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>7.99</v>
+      </c>
+      <c r="L46">
+        <v>-7.99</v>
+      </c>
+      <c r="M46">
+        <v>8.090544000000001</v>
+      </c>
+      <c r="N46">
+        <v>-16.080544</v>
+      </c>
+      <c r="O46">
+        <v>-4.020136000000001</v>
+      </c>
+      <c r="P46">
+        <v>-12.060408</v>
+      </c>
+      <c r="Q46">
+        <v>-4.070408000000002</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2603099193000569</v>
+      </c>
+      <c r="T46">
+        <v>1.827383232237115</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>-0.2468931631791385</v>
+      </c>
+      <c r="W46">
+        <v>0.2977580873671783</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.987572652716554</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2787871132495903</v>
+      </c>
+      <c r="C47">
+        <v>1.250145662320435</v>
+      </c>
+      <c r="D47">
+        <v>35.90014566232043</v>
+      </c>
+      <c r="E47">
+        <v>34.65</v>
+      </c>
+      <c r="F47">
+        <v>34.65</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>77</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>7.99</v>
+      </c>
+      <c r="L47">
+        <v>-7.99</v>
+      </c>
+      <c r="M47">
+        <v>8.274419999999999</v>
+      </c>
+      <c r="N47">
+        <v>-16.26442</v>
+      </c>
+      <c r="O47">
+        <v>-4.066105</v>
+      </c>
+      <c r="P47">
+        <v>-12.198315</v>
+      </c>
+      <c r="Q47">
+        <v>-4.208315000000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2643373723782398</v>
+      </c>
+      <c r="T47">
+        <v>1.860608381914153</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>-0.2414066484418244</v>
+      </c>
+      <c r="W47">
+        <v>0.2964479076479076</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.9656265937672976</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2807871132495904</v>
+      </c>
+      <c r="C48">
+        <v>0.1834344434441348</v>
+      </c>
+      <c r="D48">
+        <v>35.60343444344414</v>
+      </c>
+      <c r="E48">
+        <v>35.42</v>
+      </c>
+      <c r="F48">
+        <v>35.42</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>77</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>7.99</v>
+      </c>
+      <c r="L48">
+        <v>-7.99</v>
+      </c>
+      <c r="M48">
+        <v>8.458296000000001</v>
+      </c>
+      <c r="N48">
+        <v>-16.448296</v>
+      </c>
+      <c r="O48">
+        <v>-4.112074</v>
+      </c>
+      <c r="P48">
+        <v>-12.336222</v>
+      </c>
+      <c r="Q48">
+        <v>-4.346221999999999</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2685139903852443</v>
+      </c>
+      <c r="T48">
+        <v>1.895064092690341</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>-0.2361586778235238</v>
+      </c>
+      <c r="W48">
+        <v>0.2951946922642575</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.9446347112940949</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2827871132495904</v>
+      </c>
+      <c r="C49">
+        <v>-0.8784124001801317</v>
+      </c>
+      <c r="D49">
+        <v>35.31158759981987</v>
+      </c>
+      <c r="E49">
+        <v>36.19</v>
+      </c>
+      <c r="F49">
+        <v>36.19</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>77</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>7.99</v>
+      </c>
+      <c r="L49">
+        <v>-7.99</v>
+      </c>
+      <c r="M49">
+        <v>8.642172000000002</v>
+      </c>
+      <c r="N49">
+        <v>-16.632172</v>
+      </c>
+      <c r="O49">
+        <v>-4.158043000000001</v>
+      </c>
+      <c r="P49">
+        <v>-12.474129</v>
+      </c>
+      <c r="Q49">
+        <v>-4.484129000000003</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2728482166189281</v>
+      </c>
+      <c r="T49">
+        <v>1.930820018967518</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>-0.2311340251038743</v>
+      </c>
+      <c r="W49">
+        <v>0.2939948051948052</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.9245361004154975</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2847871132495903</v>
+      </c>
+      <c r="C50">
+        <v>-1.935513518066649</v>
+      </c>
+      <c r="D50">
+        <v>35.02448648193335</v>
+      </c>
+      <c r="E50">
+        <v>36.96</v>
+      </c>
+      <c r="F50">
+        <v>36.96</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>77</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>7.99</v>
+      </c>
+      <c r="L50">
+        <v>-7.99</v>
+      </c>
+      <c r="M50">
+        <v>8.826048</v>
+      </c>
+      <c r="N50">
+        <v>-16.816048</v>
+      </c>
+      <c r="O50">
+        <v>-4.204012000000001</v>
+      </c>
+      <c r="P50">
+        <v>-12.612036</v>
+      </c>
+      <c r="Q50">
+        <v>-4.622036000000001</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2773491438615998</v>
+      </c>
+      <c r="T50">
+        <v>1.967951173178431</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>-0.2263187329142103</v>
+      </c>
+      <c r="W50">
+        <v>0.2928449134199134</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.9052749316568414</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2867871132495903</v>
+      </c>
+      <c r="C51">
+        <v>-2.987983732127184</v>
+      </c>
+      <c r="D51">
+        <v>34.74201626787281</v>
+      </c>
+      <c r="E51">
+        <v>37.73</v>
+      </c>
+      <c r="F51">
+        <v>37.73</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>77</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>7.99</v>
+      </c>
+      <c r="L51">
+        <v>-7.99</v>
+      </c>
+      <c r="M51">
+        <v>9.009924</v>
+      </c>
+      <c r="N51">
+        <v>-16.999924</v>
+      </c>
+      <c r="O51">
+        <v>-4.249981</v>
+      </c>
+      <c r="P51">
+        <v>-12.749943</v>
+      </c>
+      <c r="Q51">
+        <v>-4.759943</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2820265780549645</v>
+      </c>
+      <c r="T51">
+        <v>2.006538451083891</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>-0.2216999832628999</v>
+      </c>
+      <c r="W51">
+        <v>0.2917419560031805</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.8867999330515997</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2887871132495903</v>
+      </c>
+      <c r="C52">
+        <v>-4.035934189782871</v>
+      </c>
+      <c r="D52">
+        <v>34.46406581021713</v>
+      </c>
+      <c r="E52">
+        <v>38.5</v>
+      </c>
+      <c r="F52">
+        <v>38.5</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>77</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>7.99</v>
+      </c>
+      <c r="L52">
+        <v>-7.99</v>
+      </c>
+      <c r="M52">
+        <v>9.193800000000001</v>
+      </c>
+      <c r="N52">
+        <v>-17.1838</v>
+      </c>
+      <c r="O52">
+        <v>-4.29595</v>
+      </c>
+      <c r="P52">
+        <v>-12.88785</v>
+      </c>
+      <c r="Q52">
+        <v>-4.89785</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2868911096160638</v>
+      </c>
+      <c r="T52">
+        <v>2.046669220105569</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>-0.2172659835976419</v>
+      </c>
+      <c r="W52">
+        <v>0.2906831168831169</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.8690639343905675</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2907871132495904</v>
+      </c>
+      <c r="C53">
+        <v>-5.079472509784829</v>
+      </c>
+      <c r="D53">
+        <v>34.19052749021517</v>
+      </c>
+      <c r="E53">
+        <v>39.27</v>
+      </c>
+      <c r="F53">
+        <v>39.27</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>77</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>7.99</v>
+      </c>
+      <c r="L53">
+        <v>-7.99</v>
+      </c>
+      <c r="M53">
+        <v>9.377676000000001</v>
+      </c>
+      <c r="N53">
+        <v>-17.367676</v>
+      </c>
+      <c r="O53">
+        <v>-4.341919000000001</v>
+      </c>
+      <c r="P53">
+        <v>-13.025757</v>
+      </c>
+      <c r="Q53">
+        <v>-5.035757000000002</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2919541934857794</v>
+      </c>
+      <c r="T53">
+        <v>2.08843797969956</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>-0.2130058662721979</v>
+      </c>
+      <c r="W53">
+        <v>0.2896658008658008</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.8520234650887919</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2927871132495903</v>
+      </c>
+      <c r="C54">
+        <v>-6.118702921145228</v>
+      </c>
+      <c r="D54">
+        <v>33.92129707885477</v>
+      </c>
+      <c r="E54">
+        <v>40.04</v>
+      </c>
+      <c r="F54">
+        <v>40.04</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>77</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>7.99</v>
+      </c>
+      <c r="L54">
+        <v>-7.99</v>
+      </c>
+      <c r="M54">
+        <v>9.561552000000001</v>
+      </c>
+      <c r="N54">
+        <v>-17.551552</v>
+      </c>
+      <c r="O54">
+        <v>-4.387888</v>
+      </c>
+      <c r="P54">
+        <v>-13.163664</v>
+      </c>
+      <c r="Q54">
+        <v>-5.173664</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2972282391833998</v>
+      </c>
+      <c r="T54">
+        <v>2.131947104276634</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>-0.2089095996131172</v>
+      </c>
+      <c r="W54">
+        <v>0.2886876123876124</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.8356383984524687</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2947871132495904</v>
+      </c>
+      <c r="C55">
+        <v>-7.153726395555701</v>
+      </c>
+      <c r="D55">
+        <v>33.6562736044443</v>
+      </c>
+      <c r="E55">
+        <v>40.81</v>
+      </c>
+      <c r="F55">
+        <v>40.81</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>77</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>7.99</v>
+      </c>
+      <c r="L55">
+        <v>-7.99</v>
+      </c>
+      <c r="M55">
+        <v>9.745428</v>
+      </c>
+      <c r="N55">
+        <v>-17.735428</v>
+      </c>
+      <c r="O55">
+        <v>-4.433857</v>
+      </c>
+      <c r="P55">
+        <v>-13.301571</v>
+      </c>
+      <c r="Q55">
+        <v>-5.311570999999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3027267123575147</v>
+      </c>
+      <c r="T55">
+        <v>2.177307680963371</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>-0.2049679090543791</v>
+      </c>
+      <c r="W55">
+        <v>0.2877463366821858</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.8198716362175165</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2967871132495904</v>
+      </c>
+      <c r="C56">
+        <v>-8.184640773646237</v>
+      </c>
+      <c r="D56">
+        <v>33.39535922635377</v>
+      </c>
+      <c r="E56">
+        <v>41.58000000000001</v>
+      </c>
+      <c r="F56">
+        <v>41.58000000000001</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>77</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>7.99</v>
+      </c>
+      <c r="L56">
+        <v>-7.99</v>
+      </c>
+      <c r="M56">
+        <v>9.929304000000002</v>
+      </c>
+      <c r="N56">
+        <v>-17.919304</v>
+      </c>
+      <c r="O56">
+        <v>-4.479826000000001</v>
+      </c>
+      <c r="P56">
+        <v>-13.439478</v>
+      </c>
+      <c r="Q56">
+        <v>-5.449478000000003</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.308464249582678</v>
+      </c>
+      <c r="T56">
+        <v>2.224640456636488</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>-0.2011722070348536</v>
+      </c>
+      <c r="W56">
+        <v>0.2868399230399231</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.8046888281394144</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2987871132495904</v>
+      </c>
+      <c r="C57">
+        <v>-9.211540885416724</v>
+      </c>
+      <c r="D57">
+        <v>33.13845911458328</v>
+      </c>
+      <c r="E57">
+        <v>42.35</v>
+      </c>
+      <c r="F57">
+        <v>42.35</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>77</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>7.99</v>
+      </c>
+      <c r="L57">
+        <v>-7.99</v>
+      </c>
+      <c r="M57">
+        <v>10.11318</v>
+      </c>
+      <c r="N57">
+        <v>-18.10318</v>
+      </c>
+      <c r="O57">
+        <v>-4.525795</v>
+      </c>
+      <c r="P57">
+        <v>-13.577385</v>
+      </c>
+      <c r="Q57">
+        <v>-5.587385000000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3144567884622932</v>
+      </c>
+      <c r="T57">
+        <v>2.27407691122841</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>-0.1975145305433108</v>
+      </c>
+      <c r="W57">
+        <v>0.2859664698937426</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.7900581221732432</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.3007871132495903</v>
+      </c>
+      <c r="C58">
+        <v>-10.23451866515212</v>
+      </c>
+      <c r="D58">
+        <v>32.88548133484789</v>
+      </c>
+      <c r="E58">
+        <v>43.12</v>
+      </c>
+      <c r="F58">
+        <v>43.12</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>77</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>7.99</v>
+      </c>
+      <c r="L58">
+        <v>-7.99</v>
+      </c>
+      <c r="M58">
+        <v>10.297056</v>
+      </c>
+      <c r="N58">
+        <v>-18.287056</v>
+      </c>
+      <c r="O58">
+        <v>-4.571764</v>
+      </c>
+      <c r="P58">
+        <v>-13.715292</v>
+      </c>
+      <c r="Q58">
+        <v>-5.725292</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3207217154727998</v>
+      </c>
+      <c r="T58">
+        <v>2.325760477392692</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>-0.1939874853550374</v>
+      </c>
+      <c r="W58">
+        <v>0.2851242115027829</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.7759499414201494</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.3027871132495904</v>
+      </c>
+      <c r="C59">
+        <v>-11.25366326111394</v>
+      </c>
+      <c r="D59">
+        <v>32.63633673888607</v>
+      </c>
+      <c r="E59">
+        <v>43.89000000000001</v>
+      </c>
+      <c r="F59">
+        <v>43.89000000000001</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>77</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>7.99</v>
+      </c>
+      <c r="L59">
+        <v>-7.99</v>
+      </c>
+      <c r="M59">
+        <v>10.480932</v>
+      </c>
+      <c r="N59">
+        <v>-18.470932</v>
+      </c>
+      <c r="O59">
+        <v>-4.617733000000001</v>
+      </c>
+      <c r="P59">
+        <v>-13.853199</v>
+      </c>
+      <c r="Q59">
+        <v>-5.863199000000003</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3272780344372835</v>
+      </c>
+      <c r="T59">
+        <v>2.379847930355313</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>-0.1905841961382823</v>
+      </c>
+      <c r="W59">
+        <v>0.2843115060378218</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.7623367845531295</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.3047871132495903</v>
+      </c>
+      <c r="C60">
+        <v>-12.26906114028307</v>
+      </c>
+      <c r="D60">
+        <v>32.39093885971693</v>
+      </c>
+      <c r="E60">
+        <v>44.66</v>
+      </c>
+      <c r="F60">
+        <v>44.66</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>77</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>7.99</v>
+      </c>
+      <c r="L60">
+        <v>-7.99</v>
+      </c>
+      <c r="M60">
+        <v>10.664808</v>
+      </c>
+      <c r="N60">
+        <v>-18.654808</v>
+      </c>
+      <c r="O60">
+        <v>-4.663702</v>
+      </c>
+      <c r="P60">
+        <v>-13.991106</v>
+      </c>
+      <c r="Q60">
+        <v>-6.001105999999998</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3341465590667426</v>
+      </c>
+      <c r="T60">
+        <v>2.436510976316153</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>-0.1872982617221051</v>
+      </c>
+      <c r="W60">
+        <v>0.2835268248992387</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.7491930468884205</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.3067871132495903</v>
+      </c>
+      <c r="C61">
+        <v>-13.28079618841241</v>
+      </c>
+      <c r="D61">
+        <v>32.14920381158759</v>
+      </c>
+      <c r="E61">
+        <v>45.43</v>
+      </c>
+      <c r="F61">
+        <v>45.43</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>77</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>7.99</v>
+      </c>
+      <c r="L61">
+        <v>-7.99</v>
+      </c>
+      <c r="M61">
+        <v>10.848684</v>
+      </c>
+      <c r="N61">
+        <v>-18.838684</v>
+      </c>
+      <c r="O61">
+        <v>-4.709671</v>
+      </c>
+      <c r="P61">
+        <v>-14.129013</v>
+      </c>
+      <c r="Q61">
+        <v>-6.139013</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3413501336781265</v>
+      </c>
+      <c r="T61">
+        <v>2.495938073299474</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>-0.1841237149132558</v>
+      </c>
+      <c r="W61">
+        <v>0.2827687431212855</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.7364948596530234</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.3087871132495904</v>
+      </c>
+      <c r="C62">
+        <v>-14.28894980563241</v>
+      </c>
+      <c r="D62">
+        <v>31.91105019436759</v>
+      </c>
+      <c r="E62">
+        <v>46.2</v>
+      </c>
+      <c r="F62">
+        <v>46.2</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>77</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>7.99</v>
+      </c>
+      <c r="L62">
+        <v>-7.99</v>
+      </c>
+      <c r="M62">
+        <v>11.03256</v>
+      </c>
+      <c r="N62">
+        <v>-19.02256</v>
+      </c>
+      <c r="O62">
+        <v>-4.75564</v>
+      </c>
+      <c r="P62">
+        <v>-14.26692</v>
+      </c>
+      <c r="Q62">
+        <v>-6.276919999999999</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3489138870200797</v>
+      </c>
+      <c r="T62">
+        <v>2.558336525131961</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>-0.1810549863313682</v>
+      </c>
+      <c r="W62">
+        <v>0.2820359307359308</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.7242199453254727</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.3107871132495904</v>
+      </c>
+      <c r="C63">
+        <v>-15.2936009978386</v>
+      </c>
+      <c r="D63">
+        <v>31.6763990021614</v>
+      </c>
+      <c r="E63">
+        <v>46.97</v>
+      </c>
+      <c r="F63">
+        <v>46.97</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>77</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>7.99</v>
+      </c>
+      <c r="L63">
+        <v>-7.99</v>
+      </c>
+      <c r="M63">
+        <v>11.216436</v>
+      </c>
+      <c r="N63">
+        <v>-19.206436</v>
+      </c>
+      <c r="O63">
+        <v>-4.801609</v>
+      </c>
+      <c r="P63">
+        <v>-14.404827</v>
+      </c>
+      <c r="Q63">
+        <v>-6.414827000000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3568655251487997</v>
+      </c>
+      <c r="T63">
+        <v>2.623934897571242</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>-0.1780868718013458</v>
+      </c>
+      <c r="W63">
+        <v>0.2813271449861614</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.7123474872053832</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.3127871132495904</v>
+      </c>
+      <c r="C64">
+        <v>-16.29482646407654</v>
+      </c>
+      <c r="D64">
+        <v>31.44517353592347</v>
+      </c>
+      <c r="E64">
+        <v>47.74</v>
+      </c>
+      <c r="F64">
+        <v>47.74</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>77</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>7.99</v>
+      </c>
+      <c r="L64">
+        <v>-7.99</v>
+      </c>
+      <c r="M64">
+        <v>11.400312</v>
+      </c>
+      <c r="N64">
+        <v>-19.390312</v>
+      </c>
+      <c r="O64">
+        <v>-4.847578</v>
+      </c>
+      <c r="P64">
+        <v>-14.542734</v>
+      </c>
+      <c r="Q64">
+        <v>-6.552734000000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3652356705474524</v>
+      </c>
+      <c r="T64">
+        <v>2.69298581592838</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>-0.1752145029013241</v>
+      </c>
+      <c r="W64">
+        <v>0.2806412232928362</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.7008580116052963</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.3147871132495904</v>
+      </c>
+      <c r="C65">
+        <v>-17.29270068012724</v>
+      </c>
+      <c r="D65">
+        <v>31.21729931987276</v>
+      </c>
+      <c r="E65">
+        <v>48.51</v>
+      </c>
+      <c r="F65">
+        <v>48.51</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>77</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>7.99</v>
+      </c>
+      <c r="L65">
+        <v>-7.99</v>
+      </c>
+      <c r="M65">
+        <v>11.584188</v>
+      </c>
+      <c r="N65">
+        <v>-19.574188</v>
+      </c>
+      <c r="O65">
+        <v>-4.893547</v>
+      </c>
+      <c r="P65">
+        <v>-14.680641</v>
+      </c>
+      <c r="Q65">
+        <v>-6.690640999999999</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.374058256237924</v>
+      </c>
+      <c r="T65">
+        <v>2.765769216358877</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>-0.1724333203155888</v>
+      </c>
+      <c r="W65">
+        <v>0.2799770768913626</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.6897332812623553</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.3167871132495903</v>
+      </c>
+      <c r="C66">
+        <v>-18.28729597848442</v>
+      </c>
+      <c r="D66">
+        <v>30.99270402151558</v>
+      </c>
+      <c r="E66">
+        <v>49.28</v>
+      </c>
+      <c r="F66">
+        <v>49.28</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>77</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>7.99</v>
+      </c>
+      <c r="L66">
+        <v>-7.99</v>
+      </c>
+      <c r="M66">
+        <v>11.768064</v>
+      </c>
+      <c r="N66">
+        <v>-19.758064</v>
+      </c>
+      <c r="O66">
+        <v>-4.939516</v>
+      </c>
+      <c r="P66">
+        <v>-14.818548</v>
+      </c>
+      <c r="Q66">
+        <v>-6.828548</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3833709855778664</v>
+      </c>
+      <c r="T66">
+        <v>2.842596139035512</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>-0.1697390496856577</v>
+      </c>
+      <c r="W66">
+        <v>0.2793336850649351</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.6789561987426309</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.3187871132495903</v>
+      </c>
+      <c r="C67">
+        <v>-19.27868262490403</v>
+      </c>
+      <c r="D67">
+        <v>30.77131737509598</v>
+      </c>
+      <c r="E67">
+        <v>50.05</v>
+      </c>
+      <c r="F67">
+        <v>50.05</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>77</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>7.99</v>
+      </c>
+      <c r="L67">
+        <v>-7.99</v>
+      </c>
+      <c r="M67">
+        <v>11.95194</v>
+      </c>
+      <c r="N67">
+        <v>-19.94194</v>
+      </c>
+      <c r="O67">
+        <v>-4.985485000000001</v>
+      </c>
+      <c r="P67">
+        <v>-14.956455</v>
+      </c>
+      <c r="Q67">
+        <v>-6.966455000000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3932158708800911</v>
+      </c>
+      <c r="T67">
+        <v>2.923813171579384</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>-0.1671276796904937</v>
+      </c>
+      <c r="W67">
+        <v>0.2787100899100899</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.668510718761975</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.3207871132495904</v>
+      </c>
+      <c r="C68">
+        <v>-20.26692889169608</v>
+      </c>
+      <c r="D68">
+        <v>30.55307110830392</v>
+      </c>
+      <c r="E68">
+        <v>50.82</v>
+      </c>
+      <c r="F68">
+        <v>50.82</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>77</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>7.99</v>
+      </c>
+      <c r="L68">
+        <v>-7.99</v>
+      </c>
+      <c r="M68">
+        <v>12.135816</v>
+      </c>
+      <c r="N68">
+        <v>-20.125816</v>
+      </c>
+      <c r="O68">
+        <v>-5.031454</v>
+      </c>
+      <c r="P68">
+        <v>-15.094362</v>
+      </c>
+      <c r="Q68">
+        <v>-7.104362</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4036398670824468</v>
+      </c>
+      <c r="T68">
+        <v>3.009807676625837</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>-0.1645954421194257</v>
+      </c>
+      <c r="W68">
+        <v>0.2781053915781189</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.6583817684777027</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.3227871132495904</v>
+      </c>
+      <c r="C69">
+        <v>-21.25210112791972</v>
+      </c>
+      <c r="D69">
+        <v>30.33789887208028</v>
+      </c>
+      <c r="E69">
+        <v>51.59</v>
+      </c>
+      <c r="F69">
+        <v>51.59</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>77</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>7.99</v>
+      </c>
+      <c r="L69">
+        <v>-7.99</v>
+      </c>
+      <c r="M69">
+        <v>12.319692</v>
+      </c>
+      <c r="N69">
+        <v>-20.309692</v>
+      </c>
+      <c r="O69">
+        <v>-5.077423</v>
+      </c>
+      <c r="P69">
+        <v>-15.232269</v>
+      </c>
+      <c r="Q69">
+        <v>-7.242269000000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.4146956206303998</v>
+      </c>
+      <c r="T69">
+        <v>3.101013969856923</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>-0.1621387937295835</v>
+      </c>
+      <c r="W69">
+        <v>0.2775187439426245</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.648555174918334</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.3247871132495903</v>
+      </c>
+      <c r="C70">
+        <v>-22.23426382663267</v>
+      </c>
+      <c r="D70">
+        <v>30.12573617336733</v>
+      </c>
+      <c r="E70">
+        <v>52.36000000000001</v>
+      </c>
+      <c r="F70">
+        <v>52.36000000000001</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>77</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>7.99</v>
+      </c>
+      <c r="L70">
+        <v>-7.99</v>
+      </c>
+      <c r="M70">
+        <v>12.503568</v>
+      </c>
+      <c r="N70">
+        <v>-20.493568</v>
+      </c>
+      <c r="O70">
+        <v>-5.123392000000001</v>
+      </c>
+      <c r="P70">
+        <v>-15.370176</v>
+      </c>
+      <c r="Q70">
+        <v>-7.380176000000002</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.4264423587750997</v>
+      </c>
+      <c r="T70">
+        <v>3.197920656414952</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>-0.1597543997041484</v>
+      </c>
+      <c r="W70">
+        <v>0.2769493506493507</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.6390175988165938</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.3267871132495904</v>
+      </c>
+      <c r="C71">
+        <v>-23.21347968933871</v>
+      </c>
+      <c r="D71">
+        <v>29.91652031066129</v>
+      </c>
+      <c r="E71">
+        <v>53.13</v>
+      </c>
+      <c r="F71">
+        <v>53.13</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>77</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>7.99</v>
+      </c>
+      <c r="L71">
+        <v>-7.99</v>
+      </c>
+      <c r="M71">
+        <v>12.687444</v>
+      </c>
+      <c r="N71">
+        <v>-20.677444</v>
+      </c>
+      <c r="O71">
+        <v>-5.169361</v>
+      </c>
+      <c r="P71">
+        <v>-15.508083</v>
+      </c>
+      <c r="Q71">
+        <v>-7.518083000000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4389469509936514</v>
+      </c>
+      <c r="T71">
+        <v>3.301079387267047</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>-0.1574391185490158</v>
+      </c>
+      <c r="W71">
+        <v>0.276396461509505</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.6297564741960635</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.3287871132495904</v>
+      </c>
+      <c r="C72">
+        <v>-24.18980968776808</v>
+      </c>
+      <c r="D72">
+        <v>29.71019031223193</v>
+      </c>
+      <c r="E72">
+        <v>53.90000000000001</v>
+      </c>
+      <c r="F72">
+        <v>53.90000000000001</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>77</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>7.99</v>
+      </c>
+      <c r="L72">
+        <v>-7.99</v>
+      </c>
+      <c r="M72">
+        <v>12.87132</v>
+      </c>
+      <c r="N72">
+        <v>-20.86132</v>
+      </c>
+      <c r="O72">
+        <v>-5.215330000000001</v>
+      </c>
+      <c r="P72">
+        <v>-15.64599</v>
+      </c>
+      <c r="Q72">
+        <v>-7.655990000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4522851826934398</v>
+      </c>
+      <c r="T72">
+        <v>3.411115366842616</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>-0.1551899882840299</v>
+      </c>
+      <c r="W72">
+        <v>0.2758593692022264</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.6207599531361196</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.3307871132495903</v>
+      </c>
+      <c r="C73">
+        <v>-25.16331312311889</v>
+      </c>
+      <c r="D73">
+        <v>29.5066868768811</v>
+      </c>
+      <c r="E73">
+        <v>54.66999999999999</v>
+      </c>
+      <c r="F73">
+        <v>54.66999999999999</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>77</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>7.99</v>
+      </c>
+      <c r="L73">
+        <v>-7.99</v>
+      </c>
+      <c r="M73">
+        <v>13.055196</v>
+      </c>
+      <c r="N73">
+        <v>-21.045196</v>
+      </c>
+      <c r="O73">
+        <v>-5.261298999999999</v>
+      </c>
+      <c r="P73">
+        <v>-15.783897</v>
+      </c>
+      <c r="Q73">
+        <v>-7.793896999999998</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4665432924414892</v>
+      </c>
+      <c r="T73">
+        <v>3.528740034664774</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>-0.1530042138011563</v>
+      </c>
+      <c r="W73">
+        <v>0.2753374062557161</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.612016855204625</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.3327871132495903</v>
+      </c>
+      <c r="C74">
+        <v>-26.13404768288056</v>
+      </c>
+      <c r="D74">
+        <v>29.30595231711943</v>
+      </c>
+      <c r="E74">
+        <v>55.44</v>
+      </c>
+      <c r="F74">
+        <v>55.44</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>77</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>7.99</v>
+      </c>
+      <c r="L74">
+        <v>-7.99</v>
+      </c>
+      <c r="M74">
+        <v>13.239072</v>
+      </c>
+      <c r="N74">
+        <v>-21.229072</v>
+      </c>
+      <c r="O74">
+        <v>-5.307268000000001</v>
+      </c>
+      <c r="P74">
+        <v>-15.921804</v>
+      </c>
+      <c r="Q74">
+        <v>-7.931804000000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4818198386001138</v>
+      </c>
+      <c r="T74">
+        <v>3.65476646447423</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>-0.1508791552761402</v>
+      </c>
+      <c r="W74">
+        <v>0.2748299422799423</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.6035166211045608</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.3347871132495903</v>
+      </c>
+      <c r="C75">
+        <v>-27.10206949535325</v>
+      </c>
+      <c r="D75">
+        <v>29.10793050464675</v>
+      </c>
+      <c r="E75">
+        <v>56.21</v>
+      </c>
+      <c r="F75">
+        <v>56.21</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>77</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>7.99</v>
+      </c>
+      <c r="L75">
+        <v>-7.99</v>
+      </c>
+      <c r="M75">
+        <v>13.422948</v>
+      </c>
+      <c r="N75">
+        <v>-21.412948</v>
+      </c>
+      <c r="O75">
+        <v>-5.353237</v>
+      </c>
+      <c r="P75">
+        <v>-16.059711</v>
+      </c>
+      <c r="Q75">
+        <v>-8.069711</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4982279807704884</v>
+      </c>
+      <c r="T75">
+        <v>3.790128185380682</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>-0.1488123175326314</v>
+      </c>
+      <c r="W75">
+        <v>0.2743363814267924</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.5952492701305256</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.3367871132495903</v>
+      </c>
+      <c r="C76">
+        <v>-28.0674331819719</v>
+      </c>
+      <c r="D76">
+        <v>28.91256681802809</v>
+      </c>
+      <c r="E76">
+        <v>56.98</v>
+      </c>
+      <c r="F76">
+        <v>56.98</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>77</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>7.99</v>
+      </c>
+      <c r="L76">
+        <v>-7.99</v>
+      </c>
+      <c r="M76">
+        <v>13.606824</v>
+      </c>
+      <c r="N76">
+        <v>-21.596824</v>
+      </c>
+      <c r="O76">
+        <v>-5.399206</v>
+      </c>
+      <c r="P76">
+        <v>-16.197618</v>
+      </c>
+      <c r="Q76">
+        <v>-8.207617999999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5158982877231995</v>
+      </c>
+      <c r="T76">
+        <v>3.935902346356863</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>-0.146801340268677</v>
+      </c>
+      <c r="W76">
+        <v>0.2738561600561601</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.5872053610747077</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.3387871132495903</v>
+      </c>
+      <c r="C77">
+        <v>-29.03019190753738</v>
+      </c>
+      <c r="D77">
+        <v>28.71980809246262</v>
+      </c>
+      <c r="E77">
+        <v>57.75</v>
+      </c>
+      <c r="F77">
+        <v>57.75</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>77</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>7.99</v>
+      </c>
+      <c r="L77">
+        <v>-7.99</v>
+      </c>
+      <c r="M77">
+        <v>13.7907</v>
+      </c>
+      <c r="N77">
+        <v>-21.7807</v>
+      </c>
+      <c r="O77">
+        <v>-5.445175000000001</v>
+      </c>
+      <c r="P77">
+        <v>-16.335525</v>
+      </c>
+      <c r="Q77">
+        <v>-8.345525000000004</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5349822192321276</v>
+      </c>
+      <c r="T77">
+        <v>4.093338440211138</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>-0.1448439890650946</v>
+      </c>
+      <c r="W77">
+        <v>0.2733887445887446</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.5793759562603784</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.3407871132495904</v>
+      </c>
+      <c r="C78">
+        <v>-29.9903974284513</v>
+      </c>
+      <c r="D78">
+        <v>28.52960257154871</v>
+      </c>
+      <c r="E78">
+        <v>58.52</v>
+      </c>
+      <c r="F78">
+        <v>58.52</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>77</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>7.99</v>
+      </c>
+      <c r="L78">
+        <v>-7.99</v>
+      </c>
+      <c r="M78">
+        <v>13.974576</v>
+      </c>
+      <c r="N78">
+        <v>-21.964576</v>
+      </c>
+      <c r="O78">
+        <v>-5.491144</v>
+      </c>
+      <c r="P78">
+        <v>-16.473432</v>
+      </c>
+      <c r="Q78">
+        <v>-8.483432000000002</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5556564783667997</v>
+      </c>
+      <c r="T78">
+        <v>4.263894208553269</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>-0.1429381471037118</v>
+      </c>
+      <c r="W78">
+        <v>0.2729336295283664</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.5717525884148471</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.3427871132495903</v>
+      </c>
+      <c r="C79">
+        <v>-30.94810013904695</v>
+      </c>
+      <c r="D79">
+        <v>28.34189986095305</v>
+      </c>
+      <c r="E79">
+        <v>59.29</v>
+      </c>
+      <c r="F79">
+        <v>59.29</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>77</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>7.99</v>
+      </c>
+      <c r="L79">
+        <v>-7.99</v>
+      </c>
+      <c r="M79">
+        <v>14.158452</v>
+      </c>
+      <c r="N79">
+        <v>-22.148452</v>
+      </c>
+      <c r="O79">
+        <v>-5.537113</v>
+      </c>
+      <c r="P79">
+        <v>-16.611339</v>
+      </c>
+      <c r="Q79">
+        <v>-8.621339000000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5781284991653561</v>
+      </c>
+      <c r="T79">
+        <v>4.449280913272976</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>-0.1410818075309363</v>
+      </c>
+      <c r="W79">
+        <v>0.2724903356383876</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.564327230123745</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.3447871132495903</v>
+      </c>
+      <c r="C80">
+        <v>-31.90334911610328</v>
+      </c>
+      <c r="D80">
+        <v>28.15665088389672</v>
+      </c>
+      <c r="E80">
+        <v>60.06</v>
+      </c>
+      <c r="F80">
+        <v>60.06</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>77</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>7.99</v>
+      </c>
+      <c r="L80">
+        <v>-7.99</v>
+      </c>
+      <c r="M80">
+        <v>14.342328</v>
+      </c>
+      <c r="N80">
+        <v>-22.332328</v>
+      </c>
+      <c r="O80">
+        <v>-5.583082000000001</v>
+      </c>
+      <c r="P80">
+        <v>-16.749246</v>
+      </c>
+      <c r="Q80">
+        <v>-8.759246000000003</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6026434309455995</v>
+      </c>
+      <c r="T80">
+        <v>4.651520954785384</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>-0.1392730664087448</v>
+      </c>
+      <c r="W80">
+        <v>0.2720584082584083</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.5570922656349793</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.3467871132495903</v>
+      </c>
+      <c r="C81">
+        <v>-32.85619216162434</v>
+      </c>
+      <c r="D81">
+        <v>27.97380783837566</v>
+      </c>
+      <c r="E81">
+        <v>60.83000000000001</v>
+      </c>
+      <c r="F81">
+        <v>60.83000000000001</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>77</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>7.99</v>
+      </c>
+      <c r="L81">
+        <v>-7.99</v>
+      </c>
+      <c r="M81">
+        <v>14.526204</v>
+      </c>
+      <c r="N81">
+        <v>-22.516204</v>
+      </c>
+      <c r="O81">
+        <v>-5.629051</v>
+      </c>
+      <c r="P81">
+        <v>-16.887153</v>
+      </c>
+      <c r="Q81">
+        <v>-8.897153000000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6294931181334853</v>
+      </c>
+      <c r="T81">
+        <v>4.873021952632308</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>-0.1375101162010391</v>
+      </c>
+      <c r="W81">
+        <v>0.2716374157488082</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.5500404648041566</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.3487871132495903</v>
+      </c>
+      <c r="C82">
+        <v>-33.80667584396278</v>
+      </c>
+      <c r="D82">
+        <v>27.79332415603722</v>
+      </c>
+      <c r="E82">
+        <v>61.6</v>
+      </c>
+      <c r="F82">
+        <v>61.6</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>77</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>7.99</v>
+      </c>
+      <c r="L82">
+        <v>-7.99</v>
+      </c>
+      <c r="M82">
+        <v>14.71008</v>
+      </c>
+      <c r="N82">
+        <v>-22.70008</v>
+      </c>
+      <c r="O82">
+        <v>-5.67502</v>
+      </c>
+      <c r="P82">
+        <v>-17.02506</v>
+      </c>
+      <c r="Q82">
+        <v>-9.03506</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6590277740401596</v>
+      </c>
+      <c r="T82">
+        <v>5.116673050263922</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>-0.1357912397485262</v>
+      </c>
+      <c r="W82">
+        <v>0.2712269480519481</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.5431649589941046</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.3507871132495903</v>
+      </c>
+      <c r="C83">
+        <v>-34.75484553736165</v>
+      </c>
+      <c r="D83">
+        <v>27.61515446263836</v>
+      </c>
+      <c r="E83">
+        <v>62.37</v>
+      </c>
+      <c r="F83">
+        <v>62.37</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>77</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>7.99</v>
+      </c>
+      <c r="L83">
+        <v>-7.99</v>
+      </c>
+      <c r="M83">
+        <v>14.893956</v>
+      </c>
+      <c r="N83">
+        <v>-22.883956</v>
+      </c>
+      <c r="O83">
+        <v>-5.720989</v>
+      </c>
+      <c r="P83">
+        <v>-17.162967</v>
+      </c>
+      <c r="Q83">
+        <v>-9.172967000000002</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6916713410949049</v>
+      </c>
+      <c r="T83">
+        <v>5.385971631856761</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>-0.1341148046899024</v>
+      </c>
+      <c r="W83">
+        <v>0.2708266153599487</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.5364592187596096</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.3527871132495903</v>
+      </c>
+      <c r="C84">
+        <v>-35.70074545998483</v>
+      </c>
+      <c r="D84">
+        <v>27.43925454001518</v>
+      </c>
+      <c r="E84">
+        <v>63.14000000000001</v>
+      </c>
+      <c r="F84">
+        <v>63.14000000000001</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>77</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>7.99</v>
+      </c>
+      <c r="L84">
+        <v>-7.99</v>
+      </c>
+      <c r="M84">
+        <v>15.077832</v>
+      </c>
+      <c r="N84">
+        <v>-23.067832</v>
+      </c>
+      <c r="O84">
+        <v>-5.766958000000001</v>
+      </c>
+      <c r="P84">
+        <v>-17.300874</v>
+      </c>
+      <c r="Q84">
+        <v>-9.310874</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7279419711557329</v>
+      </c>
+      <c r="T84">
+        <v>5.685192278071026</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>-0.132479258291245</v>
+      </c>
+      <c r="W84">
+        <v>0.2704360468799493</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.5299170331649801</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.3547871132495903</v>
+      </c>
+      <c r="C85">
+        <v>-36.64441871050337</v>
+      </c>
+      <c r="D85">
+        <v>27.26558128949663</v>
+      </c>
+      <c r="E85">
+        <v>63.91</v>
+      </c>
+      <c r="F85">
+        <v>63.91</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>77</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>7.99</v>
+      </c>
+      <c r="L85">
+        <v>-7.99</v>
+      </c>
+      <c r="M85">
+        <v>15.261708</v>
+      </c>
+      <c r="N85">
+        <v>-23.251708</v>
+      </c>
+      <c r="O85">
+        <v>-5.812927</v>
+      </c>
+      <c r="P85">
+        <v>-17.438781</v>
+      </c>
+      <c r="Q85">
+        <v>-9.448780999999999</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7684797341648937</v>
+      </c>
+      <c r="T85">
+        <v>6.019615353251675</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>-0.1308831226491818</v>
+      </c>
+      <c r="W85">
+        <v>0.2700548896886246</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.5235324905967274</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.3567871132495903</v>
+      </c>
+      <c r="C86">
+        <v>-37.58590730330112</v>
+      </c>
+      <c r="D86">
+        <v>27.09409269669887</v>
+      </c>
+      <c r="E86">
+        <v>64.67999999999999</v>
+      </c>
+      <c r="F86">
+        <v>64.67999999999999</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>77</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>7.99</v>
+      </c>
+      <c r="L86">
+        <v>-7.99</v>
+      </c>
+      <c r="M86">
+        <v>15.445584</v>
+      </c>
+      <c r="N86">
+        <v>-23.435584</v>
+      </c>
+      <c r="O86">
+        <v>-5.858896</v>
+      </c>
+      <c r="P86">
+        <v>-17.576688</v>
+      </c>
+      <c r="Q86">
+        <v>-9.586687999999997</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8140847175501991</v>
+      </c>
+      <c r="T86">
+        <v>6.395841312829901</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>-0.1293249902366916</v>
+      </c>
+      <c r="W86">
+        <v>0.2696828076685219</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.5172999609467666</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3587871132495903</v>
+      </c>
+      <c r="C87">
+        <v>-38.52525220236002</v>
+      </c>
+      <c r="D87">
+        <v>26.92474779763999</v>
+      </c>
+      <c r="E87">
+        <v>65.45</v>
+      </c>
+      <c r="F87">
+        <v>65.45</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>77</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>7.99</v>
+      </c>
+      <c r="L87">
+        <v>-7.99</v>
+      </c>
+      <c r="M87">
+        <v>15.62946</v>
+      </c>
+      <c r="N87">
+        <v>-23.61946</v>
+      </c>
+      <c r="O87">
+        <v>-5.904865000000001</v>
+      </c>
+      <c r="P87">
+        <v>-17.714595</v>
+      </c>
+      <c r="Q87">
+        <v>-9.724595000000003</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8657703653868791</v>
+      </c>
+      <c r="T87">
+        <v>6.822230733685228</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>-0.1278035197633187</v>
+      </c>
+      <c r="W87">
+        <v>0.2693194805194805</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.5112140790532751</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3607871132495903</v>
+      </c>
+      <c r="C88">
+        <v>-39.46249335388255</v>
+      </c>
+      <c r="D88">
+        <v>26.75750664611745</v>
+      </c>
+      <c r="E88">
+        <v>66.22</v>
+      </c>
+      <c r="F88">
+        <v>66.22</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>77</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>7.99</v>
+      </c>
+      <c r="L88">
+        <v>-7.99</v>
+      </c>
+      <c r="M88">
+        <v>15.813336</v>
+      </c>
+      <c r="N88">
+        <v>-23.803336</v>
+      </c>
+      <c r="O88">
+        <v>-5.950834</v>
+      </c>
+      <c r="P88">
+        <v>-17.852502</v>
+      </c>
+      <c r="Q88">
+        <v>-9.862502000000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9248396772002276</v>
+      </c>
+      <c r="T88">
+        <v>7.309532928948459</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>-0.1263174323242104</v>
+      </c>
+      <c r="W88">
+        <v>0.2689646028390215</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.5052697292968416</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.3627871132495903</v>
+      </c>
+      <c r="C89">
+        <v>-40.39766971770604</v>
+      </c>
+      <c r="D89">
+        <v>26.59233028229396</v>
+      </c>
+      <c r="E89">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="F89">
+        <v>66.98999999999999</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>77</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>7.99</v>
+      </c>
+      <c r="L89">
+        <v>-7.99</v>
+      </c>
+      <c r="M89">
+        <v>15.997212</v>
+      </c>
+      <c r="N89">
+        <v>-23.987212</v>
+      </c>
+      <c r="O89">
+        <v>-5.996803</v>
+      </c>
+      <c r="P89">
+        <v>-17.990409</v>
+      </c>
+      <c r="Q89">
+        <v>-10.000409</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.992996575446399</v>
+      </c>
+      <c r="T89">
+        <v>7.871804692713726</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>-0.1248655078147367</v>
+      </c>
+      <c r="W89">
+        <v>0.2686178832661592</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.4994620312589468</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3647871132495904</v>
+      </c>
+      <c r="C90">
+        <v>-41.33081929756035</v>
+      </c>
+      <c r="D90">
+        <v>26.42918070243965</v>
+      </c>
+      <c r="E90">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="F90">
+        <v>67.76000000000001</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>77</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>7.99</v>
+      </c>
+      <c r="L90">
+        <v>-7.99</v>
+      </c>
+      <c r="M90">
+        <v>16.181088</v>
+      </c>
+      <c r="N90">
+        <v>-24.171088</v>
+      </c>
+      <c r="O90">
+        <v>-6.042772000000001</v>
+      </c>
+      <c r="P90">
+        <v>-18.12831600000001</v>
+      </c>
+      <c r="Q90">
+        <v>-10.138316</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.072512956733599</v>
+      </c>
+      <c r="T90">
+        <v>8.527788417106539</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>-0.1234465815895692</v>
+      </c>
+      <c r="W90">
+        <v>0.2682790436835892</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.4937863263582771</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3667871132495903</v>
+      </c>
+      <c r="C91">
+        <v>-42.26197917021868</v>
+      </c>
+      <c r="D91">
+        <v>26.26802082978132</v>
+      </c>
+      <c r="E91">
+        <v>68.53</v>
+      </c>
+      <c r="F91">
+        <v>68.53</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>77</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>7.99</v>
+      </c>
+      <c r="L91">
+        <v>-7.99</v>
+      </c>
+      <c r="M91">
+        <v>16.364964</v>
+      </c>
+      <c r="N91">
+        <v>-24.354964</v>
+      </c>
+      <c r="O91">
+        <v>-6.088741000000001</v>
+      </c>
+      <c r="P91">
+        <v>-18.266223</v>
+      </c>
+      <c r="Q91">
+        <v>-10.276223</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.166486861891199</v>
+      </c>
+      <c r="T91">
+        <v>9.303041909570769</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>-0.1220595413469898</v>
+      </c>
+      <c r="W91">
+        <v>0.2679478184736612</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.4882381653879595</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3687871132495903</v>
+      </c>
+      <c r="C92">
+        <v>-43.19118551358829</v>
+      </c>
+      <c r="D92">
+        <v>26.1088144864117</v>
+      </c>
+      <c r="E92">
+        <v>69.3</v>
+      </c>
+      <c r="F92">
+        <v>69.3</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>77</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>7.99</v>
+      </c>
+      <c r="L92">
+        <v>-7.99</v>
+      </c>
+      <c r="M92">
+        <v>16.54884</v>
+      </c>
+      <c r="N92">
+        <v>-24.53884</v>
+      </c>
+      <c r="O92">
+        <v>-6.13471</v>
+      </c>
+      <c r="P92">
+        <v>-18.40413</v>
+      </c>
+      <c r="Q92">
+        <v>-10.41413</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.279255548080319</v>
+      </c>
+      <c r="T92">
+        <v>10.23334610052784</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>-0.1207033242209122</v>
+      </c>
+      <c r="W92">
+        <v>0.2676239538239538</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.4828132968836487</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3707871132495903</v>
+      </c>
+      <c r="C93">
+        <v>-44.1184736337858</v>
+      </c>
+      <c r="D93">
+        <v>25.95152636621421</v>
+      </c>
+      <c r="E93">
+        <v>70.07000000000001</v>
+      </c>
+      <c r="F93">
+        <v>70.07000000000001</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>77</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>7.99</v>
+      </c>
+      <c r="L93">
+        <v>-7.99</v>
+      </c>
+      <c r="M93">
+        <v>16.732716</v>
+      </c>
+      <c r="N93">
+        <v>-24.72271600000001</v>
+      </c>
+      <c r="O93">
+        <v>-6.180679000000001</v>
+      </c>
+      <c r="P93">
+        <v>-18.542037</v>
+      </c>
+      <c r="Q93">
+        <v>-10.552037</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.417083942311466</v>
+      </c>
+      <c r="T93">
+        <v>11.37038455614205</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>-0.1193769140646384</v>
+      </c>
+      <c r="W93">
+        <v>0.2673072070786356</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.4775076562585536</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3727871132495904</v>
+      </c>
+      <c r="C94">
+        <v>-45.04387799123968</v>
+      </c>
+      <c r="D94">
+        <v>25.79612200876032</v>
+      </c>
+      <c r="E94">
+        <v>70.84</v>
+      </c>
+      <c r="F94">
+        <v>70.84</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>77</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>7.99</v>
+      </c>
+      <c r="L94">
+        <v>-7.99</v>
+      </c>
+      <c r="M94">
+        <v>16.916592</v>
+      </c>
+      <c r="N94">
+        <v>-24.906592</v>
+      </c>
+      <c r="O94">
+        <v>-6.226648000000001</v>
+      </c>
+      <c r="P94">
+        <v>-18.679944</v>
+      </c>
+      <c r="Q94">
+        <v>-10.689944</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.589369435100399</v>
+      </c>
+      <c r="T94">
+        <v>12.79168262565981</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>-0.1180793389117619</v>
+      </c>
+      <c r="W94">
+        <v>0.2669973461321287</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.4723173556470477</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3747871132495904</v>
+      </c>
+      <c r="C95">
+        <v>-45.96743222586056</v>
+      </c>
+      <c r="D95">
+        <v>25.64256777413944</v>
+      </c>
+      <c r="E95">
+        <v>71.61</v>
+      </c>
+      <c r="F95">
+        <v>71.61</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>77</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>7.99</v>
+      </c>
+      <c r="L95">
+        <v>-7.99</v>
+      </c>
+      <c r="M95">
+        <v>17.100468</v>
+      </c>
+      <c r="N95">
+        <v>-25.090468</v>
+      </c>
+      <c r="O95">
+        <v>-6.272617</v>
+      </c>
+      <c r="P95">
+        <v>-18.817851</v>
+      </c>
+      <c r="Q95">
+        <v>-10.827851</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.810879354400457</v>
+      </c>
+      <c r="T95">
+        <v>14.61906585789693</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>-0.1168096686008827</v>
+      </c>
+      <c r="W95">
+        <v>0.2666941488618909</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.4672386744035311</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3767871132495904</v>
+      </c>
+      <c r="C96">
+        <v>-46.88916918131783</v>
+      </c>
+      <c r="D96">
+        <v>25.49083081868218</v>
+      </c>
+      <c r="E96">
+        <v>72.38000000000001</v>
+      </c>
+      <c r="F96">
+        <v>72.38000000000001</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>77</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>7.99</v>
+      </c>
+      <c r="L96">
+        <v>-7.99</v>
+      </c>
+      <c r="M96">
+        <v>17.284344</v>
+      </c>
+      <c r="N96">
+        <v>-25.27434400000001</v>
+      </c>
+      <c r="O96">
+        <v>-6.318586000000002</v>
+      </c>
+      <c r="P96">
+        <v>-18.955758</v>
+      </c>
+      <c r="Q96">
+        <v>-10.965758</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.1062259134672</v>
+      </c>
+      <c r="T96">
+        <v>17.05557683421309</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>-0.1155670125519371</v>
+      </c>
+      <c r="W96">
+        <v>0.2663974025974026</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.4622680502077487</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3787871132495904</v>
+      </c>
+      <c r="C97">
+        <v>-47.8091209284593</v>
+      </c>
+      <c r="D97">
+        <v>25.34087907154071</v>
+      </c>
+      <c r="E97">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="F97">
+        <v>73.15000000000001</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>77</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>7.99</v>
+      </c>
+      <c r="L97">
+        <v>-7.99</v>
+      </c>
+      <c r="M97">
+        <v>17.46822</v>
+      </c>
+      <c r="N97">
+        <v>-25.45822</v>
+      </c>
+      <c r="O97">
+        <v>-6.364555000000001</v>
+      </c>
+      <c r="P97">
+        <v>-19.093665</v>
+      </c>
+      <c r="Q97">
+        <v>-11.103665</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.519711096160642</v>
+      </c>
+      <c r="T97">
+        <v>20.46669220105572</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>-0.1143505176829694</v>
+      </c>
+      <c r="W97">
+        <v>0.2661069036226931</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.4574020707318778</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3807871132495904</v>
+      </c>
+      <c r="C98">
+        <v>-48.72731878790931</v>
+      </c>
+      <c r="D98">
+        <v>25.19268121209069</v>
+      </c>
+      <c r="E98">
+        <v>73.92</v>
+      </c>
+      <c r="F98">
+        <v>73.92</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>77</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>7.99</v>
+      </c>
+      <c r="L98">
+        <v>-7.99</v>
+      </c>
+      <c r="M98">
+        <v>17.652096</v>
+      </c>
+      <c r="N98">
+        <v>-25.642096</v>
+      </c>
+      <c r="O98">
+        <v>-6.410524000000001</v>
+      </c>
+      <c r="P98">
+        <v>-19.231572</v>
+      </c>
+      <c r="Q98">
+        <v>-11.241572</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.139938870200795</v>
+      </c>
+      <c r="T98">
+        <v>25.58336525131959</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>-0.1131593664571052</v>
+      </c>
+      <c r="W98">
+        <v>0.2658224567099567</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.4526374658284207</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3827871132495904</v>
+      </c>
+      <c r="C99">
+        <v>-49.64379335187829</v>
+      </c>
+      <c r="D99">
+        <v>25.0462066481217</v>
+      </c>
+      <c r="E99">
+        <v>74.69</v>
+      </c>
+      <c r="F99">
+        <v>74.69</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>77</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>7.99</v>
+      </c>
+      <c r="L99">
+        <v>-7.99</v>
+      </c>
+      <c r="M99">
+        <v>17.835972</v>
+      </c>
+      <c r="N99">
+        <v>-25.825972</v>
+      </c>
+      <c r="O99">
+        <v>-6.456493</v>
+      </c>
+      <c r="P99">
+        <v>-19.369479</v>
+      </c>
+      <c r="Q99">
+        <v>-11.379479</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.173651826934393</v>
+      </c>
+      <c r="T99">
+        <v>34.11115366842612</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>-0.1119927750503309</v>
+      </c>
+      <c r="W99">
+        <v>0.265543874682019</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.4479711002013234</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3847871132495904</v>
+      </c>
+      <c r="C100">
+        <v>-50.55857450521595</v>
+      </c>
+      <c r="D100">
+        <v>24.90142549478404</v>
+      </c>
+      <c r="E100">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="F100">
+        <v>75.45999999999999</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>77</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>7.99</v>
+      </c>
+      <c r="L100">
+        <v>-7.99</v>
+      </c>
+      <c r="M100">
+        <v>18.019848</v>
+      </c>
+      <c r="N100">
+        <v>-26.009848</v>
+      </c>
+      <c r="O100">
+        <v>-6.502462</v>
+      </c>
+      <c r="P100">
+        <v>-19.507386</v>
+      </c>
+      <c r="Q100">
+        <v>-11.517386</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.24107774040159</v>
+      </c>
+      <c r="T100">
+        <v>51.16673050263918</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>-0.1108499916314499</v>
+      </c>
+      <c r="W100">
+        <v>0.2652709780015903</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.4433999665257997</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3867871132495904</v>
+      </c>
+      <c r="C101">
+        <v>-51.47169144573854</v>
+      </c>
+      <c r="D101">
+        <v>24.75830855426146</v>
+      </c>
+      <c r="E101">
+        <v>76.23</v>
+      </c>
+      <c r="F101">
+        <v>76.23</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>77</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>7.99</v>
+      </c>
+      <c r="L101">
+        <v>-7.99</v>
+      </c>
+      <c r="M101">
+        <v>18.203724</v>
+      </c>
+      <c r="N101">
+        <v>-26.193724</v>
+      </c>
+      <c r="O101">
+        <v>-6.548431000000001</v>
+      </c>
+      <c r="P101">
+        <v>-19.645293</v>
+      </c>
+      <c r="Q101">
+        <v>-11.655293</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.44335548080318</v>
+      </c>
+      <c r="T101">
+        <v>102.3334610052784</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>-0.1097302947462838</v>
+      </c>
+      <c r="W101">
+        <v>0.2650035943854125</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.4389211789851353</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/ivory_coast/ivory_coast_oilfield_svcs_equip.xlsx
+++ b/research/traditional_assets/database/data/ivory_coast/ivory_coast_oilfield_svcs_equip.xlsx
@@ -1245,7 +1245,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1382,22 +1382,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1125216540491184</v>
+        <v>0.1122740999139956</v>
       </c>
       <c r="C2">
-        <v>105.8</v>
+        <v>104.8463961953064</v>
       </c>
       <c r="D2">
-        <v>105.8</v>
+        <v>105.9043961953064</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1.058</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1.058</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1418,28 +1418,28 @@
         <v>37.42</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0532174</v>
       </c>
       <c r="N2">
-        <v>37.42</v>
+        <v>37.3667826</v>
       </c>
       <c r="O2">
-        <v>9.355</v>
+        <v>9.34169565</v>
       </c>
       <c r="P2">
-        <v>28.065</v>
+        <v>28.02508695</v>
       </c>
       <c r="Q2">
-        <v>30.845</v>
+        <v>30.80508695</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1125216540491184</v>
+        <v>0.1130271211252481</v>
       </c>
       <c r="T2">
-        <v>0.7993082229751833</v>
+        <v>0.8053635883007529</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1456,7 +1456,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>703.1534798768824</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1464,22 +1464,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1122740999139956</v>
+        <v>0.1120265457788728</v>
       </c>
       <c r="C3">
-        <v>104.8463961953064</v>
+        <v>103.892998616136</v>
       </c>
       <c r="D3">
-        <v>105.9043961953064</v>
+        <v>106.008998616136</v>
       </c>
       <c r="E3">
-        <v>1.058</v>
+        <v>2.116</v>
       </c>
       <c r="F3">
-        <v>1.058</v>
+        <v>2.116</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1500,28 +1500,28 @@
         <v>37.42</v>
       </c>
       <c r="M3">
-        <v>0.0532174</v>
+        <v>0.1064348</v>
       </c>
       <c r="N3">
-        <v>37.3667826</v>
+        <v>37.3135652</v>
       </c>
       <c r="O3">
-        <v>9.34169565</v>
+        <v>9.3283913</v>
       </c>
       <c r="P3">
-        <v>28.02508695</v>
+        <v>27.9851739</v>
       </c>
       <c r="Q3">
-        <v>30.80508695</v>
+        <v>30.7651739</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1130271211252481</v>
+        <v>0.1135429038559927</v>
       </c>
       <c r="T3">
-        <v>0.8053635883007529</v>
+        <v>0.8115425325105178</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>703.1534798768824</v>
+        <v>351.5767399384412</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1546,22 +1546,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1120265457788728</v>
+        <v>0.11177899164375</v>
       </c>
       <c r="C4">
-        <v>103.892998616136</v>
+        <v>102.9398078741636</v>
       </c>
       <c r="D4">
-        <v>106.008998616136</v>
+        <v>106.1138078741636</v>
       </c>
       <c r="E4">
-        <v>2.116</v>
+        <v>3.174</v>
       </c>
       <c r="F4">
-        <v>2.116</v>
+        <v>3.174</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1582,28 +1582,28 @@
         <v>37.42</v>
       </c>
       <c r="M4">
-        <v>0.1064348</v>
+        <v>0.1596522</v>
       </c>
       <c r="N4">
-        <v>37.3135652</v>
+        <v>37.26034780000001</v>
       </c>
       <c r="O4">
-        <v>9.3283913</v>
+        <v>9.315086950000001</v>
       </c>
       <c r="P4">
-        <v>27.9851739</v>
+        <v>27.94526085</v>
       </c>
       <c r="Q4">
-        <v>30.7651739</v>
+        <v>30.72526085000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1135429038559927</v>
+        <v>0.1140693212822165</v>
       </c>
       <c r="T4">
-        <v>0.8115425325105178</v>
+        <v>0.8178488776318241</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>351.5767399384412</v>
+        <v>234.3844932922942</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.11177899164375</v>
+        <v>0.1115314375086272</v>
       </c>
       <c r="C5">
-        <v>102.9398078741636</v>
+        <v>101.9868245834853</v>
       </c>
       <c r="D5">
-        <v>106.1138078741636</v>
+        <v>106.2188245834853</v>
       </c>
       <c r="E5">
-        <v>3.174</v>
+        <v>4.232</v>
       </c>
       <c r="F5">
-        <v>3.174</v>
+        <v>4.232</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1664,28 +1664,28 @@
         <v>37.42</v>
       </c>
       <c r="M5">
-        <v>0.1596522</v>
+        <v>0.2128696</v>
       </c>
       <c r="N5">
-        <v>37.26034780000001</v>
+        <v>37.2071304</v>
       </c>
       <c r="O5">
-        <v>9.315086950000001</v>
+        <v>9.301782600000001</v>
       </c>
       <c r="P5">
-        <v>27.94526085</v>
+        <v>27.9053478</v>
       </c>
       <c r="Q5">
-        <v>30.72526085000001</v>
+        <v>30.6853478</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1140693212822165</v>
+        <v>0.1146067057381534</v>
       </c>
       <c r="T5">
-        <v>0.8178488776318241</v>
+        <v>0.8242866049431579</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>234.3844932922942</v>
+        <v>175.7883699692206</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1115314375086272</v>
+        <v>0.1112838833735044</v>
       </c>
       <c r="C6">
-        <v>101.9868245834853</v>
+        <v>101.0340493606307</v>
       </c>
       <c r="D6">
-        <v>106.2188245834853</v>
+        <v>106.3240493606307</v>
       </c>
       <c r="E6">
-        <v>4.232</v>
+        <v>5.29</v>
       </c>
       <c r="F6">
-        <v>4.232</v>
+        <v>5.29</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1746,28 +1746,28 @@
         <v>37.42</v>
       </c>
       <c r="M6">
-        <v>0.2128696</v>
+        <v>0.266087</v>
       </c>
       <c r="N6">
-        <v>37.2071304</v>
+        <v>37.153913</v>
       </c>
       <c r="O6">
-        <v>9.301782600000001</v>
+        <v>9.288478250000001</v>
       </c>
       <c r="P6">
-        <v>27.9053478</v>
+        <v>27.86543475</v>
       </c>
       <c r="Q6">
-        <v>30.6853478</v>
+        <v>30.64543475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1146067057381534</v>
+        <v>0.1151554035510573</v>
       </c>
       <c r="T6">
-        <v>0.8242866049431579</v>
+        <v>0.8308598633557827</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>175.7883699692206</v>
+        <v>140.6306959753765</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1112838833735044</v>
+        <v>0.1110363292383816</v>
       </c>
       <c r="C7">
-        <v>101.0340493606307</v>
+        <v>100.0814828245749</v>
       </c>
       <c r="D7">
-        <v>106.3240493606307</v>
+        <v>106.4294828245749</v>
       </c>
       <c r="E7">
-        <v>5.29</v>
+        <v>6.348000000000001</v>
       </c>
       <c r="F7">
-        <v>5.29</v>
+        <v>6.348000000000001</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1828,28 +1828,28 @@
         <v>37.42</v>
       </c>
       <c r="M7">
-        <v>0.266087</v>
+        <v>0.3193044</v>
       </c>
       <c r="N7">
-        <v>37.153913</v>
+        <v>37.1006956</v>
       </c>
       <c r="O7">
-        <v>9.288478250000001</v>
+        <v>9.2751739</v>
       </c>
       <c r="P7">
-        <v>27.86543475</v>
+        <v>27.8255217</v>
       </c>
       <c r="Q7">
-        <v>30.64543475</v>
+        <v>30.6055217</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1151554035510573</v>
+        <v>0.1157157757855124</v>
       </c>
       <c r="T7">
-        <v>0.8308598633557827</v>
+        <v>0.8375729783303782</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>140.6306959753765</v>
+        <v>117.1922466461471</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1110363292383816</v>
+        <v>0.1107887751032589</v>
       </c>
       <c r="C8">
-        <v>100.0814828245749</v>
+        <v>99.1291255967505</v>
       </c>
       <c r="D8">
-        <v>106.4294828245749</v>
+        <v>106.5351255967505</v>
       </c>
       <c r="E8">
-        <v>6.348</v>
+        <v>7.405999999999999</v>
       </c>
       <c r="F8">
-        <v>6.348</v>
+        <v>7.405999999999999</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1910,28 +1910,28 @@
         <v>37.42</v>
       </c>
       <c r="M8">
-        <v>0.3193044</v>
+        <v>0.3725217999999999</v>
       </c>
       <c r="N8">
-        <v>37.1006956</v>
+        <v>37.0474782</v>
       </c>
       <c r="O8">
-        <v>9.2751739</v>
+        <v>9.26186955</v>
       </c>
       <c r="P8">
-        <v>27.8255217</v>
+        <v>27.78560865</v>
       </c>
       <c r="Q8">
-        <v>30.6055217</v>
+        <v>30.56560865</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1157157757855124</v>
+        <v>0.1162881990357622</v>
       </c>
       <c r="T8">
-        <v>0.8375729783303782</v>
+        <v>0.8444304613689436</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>117.1922466461471</v>
+        <v>100.4504971252689</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1107887751032588</v>
+        <v>0.1105412209681361</v>
       </c>
       <c r="C9">
-        <v>99.12912559675048</v>
+        <v>98.17697830105999</v>
       </c>
       <c r="D9">
-        <v>106.5351255967505</v>
+        <v>106.64097830106</v>
       </c>
       <c r="E9">
-        <v>7.406000000000001</v>
+        <v>8.464</v>
       </c>
       <c r="F9">
-        <v>7.406000000000001</v>
+        <v>8.464</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1992,28 +1992,28 @@
         <v>37.42</v>
       </c>
       <c r="M9">
-        <v>0.3725218</v>
+        <v>0.4257392</v>
       </c>
       <c r="N9">
-        <v>37.0474782</v>
+        <v>36.9942608</v>
       </c>
       <c r="O9">
-        <v>9.26186955</v>
+        <v>9.2485652</v>
       </c>
       <c r="P9">
-        <v>27.78560865</v>
+        <v>27.7456956</v>
       </c>
       <c r="Q9">
-        <v>30.56560865</v>
+        <v>30.5256956</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1162881990357622</v>
+        <v>0.1168730662697131</v>
       </c>
       <c r="T9">
-        <v>0.8444304613689436</v>
+        <v>0.8514370201257389</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>100.4504971252689</v>
+        <v>87.89418498461029</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1105412209681361</v>
+        <v>0.1102936668330133</v>
       </c>
       <c r="C10">
-        <v>98.17697830105999</v>
+        <v>97.22504156388794</v>
       </c>
       <c r="D10">
-        <v>106.64097830106</v>
+        <v>106.7470415638879</v>
       </c>
       <c r="E10">
-        <v>8.464</v>
+        <v>9.522</v>
       </c>
       <c r="F10">
-        <v>8.464</v>
+        <v>9.522</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -2074,28 +2074,28 @@
         <v>37.42</v>
       </c>
       <c r="M10">
-        <v>0.4257392</v>
+        <v>0.4789566</v>
       </c>
       <c r="N10">
-        <v>36.9942608</v>
+        <v>36.94104340000001</v>
       </c>
       <c r="O10">
-        <v>9.2485652</v>
+        <v>9.235260850000001</v>
       </c>
       <c r="P10">
-        <v>27.7456956</v>
+        <v>27.70578255</v>
       </c>
       <c r="Q10">
-        <v>30.5256956</v>
+        <v>30.48578255</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1168730662697131</v>
+        <v>0.117470787728586</v>
       </c>
       <c r="T10">
-        <v>0.8514370201257389</v>
+        <v>0.8585975691848809</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>87.89418498461029</v>
+        <v>78.12816443076471</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1102936668330133</v>
+        <v>0.1100461126978904</v>
       </c>
       <c r="C11">
-        <v>97.22504156388794</v>
+        <v>96.27331601411335</v>
       </c>
       <c r="D11">
-        <v>106.7470415638879</v>
+        <v>106.8533160141133</v>
       </c>
       <c r="E11">
-        <v>9.522</v>
+        <v>10.58</v>
       </c>
       <c r="F11">
-        <v>9.522</v>
+        <v>10.58</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -2156,28 +2156,28 @@
         <v>37.42</v>
       </c>
       <c r="M11">
-        <v>0.4789566</v>
+        <v>0.5321739999999999</v>
       </c>
       <c r="N11">
-        <v>36.94104340000001</v>
+        <v>36.887826</v>
       </c>
       <c r="O11">
-        <v>9.235260850000001</v>
+        <v>9.221956500000001</v>
       </c>
       <c r="P11">
-        <v>27.70578255</v>
+        <v>27.6658695</v>
       </c>
       <c r="Q11">
-        <v>30.48578255</v>
+        <v>30.4458695</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.117470787728586</v>
+        <v>0.1180817918865449</v>
       </c>
       <c r="T11">
-        <v>0.8585975691848809</v>
+        <v>0.8659172415564486</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>78.12816443076471</v>
+        <v>70.31534798768826</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1100461126978904</v>
+        <v>0.1097985585627677</v>
       </c>
       <c r="C12">
-        <v>96.27331601411335</v>
+        <v>95.32180228312203</v>
       </c>
       <c r="D12">
-        <v>106.8533160141133</v>
+        <v>106.959802283122</v>
       </c>
       <c r="E12">
-        <v>10.58</v>
+        <v>11.638</v>
       </c>
       <c r="F12">
-        <v>10.58</v>
+        <v>11.638</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -2238,28 +2238,28 @@
         <v>37.42</v>
       </c>
       <c r="M12">
-        <v>0.5321739999999999</v>
+        <v>0.5853914</v>
       </c>
       <c r="N12">
-        <v>36.887826</v>
+        <v>36.8346086</v>
       </c>
       <c r="O12">
-        <v>9.221956500000001</v>
+        <v>9.208652150000001</v>
       </c>
       <c r="P12">
-        <v>27.6658695</v>
+        <v>27.62595645</v>
       </c>
       <c r="Q12">
-        <v>30.4458695</v>
+        <v>30.40595645000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1180817918865449</v>
+        <v>0.1187065264750199</v>
       </c>
       <c r="T12">
-        <v>0.8659172415564486</v>
+        <v>0.8734014009476021</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>70.31534798768826</v>
+        <v>63.92304362517113</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1097985585627677</v>
+        <v>0.1095510044276449</v>
       </c>
       <c r="C13">
-        <v>95.32180228312203</v>
+        <v>94.37050100481929</v>
       </c>
       <c r="D13">
-        <v>106.959802283122</v>
+        <v>107.0665010048193</v>
       </c>
       <c r="E13">
-        <v>11.638</v>
+        <v>12.696</v>
       </c>
       <c r="F13">
-        <v>11.638</v>
+        <v>12.696</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2320,28 +2320,28 @@
         <v>37.42</v>
       </c>
       <c r="M13">
-        <v>0.5853914</v>
+        <v>0.6386088</v>
       </c>
       <c r="N13">
-        <v>36.8346086</v>
+        <v>36.7813912</v>
       </c>
       <c r="O13">
-        <v>9.208652150000001</v>
+        <v>9.1953478</v>
       </c>
       <c r="P13">
-        <v>27.62595645</v>
+        <v>27.5860434</v>
       </c>
       <c r="Q13">
-        <v>30.40595645000001</v>
+        <v>30.3660434</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1187065264750199</v>
+        <v>0.1193454595768692</v>
       </c>
       <c r="T13">
-        <v>0.8734014009476021</v>
+        <v>0.8810556548703725</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>63.92304362517113</v>
+        <v>58.59612332307353</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1095510044276449</v>
+        <v>0.1093034502925221</v>
       </c>
       <c r="C14">
-        <v>94.37050100481929</v>
+        <v>93.41941281564233</v>
       </c>
       <c r="D14">
-        <v>107.0665010048193</v>
+        <v>107.1734128156423</v>
       </c>
       <c r="E14">
-        <v>12.696</v>
+        <v>13.754</v>
       </c>
       <c r="F14">
-        <v>12.696</v>
+        <v>13.754</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2402,28 +2402,28 @@
         <v>37.42</v>
       </c>
       <c r="M14">
-        <v>0.6386088</v>
+        <v>0.6918261999999999</v>
       </c>
       <c r="N14">
-        <v>36.7813912</v>
+        <v>36.7281738</v>
       </c>
       <c r="O14">
-        <v>9.1953478</v>
+        <v>9.18204345</v>
       </c>
       <c r="P14">
-        <v>27.5860434</v>
+        <v>27.54613035</v>
       </c>
       <c r="Q14">
-        <v>30.3660434</v>
+        <v>30.32613035</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1193454595768692</v>
+        <v>0.1199990807960024</v>
       </c>
       <c r="T14">
-        <v>0.8810556548703725</v>
+        <v>0.8888858686534366</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2440,7 +2440,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>58.59612332307353</v>
+        <v>54.08872922129865</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1093034502925221</v>
+        <v>0.1090558961573993</v>
       </c>
       <c r="C15">
-        <v>93.41941281564233</v>
+        <v>92.46853835457296</v>
       </c>
       <c r="D15">
-        <v>107.1734128156423</v>
+        <v>107.280538354573</v>
       </c>
       <c r="E15">
-        <v>13.754</v>
+        <v>14.812</v>
       </c>
       <c r="F15">
-        <v>13.754</v>
+        <v>14.812</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2484,28 +2484,28 @@
         <v>37.42</v>
       </c>
       <c r="M15">
-        <v>0.6918261999999999</v>
+        <v>0.7450436</v>
       </c>
       <c r="N15">
-        <v>36.7281738</v>
+        <v>36.6749564</v>
       </c>
       <c r="O15">
-        <v>9.18204345</v>
+        <v>9.1687391</v>
       </c>
       <c r="P15">
-        <v>27.54613035</v>
+        <v>27.5062173</v>
       </c>
       <c r="Q15">
-        <v>30.32613035</v>
+        <v>30.2862173</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1199990807960024</v>
+        <v>0.1206679025086038</v>
       </c>
       <c r="T15">
-        <v>0.8888858686534366</v>
+        <v>0.8968981804314557</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>54.08872922129865</v>
+        <v>50.22524856263446</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1090558961573993</v>
+        <v>0.1088083420222765</v>
       </c>
       <c r="C16">
-        <v>92.46853835457296</v>
+        <v>91.51787826315034</v>
       </c>
       <c r="D16">
-        <v>107.280538354573</v>
+        <v>107.3878782631503</v>
       </c>
       <c r="E16">
-        <v>14.812</v>
+        <v>15.87</v>
       </c>
       <c r="F16">
-        <v>14.812</v>
+        <v>15.87</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2566,28 +2566,28 @@
         <v>37.42</v>
       </c>
       <c r="M16">
-        <v>0.7450436</v>
+        <v>0.7982610000000001</v>
       </c>
       <c r="N16">
-        <v>36.6749564</v>
+        <v>36.62173900000001</v>
       </c>
       <c r="O16">
-        <v>9.1687391</v>
+        <v>9.155434750000001</v>
       </c>
       <c r="P16">
-        <v>27.5062173</v>
+        <v>27.46630425</v>
       </c>
       <c r="Q16">
-        <v>30.2862173</v>
+        <v>30.24630425</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1206679025086038</v>
+        <v>0.1213524612026782</v>
       </c>
       <c r="T16">
-        <v>0.8968981804314557</v>
+        <v>0.905099017192487</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>50.22524856263446</v>
+        <v>46.87689865845883</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1088083420222765</v>
+        <v>0.1085607878871537</v>
       </c>
       <c r="C17">
-        <v>91.51787826315034</v>
+        <v>90.56743318548376</v>
       </c>
       <c r="D17">
-        <v>107.3878782631503</v>
+        <v>107.4954331854838</v>
       </c>
       <c r="E17">
-        <v>15.87</v>
+        <v>16.928</v>
       </c>
       <c r="F17">
-        <v>15.87</v>
+        <v>16.928</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -2648,28 +2648,28 @@
         <v>37.42</v>
       </c>
       <c r="M17">
-        <v>0.7982609999999999</v>
+        <v>0.8514784</v>
       </c>
       <c r="N17">
-        <v>36.62173900000001</v>
+        <v>36.5685216</v>
       </c>
       <c r="O17">
-        <v>9.155434750000001</v>
+        <v>9.142130400000001</v>
       </c>
       <c r="P17">
-        <v>27.46630425</v>
+        <v>27.4263912</v>
       </c>
       <c r="Q17">
-        <v>30.24630425</v>
+        <v>30.20639120000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1213524612026782</v>
+        <v>0.1220533189132782</v>
       </c>
       <c r="T17">
-        <v>0.905099017192487</v>
+        <v>0.913495111971638</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>46.87689865845883</v>
+        <v>43.94709249230515</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1085607878871537</v>
+        <v>0.1083132337520309</v>
       </c>
       <c r="C18">
-        <v>90.56743318548376</v>
+        <v>89.6172037682656</v>
       </c>
       <c r="D18">
-        <v>107.4954331854838</v>
+        <v>107.6032037682656</v>
       </c>
       <c r="E18">
-        <v>16.928</v>
+        <v>17.986</v>
       </c>
       <c r="F18">
-        <v>16.928</v>
+        <v>17.986</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -2730,28 +2730,28 @@
         <v>37.42</v>
       </c>
       <c r="M18">
-        <v>0.8514784</v>
+        <v>0.9046957999999999</v>
       </c>
       <c r="N18">
-        <v>36.5685216</v>
+        <v>36.5153042</v>
       </c>
       <c r="O18">
-        <v>9.142130400000001</v>
+        <v>9.128826050000001</v>
       </c>
       <c r="P18">
-        <v>27.4263912</v>
+        <v>27.38647815</v>
       </c>
       <c r="Q18">
-        <v>30.20639120000001</v>
+        <v>30.16647815</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1220533189132782</v>
+        <v>0.122771064761483</v>
       </c>
       <c r="T18">
-        <v>0.913495111971638</v>
+        <v>0.9220935222876363</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>43.94709249230515</v>
+        <v>41.3619694045225</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1083132337520309</v>
+        <v>0.1080656796169081</v>
       </c>
       <c r="C19">
-        <v>89.6172037682656</v>
+        <v>88.66719066078416</v>
       </c>
       <c r="D19">
-        <v>107.6032037682656</v>
+        <v>107.7111906607842</v>
       </c>
       <c r="E19">
-        <v>17.986</v>
+        <v>19.044</v>
       </c>
       <c r="F19">
-        <v>17.986</v>
+        <v>19.044</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -2812,28 +2812,28 @@
         <v>37.42</v>
       </c>
       <c r="M19">
-        <v>0.9046957999999999</v>
+        <v>0.9579132</v>
       </c>
       <c r="N19">
-        <v>36.5153042</v>
+        <v>36.4620868</v>
       </c>
       <c r="O19">
-        <v>9.128826050000001</v>
+        <v>9.1155217</v>
       </c>
       <c r="P19">
-        <v>27.38647815</v>
+        <v>27.3465651</v>
       </c>
       <c r="Q19">
-        <v>30.16647815</v>
+        <v>30.1265651</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.122771064761483</v>
+        <v>0.1235063166059855</v>
       </c>
       <c r="T19">
-        <v>0.9220935222876363</v>
+        <v>0.9309016499284147</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>41.3619694045225</v>
+        <v>39.06408221538236</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1080656796169081</v>
+        <v>0.1078181254817853</v>
       </c>
       <c r="C20">
-        <v>88.66719066078416</v>
+        <v>87.71739451493683</v>
       </c>
       <c r="D20">
-        <v>107.7111906607842</v>
+        <v>107.8193945149368</v>
       </c>
       <c r="E20">
-        <v>19.044</v>
+        <v>20.102</v>
       </c>
       <c r="F20">
-        <v>19.044</v>
+        <v>20.102</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -2894,28 +2894,28 @@
         <v>37.42</v>
       </c>
       <c r="M20">
-        <v>0.9579132</v>
+        <v>1.0111306</v>
       </c>
       <c r="N20">
-        <v>36.4620868</v>
+        <v>36.4088694</v>
       </c>
       <c r="O20">
-        <v>9.1155217</v>
+        <v>9.10221735</v>
       </c>
       <c r="P20">
-        <v>27.3465651</v>
+        <v>27.30665205</v>
       </c>
       <c r="Q20">
-        <v>30.1265651</v>
+        <v>30.08665205</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1235063166059855</v>
+        <v>0.1242597228170189</v>
       </c>
       <c r="T20">
-        <v>0.9309016499284147</v>
+        <v>0.9399272622022991</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>39.06408221538236</v>
+        <v>37.00807788825697</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1078181254817853</v>
+        <v>0.1075705713466625</v>
       </c>
       <c r="C21">
-        <v>87.71739451493683</v>
+        <v>86.76781598524313</v>
       </c>
       <c r="D21">
-        <v>107.8193945149368</v>
+        <v>107.9278159852431</v>
       </c>
       <c r="E21">
-        <v>20.102</v>
+        <v>21.16</v>
       </c>
       <c r="F21">
-        <v>20.102</v>
+        <v>21.16</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -2976,28 +2976,28 @@
         <v>37.42</v>
       </c>
       <c r="M21">
-        <v>1.0111306</v>
+        <v>1.064348</v>
       </c>
       <c r="N21">
-        <v>36.4088694</v>
+        <v>36.355652</v>
       </c>
       <c r="O21">
-        <v>9.10221735</v>
+        <v>9.088913</v>
       </c>
       <c r="P21">
-        <v>27.30665205</v>
+        <v>27.266739</v>
       </c>
       <c r="Q21">
-        <v>30.08665205</v>
+        <v>30.046739</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1242597228170189</v>
+        <v>0.1250319641833281</v>
       </c>
       <c r="T21">
-        <v>0.9399272622022991</v>
+        <v>0.9491785147830302</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>37.00807788825697</v>
+        <v>35.15767399384412</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1075705713466625</v>
+        <v>0.1073230172115397</v>
       </c>
       <c r="C22">
-        <v>86.76781598524313</v>
+        <v>85.8184557288579</v>
       </c>
       <c r="D22">
-        <v>107.9278159852431</v>
+        <v>108.0364557288579</v>
       </c>
       <c r="E22">
-        <v>21.16</v>
+        <v>22.218</v>
       </c>
       <c r="F22">
-        <v>21.16</v>
+        <v>22.218</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -3058,28 +3058,28 @@
         <v>37.42</v>
       </c>
       <c r="M22">
-        <v>1.064348</v>
+        <v>1.1175654</v>
       </c>
       <c r="N22">
-        <v>36.355652</v>
+        <v>36.30243460000001</v>
       </c>
       <c r="O22">
-        <v>9.088913</v>
+        <v>9.075608650000001</v>
       </c>
       <c r="P22">
-        <v>27.266739</v>
+        <v>27.22682595000001</v>
       </c>
       <c r="Q22">
-        <v>30.046739</v>
+        <v>30.00682595000001</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1250319641833281</v>
+        <v>0.1258237559639743</v>
       </c>
       <c r="T22">
-        <v>0.9491785147830302</v>
+        <v>0.9586639762898559</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>35.15767399384412</v>
+        <v>33.48349904175631</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1073230172115397</v>
+        <v>0.1070754630764169</v>
       </c>
       <c r="C23">
-        <v>85.8184557288579</v>
+        <v>84.86931440558467</v>
       </c>
       <c r="D23">
-        <v>108.0364557288579</v>
+        <v>108.1453144055847</v>
       </c>
       <c r="E23">
-        <v>22.218</v>
+        <v>23.276</v>
       </c>
       <c r="F23">
-        <v>22.218</v>
+        <v>23.276</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -3140,28 +3140,28 @@
         <v>37.42</v>
       </c>
       <c r="M23">
-        <v>1.1175654</v>
+        <v>1.1707828</v>
       </c>
       <c r="N23">
-        <v>36.30243460000001</v>
+        <v>36.2492172</v>
       </c>
       <c r="O23">
-        <v>9.075608650000001</v>
+        <v>9.062304300000001</v>
       </c>
       <c r="P23">
-        <v>27.22682595000001</v>
+        <v>27.1869129</v>
       </c>
       <c r="Q23">
-        <v>30.00682595000001</v>
+        <v>29.9669129</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1258237559639743</v>
+        <v>0.1266358500979704</v>
       </c>
       <c r="T23">
-        <v>0.9586639762898559</v>
+        <v>0.9683926547583951</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>33.48349904175631</v>
+        <v>31.96152181258557</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1070754630764169</v>
+        <v>0.1068279089412941</v>
       </c>
       <c r="C24">
-        <v>84.86931440558467</v>
+        <v>83.92039267788888</v>
       </c>
       <c r="D24">
-        <v>108.1453144055847</v>
+        <v>108.2543926778889</v>
       </c>
       <c r="E24">
-        <v>23.276</v>
+        <v>24.334</v>
       </c>
       <c r="F24">
-        <v>23.276</v>
+        <v>24.334</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -3222,28 +3222,28 @@
         <v>37.42</v>
       </c>
       <c r="M24">
-        <v>1.1707828</v>
+        <v>1.2240002</v>
       </c>
       <c r="N24">
-        <v>36.2492172</v>
+        <v>36.1959998</v>
       </c>
       <c r="O24">
-        <v>9.062304300000001</v>
+        <v>9.048999950000001</v>
       </c>
       <c r="P24">
-        <v>27.1869129</v>
+        <v>27.14699985</v>
       </c>
       <c r="Q24">
-        <v>29.9669129</v>
+        <v>29.92699985</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1266358500979704</v>
+        <v>0.1274690375860963</v>
       </c>
       <c r="T24">
-        <v>0.9683926547583951</v>
+        <v>0.9783740261741692</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3260,7 +3260,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>31.96152181258557</v>
+        <v>30.57189042942967</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1068279089412941</v>
+        <v>0.1065803548061713</v>
       </c>
       <c r="C25">
-        <v>83.92039267788888</v>
+        <v>82.97169121091142</v>
       </c>
       <c r="D25">
-        <v>108.2543926778889</v>
+        <v>108.3636912109114</v>
       </c>
       <c r="E25">
-        <v>24.334</v>
+        <v>25.392</v>
       </c>
       <c r="F25">
-        <v>24.334</v>
+        <v>25.392</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -3304,28 +3304,28 @@
         <v>37.42</v>
       </c>
       <c r="M25">
-        <v>1.2240002</v>
+        <v>1.2772176</v>
       </c>
       <c r="N25">
-        <v>36.1959998</v>
+        <v>36.1427824</v>
       </c>
       <c r="O25">
-        <v>9.048999950000001</v>
+        <v>9.0356956</v>
       </c>
       <c r="P25">
-        <v>27.14699985</v>
+        <v>27.1070868</v>
       </c>
       <c r="Q25">
-        <v>29.92699985</v>
+        <v>29.8870868</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1274690375860963</v>
+        <v>0.1283241510607517</v>
       </c>
       <c r="T25">
-        <v>0.9783740261741692</v>
+        <v>0.9886180652587795</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>30.57189042942967</v>
+        <v>29.29806166153676</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1065803548061713</v>
+        <v>0.1063328006710485</v>
       </c>
       <c r="C26">
-        <v>82.97169121091143</v>
+        <v>82.02321067248215</v>
       </c>
       <c r="D26">
-        <v>108.3636912109114</v>
+        <v>108.4732106724822</v>
       </c>
       <c r="E26">
-        <v>25.392</v>
+        <v>26.45</v>
       </c>
       <c r="F26">
-        <v>25.392</v>
+        <v>26.45</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -3386,28 +3386,28 @@
         <v>37.42</v>
       </c>
       <c r="M26">
-        <v>1.2772176</v>
+        <v>1.330435</v>
       </c>
       <c r="N26">
-        <v>36.1427824</v>
+        <v>36.089565</v>
       </c>
       <c r="O26">
-        <v>9.0356956</v>
+        <v>9.02239125</v>
       </c>
       <c r="P26">
-        <v>27.1070868</v>
+        <v>27.06717375</v>
       </c>
       <c r="Q26">
-        <v>29.8870868</v>
+        <v>29.84717375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1283241510607517</v>
+        <v>0.129202067561398</v>
       </c>
       <c r="T26">
-        <v>0.9886180652587795</v>
+        <v>0.9991352787189791</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>29.29806166153677</v>
+        <v>28.1261391950753</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1063328006710485</v>
+        <v>0.1060852465359257</v>
       </c>
       <c r="C27">
-        <v>82.02321067248215</v>
+        <v>81.07495173313343</v>
       </c>
       <c r="D27">
-        <v>108.4732106724822</v>
+        <v>108.5829517331334</v>
       </c>
       <c r="E27">
-        <v>26.45</v>
+        <v>27.508</v>
       </c>
       <c r="F27">
-        <v>26.45</v>
+        <v>27.508</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -3468,28 +3468,28 @@
         <v>37.42</v>
       </c>
       <c r="M27">
-        <v>1.330435</v>
+        <v>1.3836524</v>
       </c>
       <c r="N27">
-        <v>36.089565</v>
+        <v>36.0363476</v>
       </c>
       <c r="O27">
-        <v>9.02239125</v>
+        <v>9.0090869</v>
       </c>
       <c r="P27">
-        <v>27.06717375</v>
+        <v>27.0272607</v>
       </c>
       <c r="Q27">
-        <v>29.84717375</v>
+        <v>29.8072607</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.129202067561398</v>
+        <v>0.1301037115350348</v>
       </c>
       <c r="T27">
-        <v>0.9991352787189791</v>
+        <v>1.009936741191617</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>28.1261391950753</v>
+        <v>27.04436461064932</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1060852465359257</v>
+        <v>0.1058376924008029</v>
       </c>
       <c r="C28">
-        <v>81.07495173313343</v>
+        <v>80.12691506611387</v>
       </c>
       <c r="D28">
-        <v>108.5829517331334</v>
+        <v>108.6929150661139</v>
       </c>
       <c r="E28">
-        <v>27.508</v>
+        <v>28.566</v>
       </c>
       <c r="F28">
-        <v>27.508</v>
+        <v>28.566</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -3550,28 +3550,28 @@
         <v>37.42</v>
       </c>
       <c r="M28">
-        <v>1.3836524</v>
+        <v>1.4368698</v>
       </c>
       <c r="N28">
-        <v>36.0363476</v>
+        <v>35.98313020000001</v>
       </c>
       <c r="O28">
-        <v>9.0090869</v>
+        <v>8.995782550000001</v>
       </c>
       <c r="P28">
-        <v>27.0272607</v>
+        <v>26.98734765</v>
       </c>
       <c r="Q28">
-        <v>29.8072607</v>
+        <v>29.76734765</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1301037115350348</v>
+        <v>0.1310300580832917</v>
       </c>
       <c r="T28">
-        <v>1.009936741191617</v>
+        <v>1.021034134142957</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>27.04436461064932</v>
+        <v>26.04272147692157</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1058376924008029</v>
+        <v>0.1055901382656801</v>
       </c>
       <c r="C29">
-        <v>80.12691506611387</v>
+        <v>79.17910134740202</v>
       </c>
       <c r="D29">
-        <v>108.6929150661139</v>
+        <v>108.803101347402</v>
       </c>
       <c r="E29">
-        <v>28.566</v>
+        <v>29.624</v>
       </c>
       <c r="F29">
-        <v>28.566</v>
+        <v>29.624</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -3632,28 +3632,28 @@
         <v>37.42</v>
       </c>
       <c r="M29">
-        <v>1.4368698</v>
+        <v>1.4900872</v>
       </c>
       <c r="N29">
-        <v>35.98313020000001</v>
+        <v>35.9299128</v>
       </c>
       <c r="O29">
-        <v>8.995782550000001</v>
+        <v>8.982478200000001</v>
       </c>
       <c r="P29">
-        <v>26.98734765</v>
+        <v>26.9474346</v>
       </c>
       <c r="Q29">
-        <v>29.76734765</v>
+        <v>29.7274346</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1310300580832917</v>
+        <v>0.1319821364801113</v>
       </c>
       <c r="T29">
-        <v>1.021034134142957</v>
+        <v>1.032439788009612</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>26.04272147692157</v>
+        <v>25.11262428131723</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1055901382656801</v>
+        <v>0.1053425841305573</v>
       </c>
       <c r="C30">
-        <v>79.17910134740202</v>
+        <v>78.23151125572041</v>
       </c>
       <c r="D30">
-        <v>108.803101347402</v>
+        <v>108.9135112557204</v>
       </c>
       <c r="E30">
-        <v>29.624</v>
+        <v>30.682</v>
       </c>
       <c r="F30">
-        <v>29.624</v>
+        <v>30.682</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -3714,28 +3714,28 @@
         <v>37.42</v>
       </c>
       <c r="M30">
-        <v>1.4900872</v>
+        <v>1.5433046</v>
       </c>
       <c r="N30">
-        <v>35.9299128</v>
+        <v>35.8766954</v>
       </c>
       <c r="O30">
-        <v>8.982478200000001</v>
+        <v>8.969173850000001</v>
       </c>
       <c r="P30">
-        <v>26.9474346</v>
+        <v>26.90752155</v>
       </c>
       <c r="Q30">
-        <v>29.7274346</v>
+        <v>29.68752155</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1319821364801113</v>
+        <v>0.1329610339867005</v>
       </c>
       <c r="T30">
-        <v>1.032439788009612</v>
+        <v>1.04416672790068</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3752,7 +3752,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>25.11262428131723</v>
+        <v>24.2466717198925</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1053425841305573</v>
+        <v>0.1050950299954345</v>
       </c>
       <c r="C31">
-        <v>78.23151125572041</v>
+        <v>77.28414547254921</v>
       </c>
       <c r="D31">
-        <v>108.9135112557204</v>
+        <v>109.0241454725492</v>
       </c>
       <c r="E31">
-        <v>30.682</v>
+        <v>31.74</v>
       </c>
       <c r="F31">
-        <v>30.682</v>
+        <v>31.74</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -3796,28 +3796,28 @@
         <v>37.42</v>
       </c>
       <c r="M31">
-        <v>1.5433046</v>
+        <v>1.596522</v>
       </c>
       <c r="N31">
-        <v>35.8766954</v>
+        <v>35.823478</v>
       </c>
       <c r="O31">
-        <v>8.969173850000001</v>
+        <v>8.9558695</v>
       </c>
       <c r="P31">
-        <v>26.90752155</v>
+        <v>26.8676085</v>
       </c>
       <c r="Q31">
-        <v>29.68752155</v>
+        <v>29.6476085</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1329610339867005</v>
+        <v>0.1339678999934779</v>
       </c>
       <c r="T31">
-        <v>1.04416672790068</v>
+        <v>1.056228723217207</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>24.2466717198925</v>
+        <v>23.43844932922942</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1050950299954345</v>
+        <v>0.1048474758603117</v>
       </c>
       <c r="C32">
-        <v>77.28414547254921</v>
+        <v>76.33700468214043</v>
       </c>
       <c r="D32">
-        <v>109.0241454725492</v>
+        <v>109.1350046821404</v>
       </c>
       <c r="E32">
-        <v>31.74</v>
+        <v>32.798</v>
       </c>
       <c r="F32">
-        <v>31.74</v>
+        <v>32.798</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -3878,28 +3878,28 @@
         <v>37.42</v>
       </c>
       <c r="M32">
-        <v>1.596522</v>
+        <v>1.6497394</v>
       </c>
       <c r="N32">
-        <v>35.823478</v>
+        <v>35.7702606</v>
       </c>
       <c r="O32">
-        <v>8.9558695</v>
+        <v>8.94256515</v>
       </c>
       <c r="P32">
-        <v>26.8676085</v>
+        <v>26.82769545</v>
       </c>
       <c r="Q32">
-        <v>29.6476085</v>
+        <v>29.60769545</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1339678999934779</v>
+        <v>0.1350039505221909</v>
       </c>
       <c r="T32">
-        <v>1.056228723217207</v>
+        <v>1.068640341586386</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -3916,7 +3916,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>23.43844932922942</v>
+        <v>22.68237031860911</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1048474758603117</v>
+        <v>0.1045999217251889</v>
       </c>
       <c r="C33">
-        <v>76.33700468214043</v>
+        <v>75.39008957153203</v>
       </c>
       <c r="D33">
-        <v>109.1350046821404</v>
+        <v>109.246089571532</v>
       </c>
       <c r="E33">
-        <v>32.798</v>
+        <v>33.856</v>
       </c>
       <c r="F33">
-        <v>32.798</v>
+        <v>33.856</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -3960,28 +3960,28 @@
         <v>37.42</v>
       </c>
       <c r="M33">
-        <v>1.6497394</v>
+        <v>1.7029568</v>
       </c>
       <c r="N33">
-        <v>35.7702606</v>
+        <v>35.7170432</v>
       </c>
       <c r="O33">
-        <v>8.94256515</v>
+        <v>8.9292608</v>
       </c>
       <c r="P33">
-        <v>26.82769545</v>
+        <v>26.7877824</v>
       </c>
       <c r="Q33">
-        <v>29.60769545</v>
+        <v>29.5677824</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1350039505221909</v>
+        <v>0.1360704731252779</v>
       </c>
       <c r="T33">
-        <v>1.068640341586386</v>
+        <v>1.08141700755466</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>22.68237031860911</v>
+        <v>21.97354624615257</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1045999217251889</v>
+        <v>0.1043523675900661</v>
       </c>
       <c r="C34">
-        <v>75.39008957153203</v>
+        <v>74.44340083056206</v>
       </c>
       <c r="D34">
-        <v>109.246089571532</v>
+        <v>109.3574008305621</v>
       </c>
       <c r="E34">
-        <v>33.856</v>
+        <v>34.914</v>
       </c>
       <c r="F34">
-        <v>33.856</v>
+        <v>34.914</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -4042,28 +4042,28 @@
         <v>37.42</v>
       </c>
       <c r="M34">
-        <v>1.7029568</v>
+        <v>1.7561742</v>
       </c>
       <c r="N34">
-        <v>35.7170432</v>
+        <v>35.66382580000001</v>
       </c>
       <c r="O34">
-        <v>8.9292608</v>
+        <v>8.915956450000001</v>
       </c>
       <c r="P34">
-        <v>26.7877824</v>
+        <v>26.74786935</v>
       </c>
       <c r="Q34">
-        <v>29.5677824</v>
+        <v>29.52786935</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1360704731252779</v>
+        <v>0.1371688322239793</v>
       </c>
       <c r="T34">
-        <v>1.08141700755466</v>
+        <v>1.094575066536912</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>21.97354624615257</v>
+        <v>21.30768120839038</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1043523675900661</v>
+        <v>0.1041048134549434</v>
       </c>
       <c r="C35">
-        <v>74.44340083056206</v>
+        <v>73.49693915188291</v>
       </c>
       <c r="D35">
-        <v>109.3574008305621</v>
+        <v>109.4689391518829</v>
       </c>
       <c r="E35">
-        <v>34.914</v>
+        <v>35.972</v>
       </c>
       <c r="F35">
-        <v>34.914</v>
+        <v>35.972</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -4124,28 +4124,28 @@
         <v>37.42</v>
       </c>
       <c r="M35">
-        <v>1.7561742</v>
+        <v>1.8093916</v>
       </c>
       <c r="N35">
-        <v>35.66382580000001</v>
+        <v>35.6106084</v>
       </c>
       <c r="O35">
-        <v>8.915956450000001</v>
+        <v>8.902652100000001</v>
       </c>
       <c r="P35">
-        <v>26.74786935</v>
+        <v>26.7079563</v>
       </c>
       <c r="Q35">
-        <v>29.52786935</v>
+        <v>29.4879563</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1371688322239793</v>
+        <v>0.1383004749317324</v>
       </c>
       <c r="T35">
-        <v>1.094575066536912</v>
+        <v>1.108131854579232</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4162,7 +4162,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>21.30768120839038</v>
+        <v>20.68098470226125</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1041048134549434</v>
+        <v>0.1038572593198206</v>
       </c>
       <c r="C36">
-        <v>73.49693915188291</v>
+        <v>72.55070523097579</v>
       </c>
       <c r="D36">
-        <v>109.4689391518829</v>
+        <v>109.5807052309758</v>
       </c>
       <c r="E36">
-        <v>35.972</v>
+        <v>37.03</v>
       </c>
       <c r="F36">
-        <v>35.972</v>
+        <v>37.03</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -4206,28 +4206,28 @@
         <v>37.42</v>
       </c>
       <c r="M36">
-        <v>1.8093916</v>
+        <v>1.862609</v>
       </c>
       <c r="N36">
-        <v>35.6106084</v>
+        <v>35.557391</v>
       </c>
       <c r="O36">
-        <v>8.902652100000001</v>
+        <v>8.889347750000001</v>
       </c>
       <c r="P36">
-        <v>26.7079563</v>
+        <v>26.66804325</v>
       </c>
       <c r="Q36">
-        <v>29.4879563</v>
+        <v>29.44804325</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1383004749317324</v>
+        <v>0.1394669374151086</v>
       </c>
       <c r="T36">
-        <v>1.108131854579232</v>
+        <v>1.122105774561315</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>20.68098470226125</v>
+        <v>20.09009942505378</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1038572593198206</v>
+        <v>0.1036097051846977</v>
       </c>
       <c r="C37">
-        <v>72.55070523097579</v>
+        <v>71.60469976616503</v>
       </c>
       <c r="D37">
-        <v>109.5807052309758</v>
+        <v>109.692699766165</v>
       </c>
       <c r="E37">
-        <v>37.03</v>
+        <v>38.088</v>
       </c>
       <c r="F37">
-        <v>37.03</v>
+        <v>38.088</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -4288,28 +4288,28 @@
         <v>37.42</v>
       </c>
       <c r="M37">
-        <v>1.862609</v>
+        <v>1.9158264</v>
       </c>
       <c r="N37">
-        <v>35.557391</v>
+        <v>35.5041736</v>
       </c>
       <c r="O37">
-        <v>8.889347750000001</v>
+        <v>8.8760434</v>
       </c>
       <c r="P37">
-        <v>26.66804325</v>
+        <v>26.6281302</v>
       </c>
       <c r="Q37">
-        <v>29.44804325</v>
+        <v>29.4081302</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1394669374151086</v>
+        <v>0.1406698518510902</v>
       </c>
       <c r="T37">
-        <v>1.122105774561315</v>
+        <v>1.136516379542839</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>20.09009942505378</v>
+        <v>19.53204110769118</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1036097051846978</v>
+        <v>0.1033621510495749</v>
       </c>
       <c r="C38">
-        <v>71.60469976616503</v>
+        <v>70.65892345863278</v>
       </c>
       <c r="D38">
-        <v>109.692699766165</v>
+        <v>109.8049234586328</v>
       </c>
       <c r="E38">
-        <v>38.088</v>
+        <v>39.146</v>
       </c>
       <c r="F38">
-        <v>38.088</v>
+        <v>39.146</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -4370,28 +4370,28 @@
         <v>37.42</v>
       </c>
       <c r="M38">
-        <v>1.9158264</v>
+        <v>1.9690438</v>
       </c>
       <c r="N38">
-        <v>35.5041736</v>
+        <v>35.4509562</v>
       </c>
       <c r="O38">
-        <v>8.8760434</v>
+        <v>8.86273905</v>
       </c>
       <c r="P38">
-        <v>26.6281302</v>
+        <v>26.58821715</v>
       </c>
       <c r="Q38">
-        <v>29.4081302</v>
+        <v>29.36821715</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1406698518510902</v>
+        <v>0.1419109540469444</v>
       </c>
       <c r="T38">
-        <v>1.136516379542839</v>
+        <v>1.151384464047585</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4408,7 +4408,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>19.53204110769118</v>
+        <v>19.0041481047806</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1033621510495749</v>
+        <v>0.1031145969144522</v>
       </c>
       <c r="C39">
-        <v>70.65892345863278</v>
+        <v>69.71337701243354</v>
       </c>
       <c r="D39">
-        <v>109.8049234586328</v>
+        <v>109.9173770124335</v>
       </c>
       <c r="E39">
-        <v>39.146</v>
+        <v>40.204</v>
       </c>
       <c r="F39">
-        <v>39.146</v>
+        <v>40.204</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -4452,28 +4452,28 @@
         <v>37.42</v>
       </c>
       <c r="M39">
-        <v>1.9690438</v>
+        <v>2.0222612</v>
       </c>
       <c r="N39">
-        <v>35.4509562</v>
+        <v>35.3977388</v>
       </c>
       <c r="O39">
-        <v>8.86273905</v>
+        <v>8.8494347</v>
       </c>
       <c r="P39">
-        <v>26.58821715</v>
+        <v>26.5483041</v>
       </c>
       <c r="Q39">
-        <v>29.36821715</v>
+        <v>29.3283041</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1419109540469444</v>
+        <v>0.1431920917975035</v>
       </c>
       <c r="T39">
-        <v>1.151384464047585</v>
+        <v>1.166732164181518</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>19.0041481047806</v>
+        <v>18.50403894412848</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1031145969144522</v>
+        <v>0.1028670427793294</v>
       </c>
       <c r="C40">
-        <v>69.71337701243354</v>
+        <v>68.76806113450894</v>
       </c>
       <c r="D40">
-        <v>109.9173770124335</v>
+        <v>110.0300611345089</v>
       </c>
       <c r="E40">
-        <v>40.204</v>
+        <v>41.262</v>
       </c>
       <c r="F40">
-        <v>40.204</v>
+        <v>41.262</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -4534,28 +4534,28 @@
         <v>37.42</v>
       </c>
       <c r="M40">
-        <v>2.0222612</v>
+        <v>2.0754786</v>
       </c>
       <c r="N40">
-        <v>35.3977388</v>
+        <v>35.3445214</v>
       </c>
       <c r="O40">
-        <v>8.8494347</v>
+        <v>8.836130350000001</v>
       </c>
       <c r="P40">
-        <v>26.5483041</v>
+        <v>26.50839105</v>
       </c>
       <c r="Q40">
-        <v>29.3283041</v>
+        <v>29.28839105</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1431920917975035</v>
+        <v>0.1445152340644744</v>
       </c>
       <c r="T40">
-        <v>1.166732164181518</v>
+        <v>1.182583067598529</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>18.50403894412848</v>
+        <v>18.02957640709955</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1028670427793294</v>
+        <v>0.1026194886442066</v>
       </c>
       <c r="C41">
-        <v>68.76806113450894</v>
+        <v>67.82297653470246</v>
       </c>
       <c r="D41">
-        <v>110.0300611345089</v>
+        <v>110.1429765347025</v>
       </c>
       <c r="E41">
-        <v>41.262</v>
+        <v>42.32</v>
       </c>
       <c r="F41">
-        <v>41.262</v>
+        <v>42.32</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -4616,28 +4616,28 @@
         <v>37.42</v>
       </c>
       <c r="M41">
-        <v>2.0754786</v>
+        <v>2.128696</v>
       </c>
       <c r="N41">
-        <v>35.3445214</v>
+        <v>35.291304</v>
       </c>
       <c r="O41">
-        <v>8.836130350000001</v>
+        <v>8.822826000000001</v>
       </c>
       <c r="P41">
-        <v>26.50839105</v>
+        <v>26.468478</v>
       </c>
       <c r="Q41">
-        <v>29.28839105</v>
+        <v>29.24847800000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1445152340644744</v>
+        <v>0.1458824810736776</v>
       </c>
       <c r="T41">
-        <v>1.182583067598529</v>
+        <v>1.198962334462775</v>
       </c>
       <c r="U41">
         <v>0.0503</v>
@@ -4654,7 +4654,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>18.02957640709955</v>
+        <v>17.57883699692206</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1026194886442066</v>
+        <v>0.1023719345090838</v>
       </c>
       <c r="C42">
-        <v>67.82297653470246</v>
+        <v>66.87812392577452</v>
       </c>
       <c r="D42">
-        <v>110.1429765347025</v>
+        <v>110.2561239257745</v>
       </c>
       <c r="E42">
-        <v>42.32</v>
+        <v>43.378</v>
       </c>
       <c r="F42">
-        <v>42.32</v>
+        <v>43.378</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -4698,28 +4698,28 @@
         <v>37.42</v>
       </c>
       <c r="M42">
-        <v>2.128696</v>
+        <v>2.1819134</v>
       </c>
       <c r="N42">
-        <v>35.291304</v>
+        <v>35.2380866</v>
       </c>
       <c r="O42">
-        <v>8.822826000000001</v>
+        <v>8.809521650000001</v>
       </c>
       <c r="P42">
-        <v>26.468478</v>
+        <v>26.42856495</v>
       </c>
       <c r="Q42">
-        <v>29.24847800000001</v>
+        <v>29.20856495</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1458824810736776</v>
+        <v>0.1472960754391251</v>
       </c>
       <c r="T42">
-        <v>1.198962334462775</v>
+        <v>1.215896830712249</v>
       </c>
       <c r="U42">
         <v>0.0503</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>17.57883699692206</v>
+        <v>17.15008487504591</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1023719345090838</v>
+        <v>0.102124380373961</v>
       </c>
       <c r="C43">
-        <v>66.87812392577452</v>
+        <v>65.93350402341724</v>
       </c>
       <c r="D43">
-        <v>110.2561239257745</v>
+        <v>110.3695040234172</v>
       </c>
       <c r="E43">
-        <v>43.378</v>
+        <v>44.436</v>
       </c>
       <c r="F43">
-        <v>43.378</v>
+        <v>44.436</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -4780,28 +4780,28 @@
         <v>37.42</v>
       </c>
       <c r="M43">
-        <v>2.1819134</v>
+        <v>2.2351308</v>
       </c>
       <c r="N43">
-        <v>35.2380866</v>
+        <v>35.1848692</v>
       </c>
       <c r="O43">
-        <v>8.809521650000001</v>
+        <v>8.7962173</v>
       </c>
       <c r="P43">
-        <v>26.42856495</v>
+        <v>26.3886519</v>
       </c>
       <c r="Q43">
-        <v>29.20856495</v>
+        <v>29.1686519</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1472960754391251</v>
+        <v>0.1487584144378638</v>
       </c>
       <c r="T43">
-        <v>1.215896830712249</v>
+        <v>1.233415275108257</v>
       </c>
       <c r="U43">
         <v>0.0503</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>17.15008487504591</v>
+        <v>16.74174952087815</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.102124380373961</v>
+        <v>0.1018768262388382</v>
       </c>
       <c r="C44">
-        <v>65.93350402341724</v>
+        <v>64.98911754626975</v>
       </c>
       <c r="D44">
-        <v>110.3695040234172</v>
+        <v>110.4831175462698</v>
       </c>
       <c r="E44">
-        <v>44.436</v>
+        <v>45.494</v>
       </c>
       <c r="F44">
-        <v>44.436</v>
+        <v>45.494</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -4862,28 +4862,28 @@
         <v>37.42</v>
       </c>
       <c r="M44">
-        <v>2.2351308</v>
+        <v>2.2883482</v>
       </c>
       <c r="N44">
-        <v>35.1848692</v>
+        <v>35.1316518</v>
       </c>
       <c r="O44">
-        <v>8.7962173</v>
+        <v>8.78291295</v>
       </c>
       <c r="P44">
-        <v>26.3886519</v>
+        <v>26.34873885</v>
       </c>
       <c r="Q44">
-        <v>29.1686519</v>
+        <v>29.12873885</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1487584144378638</v>
+        <v>0.1502720635769091</v>
       </c>
       <c r="T44">
-        <v>1.233415275108257</v>
+        <v>1.251548401763774</v>
       </c>
       <c r="U44">
         <v>0.0503</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>16.74174952087815</v>
+        <v>16.35240650876471</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1018768262388382</v>
+        <v>0.1016292721037154</v>
       </c>
       <c r="C45">
-        <v>64.98911754626975</v>
+        <v>64.04496521593322</v>
       </c>
       <c r="D45">
-        <v>110.4831175462698</v>
+        <v>110.5969652159332</v>
       </c>
       <c r="E45">
-        <v>45.494</v>
+        <v>46.552</v>
       </c>
       <c r="F45">
-        <v>45.494</v>
+        <v>46.552</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -4944,28 +4944,28 @@
         <v>37.42</v>
       </c>
       <c r="M45">
-        <v>2.2883482</v>
+        <v>2.3415656</v>
       </c>
       <c r="N45">
-        <v>35.1316518</v>
+        <v>35.0784344</v>
       </c>
       <c r="O45">
-        <v>8.78291295</v>
+        <v>8.7696086</v>
       </c>
       <c r="P45">
-        <v>26.34873885</v>
+        <v>26.3088258</v>
       </c>
       <c r="Q45">
-        <v>29.12873885</v>
+        <v>29.0888258</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1502720635769091</v>
+        <v>0.1518397716137775</v>
       </c>
       <c r="T45">
-        <v>1.251548401763774</v>
+        <v>1.270329140085559</v>
       </c>
       <c r="U45">
         <v>0.0503</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>16.35240650876471</v>
+        <v>15.98076090629278</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1016292721037154</v>
+        <v>0.1013817179685926</v>
       </c>
       <c r="C46">
-        <v>64.04496521593322</v>
+        <v>63.10104775698618</v>
       </c>
       <c r="D46">
-        <v>110.5969652159332</v>
+        <v>110.7110477569862</v>
       </c>
       <c r="E46">
-        <v>46.552</v>
+        <v>47.61</v>
       </c>
       <c r="F46">
-        <v>46.552</v>
+        <v>47.61</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -5026,28 +5026,28 @@
         <v>37.42</v>
       </c>
       <c r="M46">
-        <v>2.3415656</v>
+        <v>2.394783</v>
       </c>
       <c r="N46">
-        <v>35.0784344</v>
+        <v>35.025217</v>
       </c>
       <c r="O46">
-        <v>8.7696086</v>
+        <v>8.756304250000001</v>
       </c>
       <c r="P46">
-        <v>26.3088258</v>
+        <v>26.26891275000001</v>
       </c>
       <c r="Q46">
-        <v>29.0888258</v>
+        <v>29.04891275000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1518397716137775</v>
+        <v>0.1534644872156229</v>
       </c>
       <c r="T46">
-        <v>1.270329140085559</v>
+        <v>1.289792814346318</v>
       </c>
       <c r="U46">
         <v>0.0503</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>15.98076090629278</v>
+        <v>15.62563288615294</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1013817179685926</v>
+        <v>0.1011341638334698</v>
       </c>
       <c r="C47">
-        <v>63.10104775698618</v>
+        <v>62.15736589699994</v>
       </c>
       <c r="D47">
-        <v>110.7110477569862</v>
+        <v>110.8253658969999</v>
       </c>
       <c r="E47">
-        <v>47.61</v>
+        <v>48.668</v>
       </c>
       <c r="F47">
-        <v>47.61</v>
+        <v>48.668</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -5108,28 +5108,28 @@
         <v>37.42</v>
       </c>
       <c r="M47">
-        <v>2.394783</v>
+        <v>2.4480004</v>
       </c>
       <c r="N47">
-        <v>35.025217</v>
+        <v>34.9719996</v>
       </c>
       <c r="O47">
-        <v>8.756304250000001</v>
+        <v>8.742999900000001</v>
       </c>
       <c r="P47">
-        <v>26.26891275000001</v>
+        <v>26.2289997</v>
       </c>
       <c r="Q47">
-        <v>29.04891275000001</v>
+        <v>29.0089997</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1534644872156229</v>
+        <v>0.1551493774693885</v>
       </c>
       <c r="T47">
-        <v>1.289792814346318</v>
+        <v>1.309977365431551</v>
       </c>
       <c r="U47">
         <v>0.0503</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>15.62563288615294</v>
+        <v>15.28594521471484</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1011341638334698</v>
+        <v>0.100886609698347</v>
       </c>
       <c r="C48">
-        <v>62.15736589699994</v>
+        <v>61.21392036655408</v>
       </c>
       <c r="D48">
-        <v>110.8253658969999</v>
+        <v>110.9399203665541</v>
       </c>
       <c r="E48">
-        <v>48.668</v>
+        <v>49.726</v>
       </c>
       <c r="F48">
-        <v>48.668</v>
+        <v>49.726</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -5190,28 +5190,28 @@
         <v>37.42</v>
       </c>
       <c r="M48">
-        <v>2.4480004</v>
+        <v>2.5012178</v>
       </c>
       <c r="N48">
-        <v>34.9719996</v>
+        <v>34.9187822</v>
       </c>
       <c r="O48">
-        <v>8.742999900000001</v>
+        <v>8.729695550000001</v>
       </c>
       <c r="P48">
-        <v>26.2289997</v>
+        <v>26.18908665</v>
       </c>
       <c r="Q48">
-        <v>29.0089997</v>
+        <v>28.96908665</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1551493774693885</v>
+        <v>0.1568978484874472</v>
       </c>
       <c r="T48">
-        <v>1.309977365431551</v>
+        <v>1.33092359768981</v>
       </c>
       <c r="U48">
         <v>0.0503</v>
@@ -5228,7 +5228,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>15.28594521471484</v>
+        <v>14.96071233780601</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.100886609698347</v>
+        <v>0.1006390555632242</v>
       </c>
       <c r="C49">
-        <v>61.21392036655408</v>
+        <v>60.27071189925179</v>
       </c>
       <c r="D49">
-        <v>110.9399203665541</v>
+        <v>111.0547118992518</v>
       </c>
       <c r="E49">
-        <v>49.726</v>
+        <v>50.78400000000001</v>
       </c>
       <c r="F49">
-        <v>49.726</v>
+        <v>50.78400000000001</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -5272,28 +5272,28 @@
         <v>37.42</v>
       </c>
       <c r="M49">
-        <v>2.5012178</v>
+        <v>2.5544352</v>
       </c>
       <c r="N49">
-        <v>34.9187822</v>
+        <v>34.8655648</v>
       </c>
       <c r="O49">
-        <v>8.729695550000001</v>
+        <v>8.7163912</v>
       </c>
       <c r="P49">
-        <v>26.18908665</v>
+        <v>26.1491736</v>
       </c>
       <c r="Q49">
-        <v>28.96908665</v>
+        <v>28.9291736</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1568978484874472</v>
+        <v>0.1587135683908158</v>
       </c>
       <c r="T49">
-        <v>1.33092359768981</v>
+        <v>1.352675454265695</v>
       </c>
       <c r="U49">
         <v>0.0503</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>14.96071233780601</v>
+        <v>14.64903083076838</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1006390555632242</v>
+        <v>0.1003915014281014</v>
       </c>
       <c r="C50">
-        <v>60.2707118992518</v>
+        <v>59.3277412317359</v>
       </c>
       <c r="D50">
-        <v>111.0547118992518</v>
+        <v>111.1697412317359</v>
       </c>
       <c r="E50">
-        <v>50.784</v>
+        <v>51.842</v>
       </c>
       <c r="F50">
-        <v>50.784</v>
+        <v>51.842</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -5354,28 +5354,28 @@
         <v>37.42</v>
       </c>
       <c r="M50">
-        <v>2.5544352</v>
+        <v>2.6076526</v>
       </c>
       <c r="N50">
-        <v>34.8655648</v>
+        <v>34.8123474</v>
       </c>
       <c r="O50">
-        <v>8.7163912</v>
+        <v>8.70308685</v>
       </c>
       <c r="P50">
-        <v>26.1491736</v>
+        <v>26.10926055</v>
       </c>
       <c r="Q50">
-        <v>28.9291736</v>
+        <v>28.88926055</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1587135683908158</v>
+        <v>0.1606004929962773</v>
       </c>
       <c r="T50">
-        <v>1.352675454265695</v>
+        <v>1.375280324824948</v>
       </c>
       <c r="U50">
         <v>0.0503</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>14.64903083076838</v>
+        <v>14.35007101789556</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1003915014281014</v>
+        <v>0.1001439472929786</v>
       </c>
       <c r="C51">
-        <v>59.3277412317359</v>
+        <v>58.38500910370423</v>
       </c>
       <c r="D51">
-        <v>111.1697412317359</v>
+        <v>111.2850091037042</v>
       </c>
       <c r="E51">
-        <v>51.842</v>
+        <v>52.9</v>
       </c>
       <c r="F51">
-        <v>51.842</v>
+        <v>52.9</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -5436,28 +5436,28 @@
         <v>37.42</v>
       </c>
       <c r="M51">
-        <v>2.6076526</v>
+        <v>2.66087</v>
       </c>
       <c r="N51">
-        <v>34.8123474</v>
+        <v>34.75913</v>
       </c>
       <c r="O51">
-        <v>8.70308685</v>
+        <v>8.6897825</v>
       </c>
       <c r="P51">
-        <v>26.10926055</v>
+        <v>26.0693475</v>
       </c>
       <c r="Q51">
-        <v>28.88926055</v>
+        <v>28.8493475</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1606004929962773</v>
+        <v>0.1625628945859572</v>
       </c>
       <c r="T51">
-        <v>1.375280324824948</v>
+        <v>1.398789390206571</v>
       </c>
       <c r="U51">
         <v>0.0503</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>14.35007101789556</v>
+        <v>14.06306959753765</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1001439472929786</v>
+        <v>0.09989639315785583</v>
       </c>
       <c r="C52">
-        <v>58.38500910370423</v>
+        <v>57.4425162579258</v>
       </c>
       <c r="D52">
-        <v>111.2850091037042</v>
+        <v>111.4005162579258</v>
       </c>
       <c r="E52">
-        <v>52.9</v>
+        <v>53.958</v>
       </c>
       <c r="F52">
-        <v>52.9</v>
+        <v>53.958</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -5518,28 +5518,28 @@
         <v>37.42</v>
       </c>
       <c r="M52">
-        <v>2.66087</v>
+        <v>2.7140874</v>
       </c>
       <c r="N52">
-        <v>34.75913</v>
+        <v>34.7059126</v>
       </c>
       <c r="O52">
-        <v>8.6897825</v>
+        <v>8.676478150000001</v>
       </c>
       <c r="P52">
-        <v>26.0693475</v>
+        <v>26.02943445</v>
       </c>
       <c r="Q52">
-        <v>28.8493475</v>
+        <v>28.80943445</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1625628945859572</v>
+        <v>0.1646053941997058</v>
       </c>
       <c r="T52">
-        <v>1.398789390206571</v>
+        <v>1.42325800927724</v>
       </c>
       <c r="U52">
         <v>0.0503</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>14.06306959753765</v>
+        <v>13.78732313484083</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09989639315785583</v>
+        <v>0.09964883902273301</v>
       </c>
       <c r="C53">
-        <v>57.4425162579258</v>
+        <v>56.50026344025655</v>
       </c>
       <c r="D53">
-        <v>111.4005162579258</v>
+        <v>111.5162634402566</v>
       </c>
       <c r="E53">
-        <v>53.958</v>
+        <v>55.016</v>
       </c>
       <c r="F53">
-        <v>53.958</v>
+        <v>55.016</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -5600,28 +5600,28 @@
         <v>37.42</v>
       </c>
       <c r="M53">
-        <v>2.7140874</v>
+        <v>2.7673048</v>
       </c>
       <c r="N53">
-        <v>34.7059126</v>
+        <v>34.6526952</v>
       </c>
       <c r="O53">
-        <v>8.676478150000001</v>
+        <v>8.663173800000001</v>
       </c>
       <c r="P53">
-        <v>26.02943445</v>
+        <v>25.9895214</v>
       </c>
       <c r="Q53">
-        <v>28.80943445</v>
+        <v>28.7695214</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1646053941997058</v>
+        <v>0.1667329979640271</v>
       </c>
       <c r="T53">
-        <v>1.42325800927724</v>
+        <v>1.44874615414252</v>
       </c>
       <c r="U53">
         <v>0.0503</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>13.78732313484083</v>
+        <v>13.52218230532466</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09964883902273301</v>
+        <v>0.09940128488761021</v>
       </c>
       <c r="C54">
-        <v>56.50026344025655</v>
+        <v>55.55825139965553</v>
       </c>
       <c r="D54">
-        <v>111.5162634402566</v>
+        <v>111.6322513996555</v>
       </c>
       <c r="E54">
-        <v>55.016</v>
+        <v>56.074</v>
       </c>
       <c r="F54">
-        <v>55.016</v>
+        <v>56.074</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -5682,28 +5682,28 @@
         <v>37.42</v>
       </c>
       <c r="M54">
-        <v>2.7673048</v>
+        <v>2.8205222</v>
       </c>
       <c r="N54">
-        <v>34.6526952</v>
+        <v>34.5994778</v>
       </c>
       <c r="O54">
-        <v>8.663173800000001</v>
+        <v>8.649869450000001</v>
       </c>
       <c r="P54">
-        <v>25.9895214</v>
+        <v>25.94960835</v>
       </c>
       <c r="Q54">
-        <v>28.7695214</v>
+        <v>28.72960835</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1667329979640271</v>
+        <v>0.1689511380587452</v>
       </c>
       <c r="T54">
-        <v>1.44874615414252</v>
+        <v>1.475318900916961</v>
       </c>
       <c r="U54">
         <v>0.0503</v>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>13.52218230532466</v>
+        <v>13.26704679012986</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09940128488761021</v>
+        <v>0.09915373075248743</v>
       </c>
       <c r="C55">
-        <v>55.55825139965553</v>
+        <v>54.61648088820094</v>
       </c>
       <c r="D55">
-        <v>111.6322513996555</v>
+        <v>111.7484808882009</v>
       </c>
       <c r="E55">
-        <v>56.074</v>
+        <v>57.13200000000001</v>
       </c>
       <c r="F55">
-        <v>56.074</v>
+        <v>57.13200000000001</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -5764,28 +5764,28 @@
         <v>37.42</v>
       </c>
       <c r="M55">
-        <v>2.8205222</v>
+        <v>2.8737396</v>
       </c>
       <c r="N55">
-        <v>34.5994778</v>
+        <v>34.5462604</v>
       </c>
       <c r="O55">
-        <v>8.649869450000001</v>
+        <v>8.6365651</v>
       </c>
       <c r="P55">
-        <v>25.94960835</v>
+        <v>25.9096953</v>
       </c>
       <c r="Q55">
-        <v>28.72960835</v>
+        <v>28.6896953</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1689511380587452</v>
+        <v>0.1712657190271466</v>
       </c>
       <c r="T55">
-        <v>1.475318900916961</v>
+        <v>1.503046984507682</v>
       </c>
       <c r="U55">
         <v>0.0503</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>13.26704679012986</v>
+        <v>13.02136073846079</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09915373075248743</v>
+        <v>0.09952492661736463</v>
       </c>
       <c r="C56">
-        <v>54.61648088820094</v>
+        <v>53.38429068650911</v>
       </c>
       <c r="D56">
-        <v>111.7484808882009</v>
+        <v>111.5742906865091</v>
       </c>
       <c r="E56">
-        <v>57.13200000000001</v>
+        <v>58.19</v>
       </c>
       <c r="F56">
-        <v>57.13200000000001</v>
+        <v>58.19</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -5846,45 +5846,45 @@
         <v>37.42</v>
       </c>
       <c r="M56">
-        <v>2.8737396</v>
+        <v>3.014242</v>
       </c>
       <c r="N56">
-        <v>34.5462604</v>
+        <v>34.405758</v>
       </c>
       <c r="O56">
-        <v>8.6365651</v>
+        <v>8.6014395</v>
       </c>
       <c r="P56">
-        <v>25.9096953</v>
+        <v>25.8043185</v>
       </c>
       <c r="Q56">
-        <v>28.6896953</v>
+        <v>28.5843185</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1712657190271466</v>
+        <v>0.1736831702608103</v>
       </c>
       <c r="T56">
-        <v>1.503046984507682</v>
+        <v>1.532007427369102</v>
       </c>
       <c r="U56">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V56">
         <v>0.25</v>
       </c>
       <c r="W56">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y56">
-        <v>13.02136073846079</v>
+        <v>12.41439804766837</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09952492661736463</v>
+        <v>0.09928862248224184</v>
       </c>
       <c r="C57">
-        <v>53.38429068650911</v>
+        <v>52.43711769027274</v>
       </c>
       <c r="D57">
-        <v>111.5742906865091</v>
+        <v>111.6851176902727</v>
       </c>
       <c r="E57">
-        <v>58.19</v>
+        <v>59.248</v>
       </c>
       <c r="F57">
-        <v>58.19</v>
+        <v>59.248</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -5928,28 +5928,28 @@
         <v>37.42</v>
       </c>
       <c r="M57">
-        <v>3.014242</v>
+        <v>3.0690464</v>
       </c>
       <c r="N57">
-        <v>34.405758</v>
+        <v>34.3509536</v>
       </c>
       <c r="O57">
-        <v>8.6014395</v>
+        <v>8.587738400000001</v>
       </c>
       <c r="P57">
-        <v>25.8043185</v>
+        <v>25.7632152</v>
       </c>
       <c r="Q57">
-        <v>28.5843185</v>
+        <v>28.54321520000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1736831702608103</v>
+        <v>0.1762105056414587</v>
       </c>
       <c r="T57">
-        <v>1.532007427369102</v>
+        <v>1.562284253996949</v>
       </c>
       <c r="U57">
         <v>0.0518</v>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>12.41439804766837</v>
+        <v>12.19271236824572</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09928862248224184</v>
+        <v>0.09905231834711903</v>
       </c>
       <c r="C58">
-        <v>52.43711769027274</v>
+        <v>51.49016508239247</v>
       </c>
       <c r="D58">
-        <v>111.6851176902727</v>
+        <v>111.7961650823925</v>
       </c>
       <c r="E58">
-        <v>59.248</v>
+        <v>60.306</v>
       </c>
       <c r="F58">
-        <v>59.248</v>
+        <v>60.306</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -6010,28 +6010,28 @@
         <v>37.42</v>
       </c>
       <c r="M58">
-        <v>3.0690464</v>
+        <v>3.1238508</v>
       </c>
       <c r="N58">
-        <v>34.3509536</v>
+        <v>34.2961492</v>
       </c>
       <c r="O58">
-        <v>8.587738400000001</v>
+        <v>8.574037300000001</v>
       </c>
       <c r="P58">
-        <v>25.7632152</v>
+        <v>25.7221119</v>
       </c>
       <c r="Q58">
-        <v>28.54321520000001</v>
+        <v>28.5021119</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1762105056414587</v>
+        <v>0.178855391504928</v>
       </c>
       <c r="T58">
-        <v>1.562284253996949</v>
+        <v>1.593969305119116</v>
       </c>
       <c r="U58">
         <v>0.0518</v>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>12.19271236824572</v>
+        <v>11.97880513371509</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09905231834711903</v>
+        <v>0.09881601421199625</v>
       </c>
       <c r="C59">
-        <v>51.49016508239247</v>
+        <v>50.5434335209124</v>
       </c>
       <c r="D59">
-        <v>111.7961650823925</v>
+        <v>111.9074335209124</v>
       </c>
       <c r="E59">
-        <v>60.306</v>
+        <v>61.364</v>
       </c>
       <c r="F59">
-        <v>60.306</v>
+        <v>61.364</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -6092,28 +6092,28 @@
         <v>37.42</v>
       </c>
       <c r="M59">
-        <v>3.1238508</v>
+        <v>3.1786552</v>
       </c>
       <c r="N59">
-        <v>34.2961492</v>
+        <v>34.2413448</v>
       </c>
       <c r="O59">
-        <v>8.574037300000001</v>
+        <v>8.5603362</v>
       </c>
       <c r="P59">
-        <v>25.7221119</v>
+        <v>25.6810086</v>
       </c>
       <c r="Q59">
-        <v>28.5021119</v>
+        <v>28.4610086</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.178855391504928</v>
+        <v>0.1816262243142768</v>
       </c>
       <c r="T59">
-        <v>1.593969305119116</v>
+        <v>1.627163168199481</v>
       </c>
       <c r="U59">
         <v>0.0518</v>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>11.97880513371509</v>
+        <v>11.77227401072</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09881601421199625</v>
+        <v>0.09857971007687345</v>
       </c>
       <c r="C60">
-        <v>50.54343352091241</v>
+        <v>49.59692366649895</v>
       </c>
       <c r="D60">
-        <v>111.9074335209124</v>
+        <v>112.0189236664989</v>
       </c>
       <c r="E60">
-        <v>61.364</v>
+        <v>62.422</v>
       </c>
       <c r="F60">
-        <v>61.364</v>
+        <v>62.422</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -6174,28 +6174,28 @@
         <v>37.42</v>
       </c>
       <c r="M60">
-        <v>3.1786552</v>
+        <v>3.2334596</v>
       </c>
       <c r="N60">
-        <v>34.2413448</v>
+        <v>34.1865404</v>
       </c>
       <c r="O60">
-        <v>8.5603362</v>
+        <v>8.5466351</v>
       </c>
       <c r="P60">
-        <v>25.6810086</v>
+        <v>25.6399053</v>
       </c>
       <c r="Q60">
-        <v>28.4610086</v>
+        <v>28.4199053</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1816262243142768</v>
+        <v>0.1845322196996913</v>
       </c>
       <c r="T60">
-        <v>1.62716316819948</v>
+        <v>1.661976244113033</v>
       </c>
       <c r="U60">
         <v>0.0518</v>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>11.77227401072001</v>
+        <v>11.5727439427417</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09857971007687345</v>
+        <v>0.09834340594175066</v>
       </c>
       <c r="C61">
-        <v>49.59692366649895</v>
+        <v>48.65063618245401</v>
       </c>
       <c r="D61">
-        <v>112.0189236664989</v>
+        <v>112.130636182454</v>
       </c>
       <c r="E61">
-        <v>62.422</v>
+        <v>63.48</v>
       </c>
       <c r="F61">
-        <v>62.422</v>
+        <v>63.48</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -6256,28 +6256,28 @@
         <v>37.42</v>
       </c>
       <c r="M61">
-        <v>3.2334596</v>
+        <v>3.288264</v>
       </c>
       <c r="N61">
-        <v>34.1865404</v>
+        <v>34.131736</v>
       </c>
       <c r="O61">
-        <v>8.5466351</v>
+        <v>8.532934000000001</v>
       </c>
       <c r="P61">
-        <v>25.6399053</v>
+        <v>25.598802</v>
       </c>
       <c r="Q61">
-        <v>28.4199053</v>
+        <v>28.378802</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1845322196996913</v>
+        <v>0.1875835148543766</v>
       </c>
       <c r="T61">
-        <v>1.661976244113033</v>
+        <v>1.698529973822265</v>
       </c>
       <c r="U61">
         <v>0.0518</v>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>11.5727439427417</v>
+        <v>11.37986487702934</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09834340594175066</v>
+        <v>0.09810710180662788</v>
       </c>
       <c r="C62">
-        <v>48.65063618245401</v>
+        <v>47.70457173472803</v>
       </c>
       <c r="D62">
-        <v>112.130636182454</v>
+        <v>112.242571734728</v>
       </c>
       <c r="E62">
-        <v>63.48</v>
+        <v>64.538</v>
       </c>
       <c r="F62">
-        <v>63.48</v>
+        <v>64.538</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -6338,28 +6338,28 @@
         <v>37.42</v>
       </c>
       <c r="M62">
-        <v>3.288264</v>
+        <v>3.3430684</v>
       </c>
       <c r="N62">
-        <v>34.131736</v>
+        <v>34.0769316</v>
       </c>
       <c r="O62">
-        <v>8.532934000000001</v>
+        <v>8.5192329</v>
       </c>
       <c r="P62">
-        <v>25.598802</v>
+        <v>25.5576987</v>
       </c>
       <c r="Q62">
-        <v>28.378802</v>
+        <v>28.3376987</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1875835148543766</v>
+        <v>0.1907912866836612</v>
       </c>
       <c r="T62">
-        <v>1.698529973822265</v>
+        <v>1.736958253772995</v>
       </c>
       <c r="U62">
         <v>0.0518</v>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>11.37986487702934</v>
+        <v>11.19330971511082</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09810710180662788</v>
+        <v>0.09787079767150507</v>
       </c>
       <c r="C63">
-        <v>47.70457173472803</v>
+        <v>46.75873099193333</v>
       </c>
       <c r="D63">
-        <v>112.242571734728</v>
+        <v>112.3547309919333</v>
       </c>
       <c r="E63">
-        <v>64.538</v>
+        <v>65.596</v>
       </c>
       <c r="F63">
-        <v>64.538</v>
+        <v>65.596</v>
       </c>
       <c r="G63">
         <v>0</v>
@@ -6420,28 +6420,28 @@
         <v>37.42</v>
       </c>
       <c r="M63">
-        <v>3.3430684</v>
+        <v>3.3978728</v>
       </c>
       <c r="N63">
-        <v>34.0769316</v>
+        <v>34.0221272</v>
       </c>
       <c r="O63">
-        <v>8.5192329</v>
+        <v>8.5055318</v>
       </c>
       <c r="P63">
-        <v>25.5576987</v>
+        <v>25.5165954</v>
       </c>
       <c r="Q63">
-        <v>28.3376987</v>
+        <v>28.2965954</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1907912866836612</v>
+        <v>0.1941678886092239</v>
       </c>
       <c r="T63">
-        <v>1.736958253772995</v>
+        <v>1.777409074773763</v>
       </c>
       <c r="U63">
         <v>0.0518</v>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>11.19330971511082</v>
+        <v>11.0127724616413</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09787079767150507</v>
+        <v>0.09763449353638227</v>
       </c>
       <c r="C64">
-        <v>46.75873099193333</v>
+        <v>45.81311462535737</v>
       </c>
       <c r="D64">
-        <v>112.3547309919333</v>
+        <v>112.4671146253574</v>
       </c>
       <c r="E64">
-        <v>65.596</v>
+        <v>66.654</v>
       </c>
       <c r="F64">
-        <v>65.596</v>
+        <v>66.654</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -6502,28 +6502,28 @@
         <v>37.42</v>
       </c>
       <c r="M64">
-        <v>3.3978728</v>
+        <v>3.4526772</v>
       </c>
       <c r="N64">
-        <v>34.0221272</v>
+        <v>33.96732280000001</v>
       </c>
       <c r="O64">
-        <v>8.5055318</v>
+        <v>8.491830700000001</v>
       </c>
       <c r="P64">
-        <v>25.5165954</v>
+        <v>25.4754921</v>
       </c>
       <c r="Q64">
-        <v>28.2965954</v>
+        <v>28.2554921</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1941678886092239</v>
+        <v>0.1977270095577899</v>
       </c>
       <c r="T64">
-        <v>1.777409074773763</v>
+        <v>1.820046426639438</v>
       </c>
       <c r="U64">
         <v>0.0518</v>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>11.0127724616413</v>
+        <v>10.83796654955175</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09763449353638227</v>
+        <v>0.09739818940125948</v>
       </c>
       <c r="C65">
-        <v>45.81311462535737</v>
+        <v>44.86772330897603</v>
       </c>
       <c r="D65">
-        <v>112.4671146253574</v>
+        <v>112.579723308976</v>
       </c>
       <c r="E65">
-        <v>66.654</v>
+        <v>67.712</v>
       </c>
       <c r="F65">
-        <v>66.654</v>
+        <v>67.712</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -6584,28 +6584,28 @@
         <v>37.42</v>
       </c>
       <c r="M65">
-        <v>3.4526772</v>
+        <v>3.5074816</v>
       </c>
       <c r="N65">
-        <v>33.96732280000001</v>
+        <v>33.9125184</v>
       </c>
       <c r="O65">
-        <v>8.491830700000001</v>
+        <v>8.478129600000001</v>
       </c>
       <c r="P65">
-        <v>25.4754921</v>
+        <v>25.4343888</v>
       </c>
       <c r="Q65">
-        <v>28.2554921</v>
+        <v>28.2143888</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1977270095577899</v>
+        <v>0.201483859447943</v>
       </c>
       <c r="T65">
-        <v>1.820046426639438</v>
+        <v>1.865052520275428</v>
       </c>
       <c r="U65">
         <v>0.0518</v>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>10.83796654955175</v>
+        <v>10.66862332221501</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09739818940125948</v>
+        <v>0.09716188526613667</v>
       </c>
       <c r="C66">
-        <v>44.86772330897603</v>
+        <v>43.92255771946735</v>
       </c>
       <c r="D66">
-        <v>112.579723308976</v>
+        <v>112.6925577194673</v>
       </c>
       <c r="E66">
-        <v>67.712</v>
+        <v>68.77</v>
       </c>
       <c r="F66">
-        <v>67.712</v>
+        <v>68.77</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -6666,28 +6666,28 @@
         <v>37.42</v>
       </c>
       <c r="M66">
-        <v>3.5074816</v>
+        <v>3.562286</v>
       </c>
       <c r="N66">
-        <v>33.9125184</v>
+        <v>33.857714</v>
       </c>
       <c r="O66">
-        <v>8.478129600000001</v>
+        <v>8.4644285</v>
       </c>
       <c r="P66">
-        <v>25.4343888</v>
+        <v>25.3932855</v>
       </c>
       <c r="Q66">
-        <v>28.2143888</v>
+        <v>28.1732855</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.201483859447943</v>
+        <v>0.2054553864746762</v>
       </c>
       <c r="T66">
-        <v>1.865052520275428</v>
+        <v>1.912630390690617</v>
       </c>
       <c r="U66">
         <v>0.0518</v>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>10.66862332221501</v>
+        <v>10.50449065571939</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09716188526613667</v>
+        <v>0.09692558113101388</v>
       </c>
       <c r="C67">
-        <v>43.92255771946735</v>
+        <v>42.97761853622482</v>
       </c>
       <c r="D67">
-        <v>112.6925577194673</v>
+        <v>112.8056185362248</v>
       </c>
       <c r="E67">
-        <v>68.77</v>
+        <v>69.828</v>
       </c>
       <c r="F67">
-        <v>68.77</v>
+        <v>69.828</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -6748,28 +6748,28 @@
         <v>37.42</v>
       </c>
       <c r="M67">
-        <v>3.562286</v>
+        <v>3.6170904</v>
       </c>
       <c r="N67">
-        <v>33.857714</v>
+        <v>33.8029096</v>
       </c>
       <c r="O67">
-        <v>8.4644285</v>
+        <v>8.4507274</v>
       </c>
       <c r="P67">
-        <v>25.3932855</v>
+        <v>25.3521822</v>
       </c>
       <c r="Q67">
-        <v>28.1732855</v>
+        <v>28.1321822</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2054553864746762</v>
+        <v>0.2096605327382761</v>
       </c>
       <c r="T67">
-        <v>1.912630390690617</v>
+        <v>1.963006959365524</v>
       </c>
       <c r="U67">
         <v>0.0518</v>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>10.50449065571939</v>
+        <v>10.34533170639031</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09692558113101388</v>
+        <v>0.09668927699589108</v>
       </c>
       <c r="C68">
-        <v>42.97761853622482</v>
+        <v>42.03290644137118</v>
       </c>
       <c r="D68">
-        <v>112.8056185362248</v>
+        <v>112.9189064413712</v>
       </c>
       <c r="E68">
-        <v>69.828</v>
+        <v>70.886</v>
       </c>
       <c r="F68">
-        <v>69.828</v>
+        <v>70.886</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -6830,28 +6830,28 @@
         <v>37.42</v>
       </c>
       <c r="M68">
-        <v>3.6170904</v>
+        <v>3.6718948</v>
       </c>
       <c r="N68">
-        <v>33.8029096</v>
+        <v>33.7481052</v>
       </c>
       <c r="O68">
-        <v>8.4507274</v>
+        <v>8.437026300000001</v>
       </c>
       <c r="P68">
-        <v>25.3521822</v>
+        <v>25.31107890000001</v>
       </c>
       <c r="Q68">
-        <v>28.1321822</v>
+        <v>28.09107890000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2096605327382761</v>
+        <v>0.2141205363511851</v>
       </c>
       <c r="T68">
-        <v>1.963006959365524</v>
+        <v>2.016436653414667</v>
       </c>
       <c r="U68">
         <v>0.0518</v>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>10.34533170639031</v>
+        <v>10.19092377047404</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09668927699589108</v>
+        <v>0.09645297286076829</v>
       </c>
       <c r="C69">
-        <v>42.03290644137118</v>
+        <v>41.08842211977201</v>
       </c>
       <c r="D69">
-        <v>112.9189064413712</v>
+        <v>113.032422119772</v>
       </c>
       <c r="E69">
-        <v>70.886</v>
+        <v>71.944</v>
       </c>
       <c r="F69">
-        <v>70.886</v>
+        <v>71.944</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -6912,28 +6912,28 @@
         <v>37.42</v>
       </c>
       <c r="M69">
-        <v>3.6718948</v>
+        <v>3.7266992</v>
       </c>
       <c r="N69">
-        <v>33.7481052</v>
+        <v>33.6933008</v>
       </c>
       <c r="O69">
-        <v>8.437026300000001</v>
+        <v>8.423325200000001</v>
       </c>
       <c r="P69">
-        <v>25.31107890000001</v>
+        <v>25.2699756</v>
       </c>
       <c r="Q69">
-        <v>28.09107890000001</v>
+        <v>28.0499756</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2141205363511851</v>
+        <v>0.2188592901899009</v>
       </c>
       <c r="T69">
-        <v>2.016436653414667</v>
+        <v>2.073205703341882</v>
       </c>
       <c r="U69">
         <v>0.0518</v>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>10.19092377047404</v>
+        <v>10.04105724443765</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09645297286076829</v>
+        <v>0.09621666872564549</v>
       </c>
       <c r="C70">
-        <v>41.08842211977201</v>
+        <v>40.14416625904968</v>
       </c>
       <c r="D70">
-        <v>113.032422119772</v>
+        <v>113.1461662590497</v>
       </c>
       <c r="E70">
-        <v>71.944</v>
+        <v>73.00200000000001</v>
       </c>
       <c r="F70">
-        <v>71.944</v>
+        <v>73.00200000000001</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -6994,28 +6994,28 @@
         <v>37.42</v>
       </c>
       <c r="M70">
-        <v>3.7266992</v>
+        <v>3.7815036</v>
       </c>
       <c r="N70">
-        <v>33.6933008</v>
+        <v>33.6384964</v>
       </c>
       <c r="O70">
-        <v>8.423325200000001</v>
+        <v>8.4096241</v>
       </c>
       <c r="P70">
-        <v>25.2699756</v>
+        <v>25.2288723</v>
       </c>
       <c r="Q70">
-        <v>28.0499756</v>
+        <v>28.0088723</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2188592901899009</v>
+        <v>0.2239037700827274</v>
       </c>
       <c r="T70">
-        <v>2.073205703341882</v>
+        <v>2.13363727261924</v>
       </c>
       <c r="U70">
         <v>0.0518</v>
@@ -7032,7 +7032,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>10.04105724443765</v>
+        <v>9.895534675677686</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09621666872564549</v>
+        <v>0.09687286459052269</v>
       </c>
       <c r="C71">
-        <v>40.14416625904968</v>
+        <v>38.77087196819419</v>
       </c>
       <c r="D71">
-        <v>113.1461662590497</v>
+        <v>112.8308719681942</v>
       </c>
       <c r="E71">
-        <v>73.00200000000001</v>
+        <v>74.06</v>
       </c>
       <c r="F71">
-        <v>73.00200000000001</v>
+        <v>74.06</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -7076,45 +7076,45 @@
         <v>37.42</v>
       </c>
       <c r="M71">
-        <v>3.7815036</v>
+        <v>3.96221</v>
       </c>
       <c r="N71">
-        <v>33.6384964</v>
+        <v>33.45779</v>
       </c>
       <c r="O71">
-        <v>8.4096241</v>
+        <v>8.364447500000001</v>
       </c>
       <c r="P71">
-        <v>25.2288723</v>
+        <v>25.0933425</v>
       </c>
       <c r="Q71">
-        <v>28.0088723</v>
+        <v>27.8733425</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2239037700827274</v>
+        <v>0.2292845486350757</v>
       </c>
       <c r="T71">
-        <v>2.13363727261924</v>
+        <v>2.198097613181754</v>
       </c>
       <c r="U71">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V71">
         <v>0.25</v>
       </c>
       <c r="W71">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>9.895534675677686</v>
+        <v>9.444224309160797</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09687286459052269</v>
+        <v>0.09664931045539991</v>
       </c>
       <c r="C72">
-        <v>38.77087196819419</v>
+        <v>37.82008952798402</v>
       </c>
       <c r="D72">
-        <v>112.8308719681942</v>
+        <v>112.938089527984</v>
       </c>
       <c r="E72">
-        <v>74.06</v>
+        <v>75.11800000000001</v>
       </c>
       <c r="F72">
-        <v>74.06</v>
+        <v>75.11800000000001</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -7158,28 +7158,28 @@
         <v>37.42</v>
       </c>
       <c r="M72">
-        <v>3.96221</v>
+        <v>4.018813000000001</v>
       </c>
       <c r="N72">
-        <v>33.45779</v>
+        <v>33.401187</v>
       </c>
       <c r="O72">
-        <v>8.364447500000001</v>
+        <v>8.35029675</v>
       </c>
       <c r="P72">
-        <v>25.0933425</v>
+        <v>25.05089025</v>
       </c>
       <c r="Q72">
-        <v>27.8733425</v>
+        <v>27.83089025</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2292845486350757</v>
+        <v>0.235036415363448</v>
       </c>
       <c r="T72">
-        <v>2.198097613181754</v>
+        <v>2.267003494472719</v>
       </c>
       <c r="U72">
         <v>0.0535</v>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>9.444224309160797</v>
+        <v>9.311207065369798</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.0966493104553999</v>
+        <v>0.09642575632027711</v>
       </c>
       <c r="C73">
-        <v>37.82008952798404</v>
+        <v>36.86951104860515</v>
       </c>
       <c r="D73">
-        <v>112.938089527984</v>
+        <v>113.0455110486051</v>
       </c>
       <c r="E73">
-        <v>75.11799999999999</v>
+        <v>76.176</v>
       </c>
       <c r="F73">
-        <v>75.11799999999999</v>
+        <v>76.176</v>
       </c>
       <c r="G73">
         <v>0</v>
@@ -7240,28 +7240,28 @@
         <v>37.42</v>
       </c>
       <c r="M73">
-        <v>4.018813</v>
+        <v>4.075416</v>
       </c>
       <c r="N73">
-        <v>33.401187</v>
+        <v>33.344584</v>
       </c>
       <c r="O73">
-        <v>8.35029675</v>
+        <v>8.336146000000001</v>
       </c>
       <c r="P73">
-        <v>25.05089025</v>
+        <v>25.00843800000001</v>
       </c>
       <c r="Q73">
-        <v>27.83089025</v>
+        <v>27.78843800000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2350364153634479</v>
+        <v>0.2411991297152754</v>
       </c>
       <c r="T73">
-        <v>2.267003494472718</v>
+        <v>2.340831224427323</v>
       </c>
       <c r="U73">
         <v>0.0535</v>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>9.3112070653698</v>
+        <v>9.181884745017443</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09642575632027711</v>
+        <v>0.09620220218515431</v>
       </c>
       <c r="C74">
-        <v>36.86951104860515</v>
+        <v>35.91913711260611</v>
       </c>
       <c r="D74">
-        <v>113.0455110486051</v>
+        <v>113.1531371126061</v>
       </c>
       <c r="E74">
-        <v>76.176</v>
+        <v>77.23399999999999</v>
       </c>
       <c r="F74">
-        <v>76.176</v>
+        <v>77.23399999999999</v>
       </c>
       <c r="G74">
         <v>0</v>
@@ -7322,28 +7322,28 @@
         <v>37.42</v>
       </c>
       <c r="M74">
-        <v>4.075416</v>
+        <v>4.132019</v>
       </c>
       <c r="N74">
-        <v>33.344584</v>
+        <v>33.287981</v>
       </c>
       <c r="O74">
-        <v>8.336146000000001</v>
+        <v>8.321995250000001</v>
       </c>
       <c r="P74">
-        <v>25.00843800000001</v>
+        <v>24.96598575</v>
       </c>
       <c r="Q74">
-        <v>27.78843800000001</v>
+        <v>27.74598575</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2411991297152754</v>
+        <v>0.2478183414264974</v>
       </c>
       <c r="T74">
-        <v>2.340831224427323</v>
+        <v>2.420127675119305</v>
       </c>
       <c r="U74">
         <v>0.0535</v>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>9.181884745017443</v>
+        <v>9.056105501935011</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09620220218515431</v>
+        <v>0.09597864805003149</v>
       </c>
       <c r="C75">
-        <v>35.91913711260611</v>
+        <v>34.96896830475615</v>
       </c>
       <c r="D75">
-        <v>113.1531371126061</v>
+        <v>113.2609683047561</v>
       </c>
       <c r="E75">
-        <v>77.23399999999999</v>
+        <v>78.292</v>
       </c>
       <c r="F75">
-        <v>77.23399999999999</v>
+        <v>78.292</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -7404,28 +7404,28 @@
         <v>37.42</v>
       </c>
       <c r="M75">
-        <v>4.132019</v>
+        <v>4.188622</v>
       </c>
       <c r="N75">
-        <v>33.287981</v>
+        <v>33.231378</v>
       </c>
       <c r="O75">
-        <v>8.321995250000001</v>
+        <v>8.3078445</v>
       </c>
       <c r="P75">
-        <v>24.96598575</v>
+        <v>24.9235335</v>
       </c>
       <c r="Q75">
-        <v>27.74598575</v>
+        <v>27.7035335</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2478183414264974</v>
+        <v>0.2549467232693519</v>
       </c>
       <c r="T75">
-        <v>2.420127675119305</v>
+        <v>2.505523852787594</v>
       </c>
       <c r="U75">
         <v>0.0535</v>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>9.056105501935011</v>
+        <v>8.933725697854808</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09597864805003149</v>
+        <v>0.09575509391490872</v>
       </c>
       <c r="C76">
-        <v>34.96896830475615</v>
+        <v>34.01900521205559</v>
       </c>
       <c r="D76">
-        <v>113.2609683047561</v>
+        <v>113.3690052120556</v>
       </c>
       <c r="E76">
-        <v>78.292</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="F76">
-        <v>78.292</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -7486,28 +7486,28 @@
         <v>37.42</v>
       </c>
       <c r="M76">
-        <v>4.188622</v>
+        <v>4.245225</v>
       </c>
       <c r="N76">
-        <v>33.231378</v>
+        <v>33.174775</v>
       </c>
       <c r="O76">
-        <v>8.3078445</v>
+        <v>8.293693750000001</v>
       </c>
       <c r="P76">
-        <v>24.9235335</v>
+        <v>24.88108125</v>
       </c>
       <c r="Q76">
-        <v>27.7035335</v>
+        <v>27.66108125</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2549467232693519</v>
+        <v>0.2626453756596349</v>
       </c>
       <c r="T76">
-        <v>2.505523852787594</v>
+        <v>2.597751724669346</v>
       </c>
       <c r="U76">
         <v>0.0535</v>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>8.933725697854808</v>
+        <v>8.814609355216746</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09575509391490872</v>
+        <v>0.0955315397797859</v>
       </c>
       <c r="C77">
-        <v>34.01900521205559</v>
+        <v>33.06924842374671</v>
       </c>
       <c r="D77">
-        <v>113.3690052120556</v>
+        <v>113.4772484237467</v>
       </c>
       <c r="E77">
-        <v>79.34999999999999</v>
+        <v>80.408</v>
       </c>
       <c r="F77">
-        <v>79.34999999999999</v>
+        <v>80.408</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -7568,28 +7568,28 @@
         <v>37.42</v>
       </c>
       <c r="M77">
-        <v>4.245225</v>
+        <v>4.301828</v>
       </c>
       <c r="N77">
-        <v>33.174775</v>
+        <v>33.118172</v>
       </c>
       <c r="O77">
-        <v>8.293693750000001</v>
+        <v>8.279543</v>
       </c>
       <c r="P77">
-        <v>24.88108125</v>
+        <v>24.838629</v>
       </c>
       <c r="Q77">
-        <v>27.66108125</v>
+        <v>27.618629</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2626453756596349</v>
+        <v>0.2709855824157746</v>
       </c>
       <c r="T77">
-        <v>2.597751724669346</v>
+        <v>2.697665252541244</v>
       </c>
       <c r="U77">
         <v>0.0535</v>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>8.814609355216746</v>
+        <v>8.69862765317442</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.0955315397797859</v>
+        <v>0.09530798564466311</v>
       </c>
       <c r="C78">
-        <v>33.06924842374671</v>
+        <v>32.11969853132429</v>
       </c>
       <c r="D78">
-        <v>113.4772484237467</v>
+        <v>113.5856985313243</v>
       </c>
       <c r="E78">
-        <v>80.408</v>
+        <v>81.46599999999999</v>
       </c>
       <c r="F78">
-        <v>80.408</v>
+        <v>81.46599999999999</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -7650,28 +7650,28 @@
         <v>37.42</v>
       </c>
       <c r="M78">
-        <v>4.301828</v>
+        <v>4.358431</v>
       </c>
       <c r="N78">
-        <v>33.118172</v>
+        <v>33.06156900000001</v>
       </c>
       <c r="O78">
-        <v>8.279543</v>
+        <v>8.265392250000001</v>
       </c>
       <c r="P78">
-        <v>24.838629</v>
+        <v>24.79617675</v>
       </c>
       <c r="Q78">
-        <v>27.618629</v>
+        <v>27.57617675000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2709855824157746</v>
+        <v>0.2800510245420136</v>
       </c>
       <c r="T78">
-        <v>2.697665252541244</v>
+        <v>2.806266913271568</v>
       </c>
       <c r="U78">
         <v>0.0535</v>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>8.69862765317442</v>
+        <v>8.585658462873454</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.09530798564466311</v>
+        <v>0.09508443150954032</v>
       </c>
       <c r="C79">
-        <v>32.11969853132429</v>
+        <v>31.17035612854642</v>
       </c>
       <c r="D79">
-        <v>113.5856985313243</v>
+        <v>113.6943561285464</v>
       </c>
       <c r="E79">
-        <v>81.46599999999999</v>
+        <v>82.524</v>
       </c>
       <c r="F79">
-        <v>81.46599999999999</v>
+        <v>82.524</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -7732,28 +7732,28 @@
         <v>37.42</v>
       </c>
       <c r="M79">
-        <v>4.358431</v>
+        <v>4.415034</v>
       </c>
       <c r="N79">
-        <v>33.06156900000001</v>
+        <v>33.004966</v>
       </c>
       <c r="O79">
-        <v>8.265392250000001</v>
+        <v>8.251241500000001</v>
       </c>
       <c r="P79">
-        <v>24.79617675</v>
+        <v>24.7537245</v>
       </c>
       <c r="Q79">
-        <v>27.57617675000001</v>
+        <v>27.53372450000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2800510245420136</v>
+        <v>0.2899405977706379</v>
       </c>
       <c r="T79">
-        <v>2.806266913271568</v>
+        <v>2.924741452250103</v>
       </c>
       <c r="U79">
         <v>0.0535</v>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>8.585658462873454</v>
+        <v>8.475585918477638</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09508443150954032</v>
+        <v>0.09486087737441753</v>
       </c>
       <c r="C80">
-        <v>31.17035612854642</v>
+        <v>30.22122181144537</v>
       </c>
       <c r="D80">
-        <v>113.6943561285464</v>
+        <v>113.8032218114454</v>
       </c>
       <c r="E80">
-        <v>82.524</v>
+        <v>83.58200000000001</v>
       </c>
       <c r="F80">
-        <v>82.524</v>
+        <v>83.58200000000001</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -7814,28 +7814,28 @@
         <v>37.42</v>
       </c>
       <c r="M80">
-        <v>4.415034</v>
+        <v>4.471637</v>
       </c>
       <c r="N80">
-        <v>33.004966</v>
+        <v>32.948363</v>
       </c>
       <c r="O80">
-        <v>8.251241500000001</v>
+        <v>8.23709075</v>
       </c>
       <c r="P80">
-        <v>24.7537245</v>
+        <v>24.71127225</v>
       </c>
       <c r="Q80">
-        <v>27.53372450000001</v>
+        <v>27.49127225</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2899405977706379</v>
+        <v>0.300772035116274</v>
       </c>
       <c r="T80">
-        <v>2.924741452250103</v>
+        <v>3.054499280655165</v>
       </c>
       <c r="U80">
         <v>0.0535</v>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>8.475585918477638</v>
+        <v>8.36830002077539</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.09486087737441753</v>
+        <v>0.09463732323929475</v>
       </c>
       <c r="C81">
-        <v>30.22122181144537</v>
+        <v>29.27229617833852</v>
       </c>
       <c r="D81">
-        <v>113.8032218114454</v>
+        <v>113.9122961783385</v>
       </c>
       <c r="E81">
-        <v>83.58200000000001</v>
+        <v>84.64</v>
       </c>
       <c r="F81">
-        <v>83.58200000000001</v>
+        <v>84.64</v>
       </c>
       <c r="G81">
         <v>0</v>
@@ -7896,28 +7896,28 @@
         <v>37.42</v>
       </c>
       <c r="M81">
-        <v>4.471637</v>
+        <v>4.52824</v>
       </c>
       <c r="N81">
-        <v>32.948363</v>
+        <v>32.89176</v>
       </c>
       <c r="O81">
-        <v>8.23709075</v>
+        <v>8.222940000000001</v>
       </c>
       <c r="P81">
-        <v>24.71127225</v>
+        <v>24.66882</v>
       </c>
       <c r="Q81">
-        <v>27.49127225</v>
+        <v>27.44882</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.300772035116274</v>
+        <v>0.3126866161964738</v>
       </c>
       <c r="T81">
-        <v>3.054499280655165</v>
+        <v>3.197232891900734</v>
       </c>
       <c r="U81">
         <v>0.0535</v>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>8.36830002077539</v>
+        <v>8.263696270515698</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09463732323929475</v>
+        <v>0.09441376910417194</v>
       </c>
       <c r="C82">
-        <v>29.27229617833852</v>
+        <v>28.3235798298392</v>
       </c>
       <c r="D82">
-        <v>113.9122961783385</v>
+        <v>114.0215798298392</v>
       </c>
       <c r="E82">
-        <v>84.64</v>
+        <v>85.69800000000001</v>
       </c>
       <c r="F82">
-        <v>84.64</v>
+        <v>85.69800000000001</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -7978,28 +7978,28 @@
         <v>37.42</v>
       </c>
       <c r="M82">
-        <v>4.52824</v>
+        <v>4.584843</v>
       </c>
       <c r="N82">
-        <v>32.89176</v>
+        <v>32.835157</v>
       </c>
       <c r="O82">
-        <v>8.222940000000001</v>
+        <v>8.208789250000001</v>
       </c>
       <c r="P82">
-        <v>24.66882</v>
+        <v>24.62636775</v>
       </c>
       <c r="Q82">
-        <v>27.44882</v>
+        <v>27.40636775</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3126866161964738</v>
+        <v>0.3258553637061682</v>
       </c>
       <c r="T82">
-        <v>3.197232891900734</v>
+        <v>3.354991093803731</v>
       </c>
       <c r="U82">
         <v>0.0535</v>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>8.263696270515698</v>
+        <v>8.161675328904392</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.09441376910417194</v>
+        <v>0.09419021496904914</v>
       </c>
       <c r="C83">
-        <v>28.3235798298392</v>
+        <v>27.37507336886782</v>
       </c>
       <c r="D83">
-        <v>114.0215798298392</v>
+        <v>114.1310733688678</v>
       </c>
       <c r="E83">
-        <v>85.69800000000001</v>
+        <v>86.756</v>
       </c>
       <c r="F83">
-        <v>85.69800000000001</v>
+        <v>86.756</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -8060,28 +8060,28 @@
         <v>37.42</v>
       </c>
       <c r="M83">
-        <v>4.584843</v>
+        <v>4.641446</v>
       </c>
       <c r="N83">
-        <v>32.835157</v>
+        <v>32.778554</v>
       </c>
       <c r="O83">
-        <v>8.208789250000001</v>
+        <v>8.1946385</v>
       </c>
       <c r="P83">
-        <v>24.62636775</v>
+        <v>24.5839155</v>
       </c>
       <c r="Q83">
-        <v>27.40636775</v>
+        <v>27.3639155</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3258553637061682</v>
+        <v>0.3404873053836064</v>
       </c>
       <c r="T83">
-        <v>3.354991093803731</v>
+        <v>3.530277984807061</v>
       </c>
       <c r="U83">
         <v>0.0535</v>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>8.161675328904392</v>
+        <v>8.062142702942143</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09419021496904914</v>
+        <v>0.09396666083392635</v>
       </c>
       <c r="C84">
-        <v>27.37507336886782</v>
+        <v>26.4267774006629</v>
       </c>
       <c r="D84">
-        <v>114.1310733688678</v>
+        <v>114.2407774006629</v>
       </c>
       <c r="E84">
-        <v>86.756</v>
+        <v>87.81400000000001</v>
       </c>
       <c r="F84">
-        <v>86.756</v>
+        <v>87.81400000000001</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -8142,28 +8142,28 @@
         <v>37.42</v>
       </c>
       <c r="M84">
-        <v>4.641446</v>
+        <v>4.698049</v>
       </c>
       <c r="N84">
-        <v>32.778554</v>
+        <v>32.721951</v>
       </c>
       <c r="O84">
-        <v>8.1946385</v>
+        <v>8.180487750000001</v>
       </c>
       <c r="P84">
-        <v>24.5839155</v>
+        <v>24.54146325</v>
       </c>
       <c r="Q84">
-        <v>27.3639155</v>
+        <v>27.32146325</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3404873053836064</v>
+        <v>0.3568406519642728</v>
       </c>
       <c r="T84">
-        <v>3.530277984807061</v>
+        <v>3.726186862987253</v>
       </c>
       <c r="U84">
         <v>0.0535</v>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>8.062142702942143</v>
+        <v>7.965008453509106</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09396666083392635</v>
+        <v>0.09374310669880356</v>
       </c>
       <c r="C85">
-        <v>26.4267774006629</v>
+        <v>25.47869253279229</v>
       </c>
       <c r="D85">
-        <v>114.2407774006629</v>
+        <v>114.3506925327923</v>
       </c>
       <c r="E85">
-        <v>87.81400000000001</v>
+        <v>88.872</v>
       </c>
       <c r="F85">
-        <v>87.81400000000001</v>
+        <v>88.872</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -8224,28 +8224,28 @@
         <v>37.42</v>
       </c>
       <c r="M85">
-        <v>4.698049</v>
+        <v>4.754652</v>
       </c>
       <c r="N85">
-        <v>32.721951</v>
+        <v>32.665348</v>
       </c>
       <c r="O85">
-        <v>8.180487750000001</v>
+        <v>8.166337</v>
       </c>
       <c r="P85">
-        <v>24.54146325</v>
+        <v>24.499011</v>
       </c>
       <c r="Q85">
-        <v>27.32146325</v>
+        <v>27.279011</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3568406519642728</v>
+        <v>0.3752381668675224</v>
       </c>
       <c r="T85">
-        <v>3.726186862987253</v>
+        <v>3.94658435093997</v>
       </c>
       <c r="U85">
         <v>0.0535</v>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>7.965008453509106</v>
+        <v>7.870186924300664</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09374310669880356</v>
+        <v>0.09351955256368076</v>
       </c>
       <c r="C86">
-        <v>25.47869253279229</v>
+        <v>24.53081937516431</v>
       </c>
       <c r="D86">
-        <v>114.3506925327923</v>
+        <v>114.4608193751643</v>
       </c>
       <c r="E86">
-        <v>88.872</v>
+        <v>89.92999999999999</v>
       </c>
       <c r="F86">
-        <v>88.872</v>
+        <v>89.92999999999999</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -8306,28 +8306,28 @@
         <v>37.42</v>
       </c>
       <c r="M86">
-        <v>4.754652</v>
+        <v>4.811254999999999</v>
       </c>
       <c r="N86">
-        <v>32.665348</v>
+        <v>32.608745</v>
       </c>
       <c r="O86">
-        <v>8.166337</v>
+        <v>8.15218625</v>
       </c>
       <c r="P86">
-        <v>24.499011</v>
+        <v>24.45655875</v>
       </c>
       <c r="Q86">
-        <v>27.279011</v>
+        <v>27.23655875</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3752381668675221</v>
+        <v>0.3960886837578717</v>
       </c>
       <c r="T86">
-        <v>3.946584350939967</v>
+        <v>4.196368170619713</v>
       </c>
       <c r="U86">
         <v>0.0535</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>7.870186924300664</v>
+        <v>7.777596489897127</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09351955256368076</v>
+        <v>0.09329599842855796</v>
       </c>
       <c r="C87">
-        <v>24.53081937516431</v>
+        <v>23.58315854003905</v>
       </c>
       <c r="D87">
-        <v>114.4608193751643</v>
+        <v>114.5711585400391</v>
       </c>
       <c r="E87">
-        <v>89.92999999999999</v>
+        <v>90.988</v>
       </c>
       <c r="F87">
-        <v>89.92999999999999</v>
+        <v>90.988</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -8388,28 +8388,28 @@
         <v>37.42</v>
       </c>
       <c r="M87">
-        <v>4.811254999999999</v>
+        <v>4.867858</v>
       </c>
       <c r="N87">
-        <v>32.608745</v>
+        <v>32.552142</v>
       </c>
       <c r="O87">
-        <v>8.15218625</v>
+        <v>8.138035500000001</v>
       </c>
       <c r="P87">
-        <v>24.45655875</v>
+        <v>24.4141065</v>
       </c>
       <c r="Q87">
-        <v>27.23655875</v>
+        <v>27.1941065</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3960886837578717</v>
+        <v>0.4199178459182711</v>
       </c>
       <c r="T87">
-        <v>4.196368170619713</v>
+        <v>4.481835393110849</v>
       </c>
       <c r="U87">
         <v>0.0535</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>7.777596489897127</v>
+        <v>7.687159321409951</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09329599842855796</v>
+        <v>0.09359444429343516</v>
       </c>
       <c r="C88">
-        <v>23.58315854003905</v>
+        <v>22.37790272395766</v>
       </c>
       <c r="D88">
-        <v>114.5711585400391</v>
+        <v>114.4239027239577</v>
       </c>
       <c r="E88">
-        <v>90.988</v>
+        <v>92.04599999999999</v>
       </c>
       <c r="F88">
-        <v>90.988</v>
+        <v>92.04599999999999</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -8470,45 +8470,45 @@
         <v>37.42</v>
       </c>
       <c r="M88">
-        <v>4.867858</v>
+        <v>4.9980978</v>
       </c>
       <c r="N88">
-        <v>32.552142</v>
+        <v>32.42190220000001</v>
       </c>
       <c r="O88">
-        <v>8.138035500000001</v>
+        <v>8.105475550000001</v>
       </c>
       <c r="P88">
-        <v>24.4141065</v>
+        <v>24.31642665</v>
       </c>
       <c r="Q88">
-        <v>27.1941065</v>
+        <v>27.09642665000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4199178459182711</v>
+        <v>0.4474130330264243</v>
       </c>
       <c r="T88">
-        <v>4.481835393110849</v>
+        <v>4.811220649831391</v>
       </c>
       <c r="U88">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V88">
         <v>0.25</v>
       </c>
       <c r="W88">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y88">
-        <v>7.687159321409951</v>
+        <v>7.486848296565946</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09359444429343516</v>
+        <v>0.09337689015831237</v>
       </c>
       <c r="C89">
-        <v>22.37790272395766</v>
+        <v>21.42720841896478</v>
       </c>
       <c r="D89">
-        <v>114.4239027239577</v>
+        <v>114.5312084189648</v>
       </c>
       <c r="E89">
-        <v>92.04599999999999</v>
+        <v>93.104</v>
       </c>
       <c r="F89">
-        <v>92.04599999999999</v>
+        <v>93.104</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -8552,28 +8552,28 @@
         <v>37.42</v>
       </c>
       <c r="M89">
-        <v>4.9980978</v>
+        <v>5.0555472</v>
       </c>
       <c r="N89">
-        <v>32.42190220000001</v>
+        <v>32.3644528</v>
       </c>
       <c r="O89">
-        <v>8.105475550000001</v>
+        <v>8.091113200000001</v>
       </c>
       <c r="P89">
-        <v>24.31642665</v>
+        <v>24.2733396</v>
       </c>
       <c r="Q89">
-        <v>27.09642665000001</v>
+        <v>27.0533396</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4474130330264243</v>
+        <v>0.4794907513192698</v>
       </c>
       <c r="T89">
-        <v>4.811220649831391</v>
+        <v>5.195503449338692</v>
       </c>
       <c r="U89">
         <v>0.0543</v>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>7.486848296565946</v>
+        <v>7.40177047501406</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09337689015831237</v>
+        <v>0.09315933602318957</v>
       </c>
       <c r="C90">
-        <v>21.42720841896478</v>
+        <v>20.47671556349856</v>
       </c>
       <c r="D90">
-        <v>114.5312084189648</v>
+        <v>114.6387155634986</v>
       </c>
       <c r="E90">
-        <v>93.104</v>
+        <v>94.16199999999999</v>
       </c>
       <c r="F90">
-        <v>93.104</v>
+        <v>94.16199999999999</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -8634,28 +8634,28 @@
         <v>37.42</v>
       </c>
       <c r="M90">
-        <v>5.0555472</v>
+        <v>5.1129966</v>
       </c>
       <c r="N90">
-        <v>32.3644528</v>
+        <v>32.3070034</v>
       </c>
       <c r="O90">
-        <v>8.091113200000001</v>
+        <v>8.07675085</v>
       </c>
       <c r="P90">
-        <v>24.2733396</v>
+        <v>24.23025255</v>
       </c>
       <c r="Q90">
-        <v>27.0533396</v>
+        <v>27.01025255</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4794907513192698</v>
+        <v>0.5174007820289961</v>
       </c>
       <c r="T90">
-        <v>5.195503449338692</v>
+        <v>5.649655848756409</v>
       </c>
       <c r="U90">
         <v>0.0543</v>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>7.40177047501406</v>
+        <v>7.318604514620644</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09315933602318957</v>
+        <v>0.09294178188806676</v>
       </c>
       <c r="C91">
-        <v>20.47671556349856</v>
+        <v>19.5264247253766</v>
       </c>
       <c r="D91">
-        <v>114.6387155634986</v>
+        <v>114.7464247253766</v>
       </c>
       <c r="E91">
-        <v>94.16199999999999</v>
+        <v>95.22</v>
       </c>
       <c r="F91">
-        <v>94.16199999999999</v>
+        <v>95.22</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -8716,28 +8716,28 @@
         <v>37.42</v>
       </c>
       <c r="M91">
-        <v>5.1129966</v>
+        <v>5.170446</v>
       </c>
       <c r="N91">
-        <v>32.3070034</v>
+        <v>32.249554</v>
       </c>
       <c r="O91">
-        <v>8.07675085</v>
+        <v>8.062388500000001</v>
       </c>
       <c r="P91">
-        <v>24.23025255</v>
+        <v>24.1871655</v>
       </c>
       <c r="Q91">
-        <v>27.01025255</v>
+        <v>26.9671655</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5174007820289961</v>
+        <v>0.5628928188806678</v>
       </c>
       <c r="T91">
-        <v>5.649655848756409</v>
+        <v>6.194638728057672</v>
       </c>
       <c r="U91">
         <v>0.0543</v>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>7.318604514620644</v>
+        <v>7.237286686680415</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09294178188806676</v>
+        <v>0.09272422775294396</v>
       </c>
       <c r="C92">
-        <v>19.5264247253766</v>
+        <v>18.57633647455246</v>
       </c>
       <c r="D92">
-        <v>114.7464247253766</v>
+        <v>114.8543364745525</v>
       </c>
       <c r="E92">
-        <v>95.22</v>
+        <v>96.27800000000001</v>
       </c>
       <c r="F92">
-        <v>95.22</v>
+        <v>96.27800000000001</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -8798,28 +8798,28 @@
         <v>37.42</v>
       </c>
       <c r="M92">
-        <v>5.170446</v>
+        <v>5.2278954</v>
       </c>
       <c r="N92">
-        <v>32.249554</v>
+        <v>32.1921046</v>
       </c>
       <c r="O92">
-        <v>8.062388500000001</v>
+        <v>8.04802615</v>
       </c>
       <c r="P92">
-        <v>24.1871655</v>
+        <v>24.14407845</v>
       </c>
       <c r="Q92">
-        <v>26.9671655</v>
+        <v>26.92407845</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5628928188806678</v>
+        <v>0.6184941972549332</v>
       </c>
       <c r="T92">
-        <v>6.194638728057672</v>
+        <v>6.860728913870325</v>
       </c>
       <c r="U92">
         <v>0.0543</v>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>7.237286686680415</v>
+        <v>7.15775606374986</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09272422775294396</v>
+        <v>0.09250667361782118</v>
       </c>
       <c r="C93">
-        <v>18.57633647455246</v>
+        <v>17.62645138312578</v>
       </c>
       <c r="D93">
-        <v>114.8543364745525</v>
+        <v>114.9624513831258</v>
       </c>
       <c r="E93">
-        <v>96.27800000000001</v>
+        <v>97.336</v>
       </c>
       <c r="F93">
-        <v>96.27800000000001</v>
+        <v>97.336</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -8880,28 +8880,28 @@
         <v>37.42</v>
       </c>
       <c r="M93">
-        <v>5.2278954</v>
+        <v>5.2853448</v>
       </c>
       <c r="N93">
-        <v>32.1921046</v>
+        <v>32.1346552</v>
       </c>
       <c r="O93">
-        <v>8.04802615</v>
+        <v>8.033663800000001</v>
       </c>
       <c r="P93">
-        <v>24.14407845</v>
+        <v>24.10099140000001</v>
       </c>
       <c r="Q93">
-        <v>26.92407845</v>
+        <v>26.88099140000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6184941972549332</v>
+        <v>0.6879959202227651</v>
       </c>
       <c r="T93">
-        <v>6.860728913870325</v>
+        <v>7.693341646136144</v>
       </c>
       <c r="U93">
         <v>0.0543</v>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>7.15775606374986</v>
+        <v>7.079954367404754</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09250667361782118</v>
+        <v>0.09228911948269838</v>
       </c>
       <c r="C94">
-        <v>17.62645138312578</v>
+        <v>16.67677002535231</v>
       </c>
       <c r="D94">
-        <v>114.9624513831258</v>
+        <v>115.0707700253523</v>
       </c>
       <c r="E94">
-        <v>97.336</v>
+        <v>98.39400000000001</v>
       </c>
       <c r="F94">
-        <v>97.336</v>
+        <v>98.39400000000001</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -8962,28 +8962,28 @@
         <v>37.42</v>
       </c>
       <c r="M94">
-        <v>5.2853448</v>
+        <v>5.3427942</v>
       </c>
       <c r="N94">
-        <v>32.1346552</v>
+        <v>32.0772058</v>
       </c>
       <c r="O94">
-        <v>8.033663800000001</v>
+        <v>8.01930145</v>
       </c>
       <c r="P94">
-        <v>24.10099140000001</v>
+        <v>24.05790435</v>
       </c>
       <c r="Q94">
-        <v>26.88099140000001</v>
+        <v>26.83790435</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6879959202227651</v>
+        <v>0.7773552783242631</v>
       </c>
       <c r="T94">
-        <v>7.693341646136144</v>
+        <v>8.763843730477909</v>
       </c>
       <c r="U94">
         <v>0.0543</v>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>7.079954367404754</v>
+        <v>7.003825825819756</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09228911948269838</v>
+        <v>0.09207156534757559</v>
       </c>
       <c r="C95">
-        <v>16.67677002535231</v>
+        <v>15.72729297765414</v>
       </c>
       <c r="D95">
-        <v>115.0707700253523</v>
+        <v>115.1792929776541</v>
       </c>
       <c r="E95">
-        <v>98.39400000000001</v>
+        <v>99.452</v>
       </c>
       <c r="F95">
-        <v>98.39400000000001</v>
+        <v>99.452</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -9044,28 +9044,28 @@
         <v>37.42</v>
       </c>
       <c r="M95">
-        <v>5.3427942</v>
+        <v>5.4002436</v>
       </c>
       <c r="N95">
-        <v>32.0772058</v>
+        <v>32.01975640000001</v>
       </c>
       <c r="O95">
-        <v>8.01930145</v>
+        <v>8.004939100000001</v>
       </c>
       <c r="P95">
-        <v>24.05790435</v>
+        <v>24.0148173</v>
       </c>
       <c r="Q95">
-        <v>26.83790435</v>
+        <v>26.79481730000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7773552783242631</v>
+        <v>0.8965010891262606</v>
       </c>
       <c r="T95">
-        <v>8.763843730477909</v>
+        <v>10.1911798429336</v>
       </c>
       <c r="U95">
         <v>0.0543</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>7.003825825819756</v>
+        <v>6.929317040438696</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09207156534757559</v>
+        <v>0.09185401121245279</v>
       </c>
       <c r="C96">
-        <v>15.72729297765414</v>
+        <v>14.77802081862984</v>
       </c>
       <c r="D96">
-        <v>115.1792929776541</v>
+        <v>115.2880208186298</v>
       </c>
       <c r="E96">
-        <v>99.452</v>
+        <v>100.51</v>
       </c>
       <c r="F96">
-        <v>99.452</v>
+        <v>100.51</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -9126,28 +9126,28 @@
         <v>37.42</v>
       </c>
       <c r="M96">
-        <v>5.4002436</v>
+        <v>5.457693000000001</v>
       </c>
       <c r="N96">
-        <v>32.01975640000001</v>
+        <v>31.962307</v>
       </c>
       <c r="O96">
-        <v>8.004939100000001</v>
+        <v>7.990576750000001</v>
       </c>
       <c r="P96">
-        <v>24.0148173</v>
+        <v>23.97173025</v>
       </c>
       <c r="Q96">
-        <v>26.79481730000001</v>
+        <v>26.75173025</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8965010891262606</v>
+        <v>1.063305224249057</v>
       </c>
       <c r="T96">
-        <v>10.1911798429336</v>
+        <v>12.18945040037156</v>
       </c>
       <c r="U96">
         <v>0.0543</v>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>6.929317040438696</v>
+        <v>6.856376861065655</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09185401121245279</v>
+        <v>0.09163645707732999</v>
       </c>
       <c r="C97">
-        <v>14.77802081862984</v>
+        <v>13.82895412906493</v>
       </c>
       <c r="D97">
-        <v>115.2880208186298</v>
+        <v>115.3969541290649</v>
       </c>
       <c r="E97">
-        <v>100.51</v>
+        <v>101.568</v>
       </c>
       <c r="F97">
-        <v>100.51</v>
+        <v>101.568</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -9208,28 +9208,28 @@
         <v>37.42</v>
       </c>
       <c r="M97">
-        <v>5.457693000000001</v>
+        <v>5.515142400000001</v>
       </c>
       <c r="N97">
-        <v>31.962307</v>
+        <v>31.9048576</v>
       </c>
       <c r="O97">
-        <v>7.990576750000001</v>
+        <v>7.9762144</v>
       </c>
       <c r="P97">
-        <v>23.97173025</v>
+        <v>23.9286432</v>
       </c>
       <c r="Q97">
-        <v>26.75173025</v>
+        <v>26.7086432</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.063305224249057</v>
+        <v>1.313511426933252</v>
       </c>
       <c r="T97">
-        <v>12.18945040037156</v>
+        <v>15.18685623652851</v>
       </c>
       <c r="U97">
         <v>0.0543</v>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>6.856376861065655</v>
+        <v>6.784956268762887</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09163645707733001</v>
+        <v>0.0914189029422072</v>
       </c>
       <c r="C98">
-        <v>13.82895412906494</v>
+        <v>12.88009349194201</v>
       </c>
       <c r="D98">
-        <v>115.3969541290649</v>
+        <v>115.506093491942</v>
       </c>
       <c r="E98">
-        <v>101.568</v>
+        <v>102.626</v>
       </c>
       <c r="F98">
-        <v>101.568</v>
+        <v>102.626</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -9290,28 +9290,28 @@
         <v>37.42</v>
       </c>
       <c r="M98">
-        <v>5.5151424</v>
+        <v>5.5725918</v>
       </c>
       <c r="N98">
-        <v>31.9048576</v>
+        <v>31.8474082</v>
       </c>
       <c r="O98">
-        <v>7.9762144</v>
+        <v>7.961852050000001</v>
       </c>
       <c r="P98">
-        <v>23.9286432</v>
+        <v>23.88555615</v>
       </c>
       <c r="Q98">
-        <v>26.7086432</v>
+        <v>26.66555615</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.313511426933249</v>
+        <v>1.730521764740239</v>
       </c>
       <c r="T98">
-        <v>15.18685623652847</v>
+        <v>20.18253263012336</v>
       </c>
       <c r="U98">
         <v>0.0543</v>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>6.784956268762888</v>
+        <v>6.715008265992138</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0914189029422072</v>
+        <v>0.09120134880708441</v>
       </c>
       <c r="C99">
-        <v>12.88009349194201</v>
+        <v>11.9314394924512</v>
       </c>
       <c r="D99">
-        <v>115.506093491942</v>
+        <v>115.6154394924512</v>
       </c>
       <c r="E99">
-        <v>102.626</v>
+        <v>103.684</v>
       </c>
       <c r="F99">
-        <v>102.626</v>
+        <v>103.684</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -9372,28 +9372,28 @@
         <v>37.42</v>
       </c>
       <c r="M99">
-        <v>5.5725918</v>
+        <v>5.6300412</v>
       </c>
       <c r="N99">
-        <v>31.8474082</v>
+        <v>31.7899588</v>
       </c>
       <c r="O99">
-        <v>7.961852050000001</v>
+        <v>7.9474897</v>
       </c>
       <c r="P99">
-        <v>23.88555615</v>
+        <v>23.8424691</v>
       </c>
       <c r="Q99">
-        <v>26.66555615</v>
+        <v>26.6224691</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.730521764740239</v>
+        <v>2.564542440354218</v>
       </c>
       <c r="T99">
-        <v>20.18253263012336</v>
+        <v>30.17388541731315</v>
       </c>
       <c r="U99">
         <v>0.0543</v>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>6.715008265992138</v>
+        <v>6.646487773482013</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09120134880708441</v>
+        <v>0.09098379467196162</v>
       </c>
       <c r="C100">
-        <v>11.9314394924512</v>
+        <v>10.98299271800074</v>
       </c>
       <c r="D100">
-        <v>115.6154394924512</v>
+        <v>115.7249927180007</v>
       </c>
       <c r="E100">
-        <v>103.684</v>
+        <v>104.742</v>
       </c>
       <c r="F100">
-        <v>103.684</v>
+        <v>104.742</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -9454,28 +9454,28 @@
         <v>37.42</v>
       </c>
       <c r="M100">
-        <v>5.6300412</v>
+        <v>5.687490599999999</v>
       </c>
       <c r="N100">
-        <v>31.7899588</v>
+        <v>31.7325094</v>
       </c>
       <c r="O100">
-        <v>7.9474897</v>
+        <v>7.93312735</v>
       </c>
       <c r="P100">
-        <v>23.8424691</v>
+        <v>23.79938205</v>
       </c>
       <c r="Q100">
-        <v>26.6224691</v>
+        <v>26.57938205</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.564542440354218</v>
+        <v>5.066604467196157</v>
       </c>
       <c r="T100">
-        <v>30.17388541731315</v>
+        <v>60.1479437788825</v>
       </c>
       <c r="U100">
         <v>0.0543</v>
@@ -9492,91 +9492,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>6.646487773482013</v>
+        <v>6.579351533345831</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09098379467196162</v>
-      </c>
-      <c r="C101">
-        <v>10.98299271800074</v>
-      </c>
-      <c r="D101">
-        <v>115.7249927180007</v>
-      </c>
-      <c r="E101">
-        <v>104.742</v>
-      </c>
-      <c r="F101">
-        <v>104.742</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>105.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>40.2</v>
-      </c>
-      <c r="K101">
-        <v>2.78</v>
-      </c>
-      <c r="L101">
-        <v>37.42</v>
-      </c>
-      <c r="M101">
-        <v>5.687490599999999</v>
-      </c>
-      <c r="N101">
-        <v>31.7325094</v>
-      </c>
-      <c r="O101">
-        <v>7.93312735</v>
-      </c>
-      <c r="P101">
-        <v>23.79938205</v>
-      </c>
-      <c r="Q101">
-        <v>26.57938205</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.066604467196157</v>
-      </c>
-      <c r="T101">
-        <v>60.1479437788825</v>
-      </c>
-      <c r="U101">
-        <v>0.0543</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.040725</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A2/A</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>6.579351533345831</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
